--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -22,14 +22,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.0;(0.0);&quot;&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0;(#,##0);&quot;&quot;"/>
-    <numFmt numFmtId="170" formatCode="mmm yyyy"/>
-    <numFmt numFmtId="171" formatCode="0.0;(0.0);&quot;—&quot;"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0;(0.0);&quot;—&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0;(0.0);&quot;&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0;(#,##0);&quot;&quot;"/>
+    <numFmt numFmtId="171" formatCode="mmm yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -128,36 +128,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1346,7 +1357,7 @@
           <t>Starting</t>
         </is>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="25">
         <f>Targets!$B$6</f>
         <v/>
       </c>
@@ -1364,7 +1375,7 @@
           <t>Avg weight change</t>
         </is>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="26">
         <f>IFERROR(INDEX('Monthly Summary'!C:C,$D$5),"—")</f>
         <v/>
       </c>
@@ -1375,7 +1386,7 @@
           <t>Current (this week avg)</t>
         </is>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="25">
         <f>IFERROR(INDEX('Weekly Summary'!B:B,$D$4),"—")</f>
         <v/>
       </c>
@@ -1404,7 +1415,7 @@
           <t>Goal</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="25">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -1433,7 +1444,7 @@
           <t>Lbs lost so far</t>
         </is>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="25">
         <f>IFERROR(Targets!$B$6-INDEX('Weekly Summary'!B:B,$D$4),"—")</f>
         <v/>
       </c>
@@ -1451,7 +1462,7 @@
           <t>Pace to goal (weeks, from today)</t>
         </is>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="25">
         <f>Targets!$B$19</f>
         <v/>
       </c>
@@ -1462,7 +1473,7 @@
           <t>Lbs to go</t>
         </is>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="25">
         <f>IFERROR(INDEX('Weekly Summary'!B:B,$D$4)-Targets!$B$7,"—")</f>
         <v/>
       </c>
@@ -1471,7 +1482,7 @@
           <t>Weight change this week</t>
         </is>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="26">
         <f>IFERROR(INDEX('Weekly Summary'!C:C,$D$4),"—")</f>
         <v/>
       </c>
@@ -1549,7 +1560,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
     </row>
@@ -1585,7 +1596,7 @@
           <t>Activity multiplier</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="27" t="n">
         <v>1.375</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1733,7 +1744,7 @@
           <t>Pace to goal (weeks)</t>
         </is>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="28">
         <f>ROUND((B6-B7)/(B11/500),1)</f>
         <v/>
       </c>
@@ -1840,10 +1851,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="29" t="n">
         <v>46249</v>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="30" t="n">
         <v>201.4</v>
       </c>
       <c r="C2" s="18" t="n">
@@ -1869,28 +1880,28 @@
           <t>EXAMPLE ROW — overwrite with your real day</t>
         </is>
       </c>
-      <c r="J2" s="19">
+      <c r="J2" s="31">
         <f>IF(C2="","",C2-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K2" s="19">
+      <c r="K2" s="31">
         <f>IF(D2="","",D2-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L2" s="19">
+      <c r="L2" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B2,$A$2:$A2,"&gt;="&amp;(A2-6),$A$2:$A2,"&lt;="&amp;A2),"")</f>
         <v/>
       </c>
-      <c r="M2" s="19">
+      <c r="M2" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C2,$A$2:$A2,"&gt;="&amp;(A2-6),$A$2:$A2,"&lt;="&amp;A2),"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n">
+      <c r="A3" s="32" t="n">
         <v>46250</v>
       </c>
-      <c r="B3" s="17" t="n"/>
+      <c r="B3" s="30" t="n"/>
       <c r="C3" s="18" t="n"/>
       <c r="D3" s="18" t="n"/>
       <c r="E3" s="18" t="n"/>
@@ -1898,28 +1909,28 @@
       <c r="G3" s="18" t="n"/>
       <c r="H3" s="18" t="n"/>
       <c r="I3" s="18" t="n"/>
-      <c r="J3" s="19">
+      <c r="J3" s="31">
         <f>IF(C3="","",C3-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="31">
         <f>IF(D3="","",D3-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B3,$A$2:$A3,"&gt;="&amp;(A3-6),$A$2:$A3,"&lt;="&amp;A3),"")</f>
         <v/>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C3,$A$2:$A3,"&gt;="&amp;(A3-6),$A$2:$A3,"&lt;="&amp;A3),"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="32" t="n">
         <v>46251</v>
       </c>
-      <c r="B4" s="17" t="n"/>
+      <c r="B4" s="30" t="n"/>
       <c r="C4" s="18" t="n"/>
       <c r="D4" s="18" t="n"/>
       <c r="E4" s="18" t="n"/>
@@ -1927,28 +1938,28 @@
       <c r="G4" s="18" t="n"/>
       <c r="H4" s="18" t="n"/>
       <c r="I4" s="18" t="n"/>
-      <c r="J4" s="19">
+      <c r="J4" s="31">
         <f>IF(C4="","",C4-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="31">
         <f>IF(D4="","",D4-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B4,$A$2:$A4,"&gt;="&amp;(A4-6),$A$2:$A4,"&lt;="&amp;A4),"")</f>
         <v/>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C4,$A$2:$A4,"&gt;="&amp;(A4-6),$A$2:$A4,"&lt;="&amp;A4),"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="32" t="n">
         <v>46252</v>
       </c>
-      <c r="B5" s="17" t="n"/>
+      <c r="B5" s="30" t="n"/>
       <c r="C5" s="18" t="n"/>
       <c r="D5" s="18" t="n"/>
       <c r="E5" s="18" t="n"/>
@@ -1956,28 +1967,28 @@
       <c r="G5" s="18" t="n"/>
       <c r="H5" s="18" t="n"/>
       <c r="I5" s="18" t="n"/>
-      <c r="J5" s="19">
+      <c r="J5" s="31">
         <f>IF(C5="","",C5-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="31">
         <f>IF(D5="","",D5-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B5,$A$2:$A5,"&gt;="&amp;(A5-6),$A$2:$A5,"&lt;="&amp;A5),"")</f>
         <v/>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C5,$A$2:$A5,"&gt;="&amp;(A5-6),$A$2:$A5,"&lt;="&amp;A5),"")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="32" t="n">
         <v>46253</v>
       </c>
-      <c r="B6" s="17" t="n"/>
+      <c r="B6" s="30" t="n"/>
       <c r="C6" s="18" t="n"/>
       <c r="D6" s="18" t="n"/>
       <c r="E6" s="18" t="n"/>
@@ -1985,28 +1996,28 @@
       <c r="G6" s="18" t="n"/>
       <c r="H6" s="18" t="n"/>
       <c r="I6" s="18" t="n"/>
-      <c r="J6" s="19">
+      <c r="J6" s="31">
         <f>IF(C6="","",C6-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="31">
         <f>IF(D6="","",D6-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B6,$A$2:$A6,"&gt;="&amp;(A6-6),$A$2:$A6,"&lt;="&amp;A6),"")</f>
         <v/>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C6,$A$2:$A6,"&gt;="&amp;(A6-6),$A$2:$A6,"&lt;="&amp;A6),"")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="32" t="n">
         <v>46254</v>
       </c>
-      <c r="B7" s="17" t="n"/>
+      <c r="B7" s="30" t="n"/>
       <c r="C7" s="18" t="n"/>
       <c r="D7" s="18" t="n"/>
       <c r="E7" s="18" t="n"/>
@@ -2014,28 +2025,28 @@
       <c r="G7" s="18" t="n"/>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="n"/>
-      <c r="J7" s="19">
+      <c r="J7" s="31">
         <f>IF(C7="","",C7-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="31">
         <f>IF(D7="","",D7-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B7,$A$2:$A7,"&gt;="&amp;(A7-6),$A$2:$A7,"&lt;="&amp;A7),"")</f>
         <v/>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C7,$A$2:$A7,"&gt;="&amp;(A7-6),$A$2:$A7,"&lt;="&amp;A7),"")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="32" t="n">
         <v>46255</v>
       </c>
-      <c r="B8" s="17" t="n"/>
+      <c r="B8" s="30" t="n"/>
       <c r="C8" s="18" t="n"/>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="18" t="n"/>
@@ -2043,28 +2054,28 @@
       <c r="G8" s="18" t="n"/>
       <c r="H8" s="18" t="n"/>
       <c r="I8" s="18" t="n"/>
-      <c r="J8" s="19">
+      <c r="J8" s="31">
         <f>IF(C8="","",C8-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="31">
         <f>IF(D8="","",D8-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B8,$A$2:$A8,"&gt;="&amp;(A8-6),$A$2:$A8,"&lt;="&amp;A8),"")</f>
         <v/>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C8,$A$2:$A8,"&gt;="&amp;(A8-6),$A$2:$A8,"&lt;="&amp;A8),"")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="32" t="n">
         <v>46256</v>
       </c>
-      <c r="B9" s="17" t="n"/>
+      <c r="B9" s="30" t="n"/>
       <c r="C9" s="18" t="n"/>
       <c r="D9" s="18" t="n"/>
       <c r="E9" s="18" t="n"/>
@@ -2072,28 +2083,28 @@
       <c r="G9" s="18" t="n"/>
       <c r="H9" s="18" t="n"/>
       <c r="I9" s="18" t="n"/>
-      <c r="J9" s="19">
+      <c r="J9" s="31">
         <f>IF(C9="","",C9-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="31">
         <f>IF(D9="","",D9-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B9,$A$2:$A9,"&gt;="&amp;(A9-6),$A$2:$A9,"&lt;="&amp;A9),"")</f>
         <v/>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C9,$A$2:$A9,"&gt;="&amp;(A9-6),$A$2:$A9,"&lt;="&amp;A9),"")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="32" t="n">
         <v>46257</v>
       </c>
-      <c r="B10" s="17" t="n"/>
+      <c r="B10" s="30" t="n"/>
       <c r="C10" s="18" t="n"/>
       <c r="D10" s="18" t="n"/>
       <c r="E10" s="18" t="n"/>
@@ -2101,28 +2112,28 @@
       <c r="G10" s="18" t="n"/>
       <c r="H10" s="18" t="n"/>
       <c r="I10" s="18" t="n"/>
-      <c r="J10" s="19">
+      <c r="J10" s="31">
         <f>IF(C10="","",C10-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="31">
         <f>IF(D10="","",D10-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B10,$A$2:$A10,"&gt;="&amp;(A10-6),$A$2:$A10,"&lt;="&amp;A10),"")</f>
         <v/>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C10,$A$2:$A10,"&gt;="&amp;(A10-6),$A$2:$A10,"&lt;="&amp;A10),"")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="32" t="n">
         <v>46258</v>
       </c>
-      <c r="B11" s="17" t="n"/>
+      <c r="B11" s="30" t="n"/>
       <c r="C11" s="18" t="n"/>
       <c r="D11" s="18" t="n"/>
       <c r="E11" s="18" t="n"/>
@@ -2130,28 +2141,28 @@
       <c r="G11" s="18" t="n"/>
       <c r="H11" s="18" t="n"/>
       <c r="I11" s="18" t="n"/>
-      <c r="J11" s="19">
+      <c r="J11" s="31">
         <f>IF(C11="","",C11-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="31">
         <f>IF(D11="","",D11-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B11,$A$2:$A11,"&gt;="&amp;(A11-6),$A$2:$A11,"&lt;="&amp;A11),"")</f>
         <v/>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C11,$A$2:$A11,"&gt;="&amp;(A11-6),$A$2:$A11,"&lt;="&amp;A11),"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="32" t="n">
         <v>46259</v>
       </c>
-      <c r="B12" s="17" t="n"/>
+      <c r="B12" s="30" t="n"/>
       <c r="C12" s="18" t="n"/>
       <c r="D12" s="18" t="n"/>
       <c r="E12" s="18" t="n"/>
@@ -2159,28 +2170,28 @@
       <c r="G12" s="18" t="n"/>
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="18" t="n"/>
-      <c r="J12" s="19">
+      <c r="J12" s="31">
         <f>IF(C12="","",C12-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="31">
         <f>IF(D12="","",D12-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B12,$A$2:$A12,"&gt;="&amp;(A12-6),$A$2:$A12,"&lt;="&amp;A12),"")</f>
         <v/>
       </c>
-      <c r="M12" s="19">
+      <c r="M12" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C12,$A$2:$A12,"&gt;="&amp;(A12-6),$A$2:$A12,"&lt;="&amp;A12),"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="32" t="n">
         <v>46260</v>
       </c>
-      <c r="B13" s="17" t="n"/>
+      <c r="B13" s="30" t="n"/>
       <c r="C13" s="18" t="n"/>
       <c r="D13" s="18" t="n"/>
       <c r="E13" s="18" t="n"/>
@@ -2188,28 +2199,28 @@
       <c r="G13" s="18" t="n"/>
       <c r="H13" s="18" t="n"/>
       <c r="I13" s="18" t="n"/>
-      <c r="J13" s="19">
+      <c r="J13" s="31">
         <f>IF(C13="","",C13-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="31">
         <f>IF(D13="","",D13-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B13,$A$2:$A13,"&gt;="&amp;(A13-6),$A$2:$A13,"&lt;="&amp;A13),"")</f>
         <v/>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C13,$A$2:$A13,"&gt;="&amp;(A13-6),$A$2:$A13,"&lt;="&amp;A13),"")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="32" t="n">
         <v>46261</v>
       </c>
-      <c r="B14" s="17" t="n"/>
+      <c r="B14" s="30" t="n"/>
       <c r="C14" s="18" t="n"/>
       <c r="D14" s="18" t="n"/>
       <c r="E14" s="18" t="n"/>
@@ -2217,28 +2228,28 @@
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="18" t="n"/>
       <c r="I14" s="18" t="n"/>
-      <c r="J14" s="19">
+      <c r="J14" s="31">
         <f>IF(C14="","",C14-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="31">
         <f>IF(D14="","",D14-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B14,$A$2:$A14,"&gt;="&amp;(A14-6),$A$2:$A14,"&lt;="&amp;A14),"")</f>
         <v/>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C14,$A$2:$A14,"&gt;="&amp;(A14-6),$A$2:$A14,"&lt;="&amp;A14),"")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="32" t="n">
         <v>46262</v>
       </c>
-      <c r="B15" s="17" t="n"/>
+      <c r="B15" s="30" t="n"/>
       <c r="C15" s="18" t="n"/>
       <c r="D15" s="18" t="n"/>
       <c r="E15" s="18" t="n"/>
@@ -2246,28 +2257,28 @@
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="18" t="n"/>
       <c r="I15" s="18" t="n"/>
-      <c r="J15" s="19">
+      <c r="J15" s="31">
         <f>IF(C15="","",C15-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="31">
         <f>IF(D15="","",D15-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B15,$A$2:$A15,"&gt;="&amp;(A15-6),$A$2:$A15,"&lt;="&amp;A15),"")</f>
         <v/>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C15,$A$2:$A15,"&gt;="&amp;(A15-6),$A$2:$A15,"&lt;="&amp;A15),"")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="32" t="n">
         <v>46263</v>
       </c>
-      <c r="B16" s="17" t="n"/>
+      <c r="B16" s="30" t="n"/>
       <c r="C16" s="18" t="n"/>
       <c r="D16" s="18" t="n"/>
       <c r="E16" s="18" t="n"/>
@@ -2275,28 +2286,28 @@
       <c r="G16" s="18" t="n"/>
       <c r="H16" s="18" t="n"/>
       <c r="I16" s="18" t="n"/>
-      <c r="J16" s="19">
+      <c r="J16" s="31">
         <f>IF(C16="","",C16-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="31">
         <f>IF(D16="","",D16-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B16,$A$2:$A16,"&gt;="&amp;(A16-6),$A$2:$A16,"&lt;="&amp;A16),"")</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C16,$A$2:$A16,"&gt;="&amp;(A16-6),$A$2:$A16,"&lt;="&amp;A16),"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="32" t="n">
         <v>46264</v>
       </c>
-      <c r="B17" s="17" t="n"/>
+      <c r="B17" s="30" t="n"/>
       <c r="C17" s="18" t="n"/>
       <c r="D17" s="18" t="n"/>
       <c r="E17" s="18" t="n"/>
@@ -2304,28 +2315,28 @@
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="18" t="n"/>
       <c r="I17" s="18" t="n"/>
-      <c r="J17" s="19">
+      <c r="J17" s="31">
         <f>IF(C17="","",C17-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="31">
         <f>IF(D17="","",D17-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B17,$A$2:$A17,"&gt;="&amp;(A17-6),$A$2:$A17,"&lt;="&amp;A17),"")</f>
         <v/>
       </c>
-      <c r="M17" s="19">
+      <c r="M17" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C17,$A$2:$A17,"&gt;="&amp;(A17-6),$A$2:$A17,"&lt;="&amp;A17),"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="32" t="n">
         <v>46265</v>
       </c>
-      <c r="B18" s="17" t="n"/>
+      <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n"/>
       <c r="D18" s="18" t="n"/>
       <c r="E18" s="18" t="n"/>
@@ -2333,28 +2344,28 @@
       <c r="G18" s="18" t="n"/>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="n"/>
-      <c r="J18" s="19">
+      <c r="J18" s="31">
         <f>IF(C18="","",C18-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="31">
         <f>IF(D18="","",D18-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B18,$A$2:$A18,"&gt;="&amp;(A18-6),$A$2:$A18,"&lt;="&amp;A18),"")</f>
         <v/>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C18,$A$2:$A18,"&gt;="&amp;(A18-6),$A$2:$A18,"&lt;="&amp;A18),"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="32" t="n">
         <v>46266</v>
       </c>
-      <c r="B19" s="17" t="n"/>
+      <c r="B19" s="30" t="n"/>
       <c r="C19" s="18" t="n"/>
       <c r="D19" s="18" t="n"/>
       <c r="E19" s="18" t="n"/>
@@ -2362,28 +2373,28 @@
       <c r="G19" s="18" t="n"/>
       <c r="H19" s="18" t="n"/>
       <c r="I19" s="18" t="n"/>
-      <c r="J19" s="19">
+      <c r="J19" s="31">
         <f>IF(C19="","",C19-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="31">
         <f>IF(D19="","",D19-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B19,$A$2:$A19,"&gt;="&amp;(A19-6),$A$2:$A19,"&lt;="&amp;A19),"")</f>
         <v/>
       </c>
-      <c r="M19" s="19">
+      <c r="M19" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C19,$A$2:$A19,"&gt;="&amp;(A19-6),$A$2:$A19,"&lt;="&amp;A19),"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="32" t="n">
         <v>46267</v>
       </c>
-      <c r="B20" s="17" t="n"/>
+      <c r="B20" s="30" t="n"/>
       <c r="C20" s="18" t="n"/>
       <c r="D20" s="18" t="n"/>
       <c r="E20" s="18" t="n"/>
@@ -2391,28 +2402,28 @@
       <c r="G20" s="18" t="n"/>
       <c r="H20" s="18" t="n"/>
       <c r="I20" s="18" t="n"/>
-      <c r="J20" s="19">
+      <c r="J20" s="31">
         <f>IF(C20="","",C20-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="31">
         <f>IF(D20="","",D20-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B20,$A$2:$A20,"&gt;="&amp;(A20-6),$A$2:$A20,"&lt;="&amp;A20),"")</f>
         <v/>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C20,$A$2:$A20,"&gt;="&amp;(A20-6),$A$2:$A20,"&lt;="&amp;A20),"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="32" t="n">
         <v>46268</v>
       </c>
-      <c r="B21" s="17" t="n"/>
+      <c r="B21" s="30" t="n"/>
       <c r="C21" s="18" t="n"/>
       <c r="D21" s="18" t="n"/>
       <c r="E21" s="18" t="n"/>
@@ -2420,28 +2431,28 @@
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="18" t="n"/>
       <c r="I21" s="18" t="n"/>
-      <c r="J21" s="19">
+      <c r="J21" s="31">
         <f>IF(C21="","",C21-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="31">
         <f>IF(D21="","",D21-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B21,$A$2:$A21,"&gt;="&amp;(A21-6),$A$2:$A21,"&lt;="&amp;A21),"")</f>
         <v/>
       </c>
-      <c r="M21" s="19">
+      <c r="M21" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C21,$A$2:$A21,"&gt;="&amp;(A21-6),$A$2:$A21,"&lt;="&amp;A21),"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="32" t="n">
         <v>46269</v>
       </c>
-      <c r="B22" s="17" t="n"/>
+      <c r="B22" s="30" t="n"/>
       <c r="C22" s="18" t="n"/>
       <c r="D22" s="18" t="n"/>
       <c r="E22" s="18" t="n"/>
@@ -2449,28 +2460,28 @@
       <c r="G22" s="18" t="n"/>
       <c r="H22" s="18" t="n"/>
       <c r="I22" s="18" t="n"/>
-      <c r="J22" s="19">
+      <c r="J22" s="31">
         <f>IF(C22="","",C22-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="31">
         <f>IF(D22="","",D22-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B22,$A$2:$A22,"&gt;="&amp;(A22-6),$A$2:$A22,"&lt;="&amp;A22),"")</f>
         <v/>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C22,$A$2:$A22,"&gt;="&amp;(A22-6),$A$2:$A22,"&lt;="&amp;A22),"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="n">
+      <c r="A23" s="32" t="n">
         <v>46270</v>
       </c>
-      <c r="B23" s="17" t="n"/>
+      <c r="B23" s="30" t="n"/>
       <c r="C23" s="18" t="n"/>
       <c r="D23" s="18" t="n"/>
       <c r="E23" s="18" t="n"/>
@@ -2478,28 +2489,28 @@
       <c r="G23" s="18" t="n"/>
       <c r="H23" s="18" t="n"/>
       <c r="I23" s="18" t="n"/>
-      <c r="J23" s="19">
+      <c r="J23" s="31">
         <f>IF(C23="","",C23-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="31">
         <f>IF(D23="","",D23-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B23,$A$2:$A23,"&gt;="&amp;(A23-6),$A$2:$A23,"&lt;="&amp;A23),"")</f>
         <v/>
       </c>
-      <c r="M23" s="19">
+      <c r="M23" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C23,$A$2:$A23,"&gt;="&amp;(A23-6),$A$2:$A23,"&lt;="&amp;A23),"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="n">
+      <c r="A24" s="32" t="n">
         <v>46271</v>
       </c>
-      <c r="B24" s="17" t="n"/>
+      <c r="B24" s="30" t="n"/>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="18" t="n"/>
       <c r="E24" s="18" t="n"/>
@@ -2507,28 +2518,28 @@
       <c r="G24" s="18" t="n"/>
       <c r="H24" s="18" t="n"/>
       <c r="I24" s="18" t="n"/>
-      <c r="J24" s="19">
+      <c r="J24" s="31">
         <f>IF(C24="","",C24-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="31">
         <f>IF(D24="","",D24-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B24,$A$2:$A24,"&gt;="&amp;(A24-6),$A$2:$A24,"&lt;="&amp;A24),"")</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C24,$A$2:$A24,"&gt;="&amp;(A24-6),$A$2:$A24,"&lt;="&amp;A24),"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n">
+      <c r="A25" s="32" t="n">
         <v>46272</v>
       </c>
-      <c r="B25" s="17" t="n"/>
+      <c r="B25" s="30" t="n"/>
       <c r="C25" s="18" t="n"/>
       <c r="D25" s="18" t="n"/>
       <c r="E25" s="18" t="n"/>
@@ -2536,28 +2547,28 @@
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="18" t="n"/>
       <c r="I25" s="18" t="n"/>
-      <c r="J25" s="19">
+      <c r="J25" s="31">
         <f>IF(C25="","",C25-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="31">
         <f>IF(D25="","",D25-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B25,$A$2:$A25,"&gt;="&amp;(A25-6),$A$2:$A25,"&lt;="&amp;A25),"")</f>
         <v/>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C25,$A$2:$A25,"&gt;="&amp;(A25-6),$A$2:$A25,"&lt;="&amp;A25),"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="32" t="n">
         <v>46273</v>
       </c>
-      <c r="B26" s="17" t="n"/>
+      <c r="B26" s="30" t="n"/>
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="18" t="n"/>
       <c r="E26" s="18" t="n"/>
@@ -2565,28 +2576,28 @@
       <c r="G26" s="18" t="n"/>
       <c r="H26" s="18" t="n"/>
       <c r="I26" s="18" t="n"/>
-      <c r="J26" s="19">
+      <c r="J26" s="31">
         <f>IF(C26="","",C26-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="31">
         <f>IF(D26="","",D26-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B26,$A$2:$A26,"&gt;="&amp;(A26-6),$A$2:$A26,"&lt;="&amp;A26),"")</f>
         <v/>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C26,$A$2:$A26,"&gt;="&amp;(A26-6),$A$2:$A26,"&lt;="&amp;A26),"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="32" t="n">
         <v>46274</v>
       </c>
-      <c r="B27" s="17" t="n"/>
+      <c r="B27" s="30" t="n"/>
       <c r="C27" s="18" t="n"/>
       <c r="D27" s="18" t="n"/>
       <c r="E27" s="18" t="n"/>
@@ -2594,28 +2605,28 @@
       <c r="G27" s="18" t="n"/>
       <c r="H27" s="18" t="n"/>
       <c r="I27" s="18" t="n"/>
-      <c r="J27" s="19">
+      <c r="J27" s="31">
         <f>IF(C27="","",C27-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="31">
         <f>IF(D27="","",D27-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B27,$A$2:$A27,"&gt;="&amp;(A27-6),$A$2:$A27,"&lt;="&amp;A27),"")</f>
         <v/>
       </c>
-      <c r="M27" s="19">
+      <c r="M27" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C27,$A$2:$A27,"&gt;="&amp;(A27-6),$A$2:$A27,"&lt;="&amp;A27),"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="32" t="n">
         <v>46275</v>
       </c>
-      <c r="B28" s="17" t="n"/>
+      <c r="B28" s="30" t="n"/>
       <c r="C28" s="18" t="n"/>
       <c r="D28" s="18" t="n"/>
       <c r="E28" s="18" t="n"/>
@@ -2623,28 +2634,28 @@
       <c r="G28" s="18" t="n"/>
       <c r="H28" s="18" t="n"/>
       <c r="I28" s="18" t="n"/>
-      <c r="J28" s="19">
+      <c r="J28" s="31">
         <f>IF(C28="","",C28-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="31">
         <f>IF(D28="","",D28-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B28,$A$2:$A28,"&gt;="&amp;(A28-6),$A$2:$A28,"&lt;="&amp;A28),"")</f>
         <v/>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C28,$A$2:$A28,"&gt;="&amp;(A28-6),$A$2:$A28,"&lt;="&amp;A28),"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="n">
+      <c r="A29" s="32" t="n">
         <v>46276</v>
       </c>
-      <c r="B29" s="17" t="n"/>
+      <c r="B29" s="30" t="n"/>
       <c r="C29" s="18" t="n"/>
       <c r="D29" s="18" t="n"/>
       <c r="E29" s="18" t="n"/>
@@ -2652,28 +2663,28 @@
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="18" t="n"/>
       <c r="I29" s="18" t="n"/>
-      <c r="J29" s="19">
+      <c r="J29" s="31">
         <f>IF(C29="","",C29-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="31">
         <f>IF(D29="","",D29-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B29,$A$2:$A29,"&gt;="&amp;(A29-6),$A$2:$A29,"&lt;="&amp;A29),"")</f>
         <v/>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C29,$A$2:$A29,"&gt;="&amp;(A29-6),$A$2:$A29,"&lt;="&amp;A29),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="n">
+      <c r="A30" s="32" t="n">
         <v>46277</v>
       </c>
-      <c r="B30" s="17" t="n"/>
+      <c r="B30" s="30" t="n"/>
       <c r="C30" s="18" t="n"/>
       <c r="D30" s="18" t="n"/>
       <c r="E30" s="18" t="n"/>
@@ -2681,28 +2692,28 @@
       <c r="G30" s="18" t="n"/>
       <c r="H30" s="18" t="n"/>
       <c r="I30" s="18" t="n"/>
-      <c r="J30" s="19">
+      <c r="J30" s="31">
         <f>IF(C30="","",C30-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="31">
         <f>IF(D30="","",D30-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B30,$A$2:$A30,"&gt;="&amp;(A30-6),$A$2:$A30,"&lt;="&amp;A30),"")</f>
         <v/>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C30,$A$2:$A30,"&gt;="&amp;(A30-6),$A$2:$A30,"&lt;="&amp;A30),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="n">
+      <c r="A31" s="32" t="n">
         <v>46278</v>
       </c>
-      <c r="B31" s="17" t="n"/>
+      <c r="B31" s="30" t="n"/>
       <c r="C31" s="18" t="n"/>
       <c r="D31" s="18" t="n"/>
       <c r="E31" s="18" t="n"/>
@@ -2710,28 +2721,28 @@
       <c r="G31" s="18" t="n"/>
       <c r="H31" s="18" t="n"/>
       <c r="I31" s="18" t="n"/>
-      <c r="J31" s="19">
+      <c r="J31" s="31">
         <f>IF(C31="","",C31-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="31">
         <f>IF(D31="","",D31-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B31,$A$2:$A31,"&gt;="&amp;(A31-6),$A$2:$A31,"&lt;="&amp;A31),"")</f>
         <v/>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C31,$A$2:$A31,"&gt;="&amp;(A31-6),$A$2:$A31,"&lt;="&amp;A31),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="32" t="n">
         <v>46279</v>
       </c>
-      <c r="B32" s="17" t="n"/>
+      <c r="B32" s="30" t="n"/>
       <c r="C32" s="18" t="n"/>
       <c r="D32" s="18" t="n"/>
       <c r="E32" s="18" t="n"/>
@@ -2739,28 +2750,28 @@
       <c r="G32" s="18" t="n"/>
       <c r="H32" s="18" t="n"/>
       <c r="I32" s="18" t="n"/>
-      <c r="J32" s="19">
+      <c r="J32" s="31">
         <f>IF(C32="","",C32-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="31">
         <f>IF(D32="","",D32-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B32,$A$2:$A32,"&gt;="&amp;(A32-6),$A$2:$A32,"&lt;="&amp;A32),"")</f>
         <v/>
       </c>
-      <c r="M32" s="19">
+      <c r="M32" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C32,$A$2:$A32,"&gt;="&amp;(A32-6),$A$2:$A32,"&lt;="&amp;A32),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="n">
+      <c r="A33" s="32" t="n">
         <v>46280</v>
       </c>
-      <c r="B33" s="17" t="n"/>
+      <c r="B33" s="30" t="n"/>
       <c r="C33" s="18" t="n"/>
       <c r="D33" s="18" t="n"/>
       <c r="E33" s="18" t="n"/>
@@ -2768,28 +2779,28 @@
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="18" t="n"/>
       <c r="I33" s="18" t="n"/>
-      <c r="J33" s="19">
+      <c r="J33" s="31">
         <f>IF(C33="","",C33-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="31">
         <f>IF(D33="","",D33-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B33,$A$2:$A33,"&gt;="&amp;(A33-6),$A$2:$A33,"&lt;="&amp;A33),"")</f>
         <v/>
       </c>
-      <c r="M33" s="19">
+      <c r="M33" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C33,$A$2:$A33,"&gt;="&amp;(A33-6),$A$2:$A33,"&lt;="&amp;A33),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="n">
+      <c r="A34" s="32" t="n">
         <v>46281</v>
       </c>
-      <c r="B34" s="17" t="n"/>
+      <c r="B34" s="30" t="n"/>
       <c r="C34" s="18" t="n"/>
       <c r="D34" s="18" t="n"/>
       <c r="E34" s="18" t="n"/>
@@ -2797,28 +2808,28 @@
       <c r="G34" s="18" t="n"/>
       <c r="H34" s="18" t="n"/>
       <c r="I34" s="18" t="n"/>
-      <c r="J34" s="19">
+      <c r="J34" s="31">
         <f>IF(C34="","",C34-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K34" s="19">
+      <c r="K34" s="31">
         <f>IF(D34="","",D34-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B34,$A$2:$A34,"&gt;="&amp;(A34-6),$A$2:$A34,"&lt;="&amp;A34),"")</f>
         <v/>
       </c>
-      <c r="M34" s="19">
+      <c r="M34" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C34,$A$2:$A34,"&gt;="&amp;(A34-6),$A$2:$A34,"&lt;="&amp;A34),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="n">
+      <c r="A35" s="32" t="n">
         <v>46282</v>
       </c>
-      <c r="B35" s="17" t="n"/>
+      <c r="B35" s="30" t="n"/>
       <c r="C35" s="18" t="n"/>
       <c r="D35" s="18" t="n"/>
       <c r="E35" s="18" t="n"/>
@@ -2826,28 +2837,28 @@
       <c r="G35" s="18" t="n"/>
       <c r="H35" s="18" t="n"/>
       <c r="I35" s="18" t="n"/>
-      <c r="J35" s="19">
+      <c r="J35" s="31">
         <f>IF(C35="","",C35-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="31">
         <f>IF(D35="","",D35-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B35,$A$2:$A35,"&gt;="&amp;(A35-6),$A$2:$A35,"&lt;="&amp;A35),"")</f>
         <v/>
       </c>
-      <c r="M35" s="19">
+      <c r="M35" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C35,$A$2:$A35,"&gt;="&amp;(A35-6),$A$2:$A35,"&lt;="&amp;A35),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="n">
+      <c r="A36" s="32" t="n">
         <v>46283</v>
       </c>
-      <c r="B36" s="17" t="n"/>
+      <c r="B36" s="30" t="n"/>
       <c r="C36" s="18" t="n"/>
       <c r="D36" s="18" t="n"/>
       <c r="E36" s="18" t="n"/>
@@ -2855,28 +2866,28 @@
       <c r="G36" s="18" t="n"/>
       <c r="H36" s="18" t="n"/>
       <c r="I36" s="18" t="n"/>
-      <c r="J36" s="19">
+      <c r="J36" s="31">
         <f>IF(C36="","",C36-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="31">
         <f>IF(D36="","",D36-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B36,$A$2:$A36,"&gt;="&amp;(A36-6),$A$2:$A36,"&lt;="&amp;A36),"")</f>
         <v/>
       </c>
-      <c r="M36" s="19">
+      <c r="M36" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C36,$A$2:$A36,"&gt;="&amp;(A36-6),$A$2:$A36,"&lt;="&amp;A36),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="n">
+      <c r="A37" s="32" t="n">
         <v>46284</v>
       </c>
-      <c r="B37" s="17" t="n"/>
+      <c r="B37" s="30" t="n"/>
       <c r="C37" s="18" t="n"/>
       <c r="D37" s="18" t="n"/>
       <c r="E37" s="18" t="n"/>
@@ -2884,28 +2895,28 @@
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="18" t="n"/>
       <c r="I37" s="18" t="n"/>
-      <c r="J37" s="19">
+      <c r="J37" s="31">
         <f>IF(C37="","",C37-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="31">
         <f>IF(D37="","",D37-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B37,$A$2:$A37,"&gt;="&amp;(A37-6),$A$2:$A37,"&lt;="&amp;A37),"")</f>
         <v/>
       </c>
-      <c r="M37" s="19">
+      <c r="M37" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C37,$A$2:$A37,"&gt;="&amp;(A37-6),$A$2:$A37,"&lt;="&amp;A37),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="n">
+      <c r="A38" s="32" t="n">
         <v>46285</v>
       </c>
-      <c r="B38" s="17" t="n"/>
+      <c r="B38" s="30" t="n"/>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="18" t="n"/>
       <c r="E38" s="18" t="n"/>
@@ -2913,28 +2924,28 @@
       <c r="G38" s="18" t="n"/>
       <c r="H38" s="18" t="n"/>
       <c r="I38" s="18" t="n"/>
-      <c r="J38" s="19">
+      <c r="J38" s="31">
         <f>IF(C38="","",C38-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="31">
         <f>IF(D38="","",D38-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B38,$A$2:$A38,"&gt;="&amp;(A38-6),$A$2:$A38,"&lt;="&amp;A38),"")</f>
         <v/>
       </c>
-      <c r="M38" s="19">
+      <c r="M38" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C38,$A$2:$A38,"&gt;="&amp;(A38-6),$A$2:$A38,"&lt;="&amp;A38),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="n">
+      <c r="A39" s="32" t="n">
         <v>46286</v>
       </c>
-      <c r="B39" s="17" t="n"/>
+      <c r="B39" s="30" t="n"/>
       <c r="C39" s="18" t="n"/>
       <c r="D39" s="18" t="n"/>
       <c r="E39" s="18" t="n"/>
@@ -2942,28 +2953,28 @@
       <c r="G39" s="18" t="n"/>
       <c r="H39" s="18" t="n"/>
       <c r="I39" s="18" t="n"/>
-      <c r="J39" s="19">
+      <c r="J39" s="31">
         <f>IF(C39="","",C39-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="31">
         <f>IF(D39="","",D39-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B39,$A$2:$A39,"&gt;="&amp;(A39-6),$A$2:$A39,"&lt;="&amp;A39),"")</f>
         <v/>
       </c>
-      <c r="M39" s="19">
+      <c r="M39" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C39,$A$2:$A39,"&gt;="&amp;(A39-6),$A$2:$A39,"&lt;="&amp;A39),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n">
+      <c r="A40" s="32" t="n">
         <v>46287</v>
       </c>
-      <c r="B40" s="17" t="n"/>
+      <c r="B40" s="30" t="n"/>
       <c r="C40" s="18" t="n"/>
       <c r="D40" s="18" t="n"/>
       <c r="E40" s="18" t="n"/>
@@ -2971,28 +2982,28 @@
       <c r="G40" s="18" t="n"/>
       <c r="H40" s="18" t="n"/>
       <c r="I40" s="18" t="n"/>
-      <c r="J40" s="19">
+      <c r="J40" s="31">
         <f>IF(C40="","",C40-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="31">
         <f>IF(D40="","",D40-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B40,$A$2:$A40,"&gt;="&amp;(A40-6),$A$2:$A40,"&lt;="&amp;A40),"")</f>
         <v/>
       </c>
-      <c r="M40" s="19">
+      <c r="M40" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C40,$A$2:$A40,"&gt;="&amp;(A40-6),$A$2:$A40,"&lt;="&amp;A40),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="n">
+      <c r="A41" s="32" t="n">
         <v>46288</v>
       </c>
-      <c r="B41" s="17" t="n"/>
+      <c r="B41" s="30" t="n"/>
       <c r="C41" s="18" t="n"/>
       <c r="D41" s="18" t="n"/>
       <c r="E41" s="18" t="n"/>
@@ -3000,28 +3011,28 @@
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="18" t="n"/>
       <c r="I41" s="18" t="n"/>
-      <c r="J41" s="19">
+      <c r="J41" s="31">
         <f>IF(C41="","",C41-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="31">
         <f>IF(D41="","",D41-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B41,$A$2:$A41,"&gt;="&amp;(A41-6),$A$2:$A41,"&lt;="&amp;A41),"")</f>
         <v/>
       </c>
-      <c r="M41" s="19">
+      <c r="M41" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C41,$A$2:$A41,"&gt;="&amp;(A41-6),$A$2:$A41,"&lt;="&amp;A41),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="n">
+      <c r="A42" s="32" t="n">
         <v>46289</v>
       </c>
-      <c r="B42" s="17" t="n"/>
+      <c r="B42" s="30" t="n"/>
       <c r="C42" s="18" t="n"/>
       <c r="D42" s="18" t="n"/>
       <c r="E42" s="18" t="n"/>
@@ -3029,28 +3040,28 @@
       <c r="G42" s="18" t="n"/>
       <c r="H42" s="18" t="n"/>
       <c r="I42" s="18" t="n"/>
-      <c r="J42" s="19">
+      <c r="J42" s="31">
         <f>IF(C42="","",C42-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="31">
         <f>IF(D42="","",D42-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B42,$A$2:$A42,"&gt;="&amp;(A42-6),$A$2:$A42,"&lt;="&amp;A42),"")</f>
         <v/>
       </c>
-      <c r="M42" s="19">
+      <c r="M42" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C42,$A$2:$A42,"&gt;="&amp;(A42-6),$A$2:$A42,"&lt;="&amp;A42),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="n">
+      <c r="A43" s="32" t="n">
         <v>46290</v>
       </c>
-      <c r="B43" s="17" t="n"/>
+      <c r="B43" s="30" t="n"/>
       <c r="C43" s="18" t="n"/>
       <c r="D43" s="18" t="n"/>
       <c r="E43" s="18" t="n"/>
@@ -3058,28 +3069,28 @@
       <c r="G43" s="18" t="n"/>
       <c r="H43" s="18" t="n"/>
       <c r="I43" s="18" t="n"/>
-      <c r="J43" s="19">
+      <c r="J43" s="31">
         <f>IF(C43="","",C43-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="31">
         <f>IF(D43="","",D43-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B43,$A$2:$A43,"&gt;="&amp;(A43-6),$A$2:$A43,"&lt;="&amp;A43),"")</f>
         <v/>
       </c>
-      <c r="M43" s="19">
+      <c r="M43" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C43,$A$2:$A43,"&gt;="&amp;(A43-6),$A$2:$A43,"&lt;="&amp;A43),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="n">
+      <c r="A44" s="32" t="n">
         <v>46291</v>
       </c>
-      <c r="B44" s="17" t="n"/>
+      <c r="B44" s="30" t="n"/>
       <c r="C44" s="18" t="n"/>
       <c r="D44" s="18" t="n"/>
       <c r="E44" s="18" t="n"/>
@@ -3087,28 +3098,28 @@
       <c r="G44" s="18" t="n"/>
       <c r="H44" s="18" t="n"/>
       <c r="I44" s="18" t="n"/>
-      <c r="J44" s="19">
+      <c r="J44" s="31">
         <f>IF(C44="","",C44-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="31">
         <f>IF(D44="","",D44-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B44,$A$2:$A44,"&gt;="&amp;(A44-6),$A$2:$A44,"&lt;="&amp;A44),"")</f>
         <v/>
       </c>
-      <c r="M44" s="19">
+      <c r="M44" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C44,$A$2:$A44,"&gt;="&amp;(A44-6),$A$2:$A44,"&lt;="&amp;A44),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="n">
+      <c r="A45" s="32" t="n">
         <v>46292</v>
       </c>
-      <c r="B45" s="17" t="n"/>
+      <c r="B45" s="30" t="n"/>
       <c r="C45" s="18" t="n"/>
       <c r="D45" s="18" t="n"/>
       <c r="E45" s="18" t="n"/>
@@ -3116,28 +3127,28 @@
       <c r="G45" s="18" t="n"/>
       <c r="H45" s="18" t="n"/>
       <c r="I45" s="18" t="n"/>
-      <c r="J45" s="19">
+      <c r="J45" s="31">
         <f>IF(C45="","",C45-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K45" s="19">
+      <c r="K45" s="31">
         <f>IF(D45="","",D45-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B45,$A$2:$A45,"&gt;="&amp;(A45-6),$A$2:$A45,"&lt;="&amp;A45),"")</f>
         <v/>
       </c>
-      <c r="M45" s="19">
+      <c r="M45" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C45,$A$2:$A45,"&gt;="&amp;(A45-6),$A$2:$A45,"&lt;="&amp;A45),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="n">
+      <c r="A46" s="32" t="n">
         <v>46293</v>
       </c>
-      <c r="B46" s="17" t="n"/>
+      <c r="B46" s="30" t="n"/>
       <c r="C46" s="18" t="n"/>
       <c r="D46" s="18" t="n"/>
       <c r="E46" s="18" t="n"/>
@@ -3145,28 +3156,28 @@
       <c r="G46" s="18" t="n"/>
       <c r="H46" s="18" t="n"/>
       <c r="I46" s="18" t="n"/>
-      <c r="J46" s="19">
+      <c r="J46" s="31">
         <f>IF(C46="","",C46-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K46" s="19">
+      <c r="K46" s="31">
         <f>IF(D46="","",D46-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B46,$A$2:$A46,"&gt;="&amp;(A46-6),$A$2:$A46,"&lt;="&amp;A46),"")</f>
         <v/>
       </c>
-      <c r="M46" s="19">
+      <c r="M46" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C46,$A$2:$A46,"&gt;="&amp;(A46-6),$A$2:$A46,"&lt;="&amp;A46),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="n">
+      <c r="A47" s="32" t="n">
         <v>46294</v>
       </c>
-      <c r="B47" s="17" t="n"/>
+      <c r="B47" s="30" t="n"/>
       <c r="C47" s="18" t="n"/>
       <c r="D47" s="18" t="n"/>
       <c r="E47" s="18" t="n"/>
@@ -3174,28 +3185,28 @@
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="18" t="n"/>
       <c r="I47" s="18" t="n"/>
-      <c r="J47" s="19">
+      <c r="J47" s="31">
         <f>IF(C47="","",C47-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K47" s="19">
+      <c r="K47" s="31">
         <f>IF(D47="","",D47-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B47,$A$2:$A47,"&gt;="&amp;(A47-6),$A$2:$A47,"&lt;="&amp;A47),"")</f>
         <v/>
       </c>
-      <c r="M47" s="19">
+      <c r="M47" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C47,$A$2:$A47,"&gt;="&amp;(A47-6),$A$2:$A47,"&lt;="&amp;A47),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="n">
+      <c r="A48" s="32" t="n">
         <v>46295</v>
       </c>
-      <c r="B48" s="17" t="n"/>
+      <c r="B48" s="30" t="n"/>
       <c r="C48" s="18" t="n"/>
       <c r="D48" s="18" t="n"/>
       <c r="E48" s="18" t="n"/>
@@ -3203,28 +3214,28 @@
       <c r="G48" s="18" t="n"/>
       <c r="H48" s="18" t="n"/>
       <c r="I48" s="18" t="n"/>
-      <c r="J48" s="19">
+      <c r="J48" s="31">
         <f>IF(C48="","",C48-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K48" s="19">
+      <c r="K48" s="31">
         <f>IF(D48="","",D48-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B48,$A$2:$A48,"&gt;="&amp;(A48-6),$A$2:$A48,"&lt;="&amp;A48),"")</f>
         <v/>
       </c>
-      <c r="M48" s="19">
+      <c r="M48" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C48,$A$2:$A48,"&gt;="&amp;(A48-6),$A$2:$A48,"&lt;="&amp;A48),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="n">
+      <c r="A49" s="32" t="n">
         <v>46296</v>
       </c>
-      <c r="B49" s="17" t="n"/>
+      <c r="B49" s="30" t="n"/>
       <c r="C49" s="18" t="n"/>
       <c r="D49" s="18" t="n"/>
       <c r="E49" s="18" t="n"/>
@@ -3232,28 +3243,28 @@
       <c r="G49" s="18" t="n"/>
       <c r="H49" s="18" t="n"/>
       <c r="I49" s="18" t="n"/>
-      <c r="J49" s="19">
+      <c r="J49" s="31">
         <f>IF(C49="","",C49-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K49" s="19">
+      <c r="K49" s="31">
         <f>IF(D49="","",D49-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B49,$A$2:$A49,"&gt;="&amp;(A49-6),$A$2:$A49,"&lt;="&amp;A49),"")</f>
         <v/>
       </c>
-      <c r="M49" s="19">
+      <c r="M49" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C49,$A$2:$A49,"&gt;="&amp;(A49-6),$A$2:$A49,"&lt;="&amp;A49),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="n">
+      <c r="A50" s="32" t="n">
         <v>46297</v>
       </c>
-      <c r="B50" s="17" t="n"/>
+      <c r="B50" s="30" t="n"/>
       <c r="C50" s="18" t="n"/>
       <c r="D50" s="18" t="n"/>
       <c r="E50" s="18" t="n"/>
@@ -3261,28 +3272,28 @@
       <c r="G50" s="18" t="n"/>
       <c r="H50" s="18" t="n"/>
       <c r="I50" s="18" t="n"/>
-      <c r="J50" s="19">
+      <c r="J50" s="31">
         <f>IF(C50="","",C50-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K50" s="19">
+      <c r="K50" s="31">
         <f>IF(D50="","",D50-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L50" s="19">
+      <c r="L50" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B50,$A$2:$A50,"&gt;="&amp;(A50-6),$A$2:$A50,"&lt;="&amp;A50),"")</f>
         <v/>
       </c>
-      <c r="M50" s="19">
+      <c r="M50" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C50,$A$2:$A50,"&gt;="&amp;(A50-6),$A$2:$A50,"&lt;="&amp;A50),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="n">
+      <c r="A51" s="32" t="n">
         <v>46298</v>
       </c>
-      <c r="B51" s="17" t="n"/>
+      <c r="B51" s="30" t="n"/>
       <c r="C51" s="18" t="n"/>
       <c r="D51" s="18" t="n"/>
       <c r="E51" s="18" t="n"/>
@@ -3290,28 +3301,28 @@
       <c r="G51" s="18" t="n"/>
       <c r="H51" s="18" t="n"/>
       <c r="I51" s="18" t="n"/>
-      <c r="J51" s="19">
+      <c r="J51" s="31">
         <f>IF(C51="","",C51-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K51" s="19">
+      <c r="K51" s="31">
         <f>IF(D51="","",D51-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L51" s="19">
+      <c r="L51" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B51,$A$2:$A51,"&gt;="&amp;(A51-6),$A$2:$A51,"&lt;="&amp;A51),"")</f>
         <v/>
       </c>
-      <c r="M51" s="19">
+      <c r="M51" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C51,$A$2:$A51,"&gt;="&amp;(A51-6),$A$2:$A51,"&lt;="&amp;A51),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="n">
+      <c r="A52" s="32" t="n">
         <v>46299</v>
       </c>
-      <c r="B52" s="17" t="n"/>
+      <c r="B52" s="30" t="n"/>
       <c r="C52" s="18" t="n"/>
       <c r="D52" s="18" t="n"/>
       <c r="E52" s="18" t="n"/>
@@ -3319,28 +3330,28 @@
       <c r="G52" s="18" t="n"/>
       <c r="H52" s="18" t="n"/>
       <c r="I52" s="18" t="n"/>
-      <c r="J52" s="19">
+      <c r="J52" s="31">
         <f>IF(C52="","",C52-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K52" s="19">
+      <c r="K52" s="31">
         <f>IF(D52="","",D52-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B52,$A$2:$A52,"&gt;="&amp;(A52-6),$A$2:$A52,"&lt;="&amp;A52),"")</f>
         <v/>
       </c>
-      <c r="M52" s="19">
+      <c r="M52" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C52,$A$2:$A52,"&gt;="&amp;(A52-6),$A$2:$A52,"&lt;="&amp;A52),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="n">
+      <c r="A53" s="32" t="n">
         <v>46300</v>
       </c>
-      <c r="B53" s="17" t="n"/>
+      <c r="B53" s="30" t="n"/>
       <c r="C53" s="18" t="n"/>
       <c r="D53" s="18" t="n"/>
       <c r="E53" s="18" t="n"/>
@@ -3348,28 +3359,28 @@
       <c r="G53" s="18" t="n"/>
       <c r="H53" s="18" t="n"/>
       <c r="I53" s="18" t="n"/>
-      <c r="J53" s="19">
+      <c r="J53" s="31">
         <f>IF(C53="","",C53-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="31">
         <f>IF(D53="","",D53-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B53,$A$2:$A53,"&gt;="&amp;(A53-6),$A$2:$A53,"&lt;="&amp;A53),"")</f>
         <v/>
       </c>
-      <c r="M53" s="19">
+      <c r="M53" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C53,$A$2:$A53,"&gt;="&amp;(A53-6),$A$2:$A53,"&lt;="&amp;A53),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="n">
+      <c r="A54" s="32" t="n">
         <v>46301</v>
       </c>
-      <c r="B54" s="17" t="n"/>
+      <c r="B54" s="30" t="n"/>
       <c r="C54" s="18" t="n"/>
       <c r="D54" s="18" t="n"/>
       <c r="E54" s="18" t="n"/>
@@ -3377,28 +3388,28 @@
       <c r="G54" s="18" t="n"/>
       <c r="H54" s="18" t="n"/>
       <c r="I54" s="18" t="n"/>
-      <c r="J54" s="19">
+      <c r="J54" s="31">
         <f>IF(C54="","",C54-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K54" s="19">
+      <c r="K54" s="31">
         <f>IF(D54="","",D54-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B54,$A$2:$A54,"&gt;="&amp;(A54-6),$A$2:$A54,"&lt;="&amp;A54),"")</f>
         <v/>
       </c>
-      <c r="M54" s="19">
+      <c r="M54" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C54,$A$2:$A54,"&gt;="&amp;(A54-6),$A$2:$A54,"&lt;="&amp;A54),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="n">
+      <c r="A55" s="32" t="n">
         <v>46302</v>
       </c>
-      <c r="B55" s="17" t="n"/>
+      <c r="B55" s="30" t="n"/>
       <c r="C55" s="18" t="n"/>
       <c r="D55" s="18" t="n"/>
       <c r="E55" s="18" t="n"/>
@@ -3406,28 +3417,28 @@
       <c r="G55" s="18" t="n"/>
       <c r="H55" s="18" t="n"/>
       <c r="I55" s="18" t="n"/>
-      <c r="J55" s="19">
+      <c r="J55" s="31">
         <f>IF(C55="","",C55-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K55" s="19">
+      <c r="K55" s="31">
         <f>IF(D55="","",D55-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B55,$A$2:$A55,"&gt;="&amp;(A55-6),$A$2:$A55,"&lt;="&amp;A55),"")</f>
         <v/>
       </c>
-      <c r="M55" s="19">
+      <c r="M55" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C55,$A$2:$A55,"&gt;="&amp;(A55-6),$A$2:$A55,"&lt;="&amp;A55),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="n">
+      <c r="A56" s="32" t="n">
         <v>46303</v>
       </c>
-      <c r="B56" s="17" t="n"/>
+      <c r="B56" s="30" t="n"/>
       <c r="C56" s="18" t="n"/>
       <c r="D56" s="18" t="n"/>
       <c r="E56" s="18" t="n"/>
@@ -3435,28 +3446,28 @@
       <c r="G56" s="18" t="n"/>
       <c r="H56" s="18" t="n"/>
       <c r="I56" s="18" t="n"/>
-      <c r="J56" s="19">
+      <c r="J56" s="31">
         <f>IF(C56="","",C56-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K56" s="19">
+      <c r="K56" s="31">
         <f>IF(D56="","",D56-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B56,$A$2:$A56,"&gt;="&amp;(A56-6),$A$2:$A56,"&lt;="&amp;A56),"")</f>
         <v/>
       </c>
-      <c r="M56" s="19">
+      <c r="M56" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C56,$A$2:$A56,"&gt;="&amp;(A56-6),$A$2:$A56,"&lt;="&amp;A56),"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="n">
+      <c r="A57" s="32" t="n">
         <v>46304</v>
       </c>
-      <c r="B57" s="17" t="n"/>
+      <c r="B57" s="30" t="n"/>
       <c r="C57" s="18" t="n"/>
       <c r="D57" s="18" t="n"/>
       <c r="E57" s="18" t="n"/>
@@ -3464,28 +3475,28 @@
       <c r="G57" s="18" t="n"/>
       <c r="H57" s="18" t="n"/>
       <c r="I57" s="18" t="n"/>
-      <c r="J57" s="19">
+      <c r="J57" s="31">
         <f>IF(C57="","",C57-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K57" s="19">
+      <c r="K57" s="31">
         <f>IF(D57="","",D57-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B57,$A$2:$A57,"&gt;="&amp;(A57-6),$A$2:$A57,"&lt;="&amp;A57),"")</f>
         <v/>
       </c>
-      <c r="M57" s="19">
+      <c r="M57" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C57,$A$2:$A57,"&gt;="&amp;(A57-6),$A$2:$A57,"&lt;="&amp;A57),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="n">
+      <c r="A58" s="32" t="n">
         <v>46305</v>
       </c>
-      <c r="B58" s="17" t="n"/>
+      <c r="B58" s="30" t="n"/>
       <c r="C58" s="18" t="n"/>
       <c r="D58" s="18" t="n"/>
       <c r="E58" s="18" t="n"/>
@@ -3493,28 +3504,28 @@
       <c r="G58" s="18" t="n"/>
       <c r="H58" s="18" t="n"/>
       <c r="I58" s="18" t="n"/>
-      <c r="J58" s="19">
+      <c r="J58" s="31">
         <f>IF(C58="","",C58-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K58" s="19">
+      <c r="K58" s="31">
         <f>IF(D58="","",D58-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B58,$A$2:$A58,"&gt;="&amp;(A58-6),$A$2:$A58,"&lt;="&amp;A58),"")</f>
         <v/>
       </c>
-      <c r="M58" s="19">
+      <c r="M58" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C58,$A$2:$A58,"&gt;="&amp;(A58-6),$A$2:$A58,"&lt;="&amp;A58),"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="n">
+      <c r="A59" s="32" t="n">
         <v>46306</v>
       </c>
-      <c r="B59" s="17" t="n"/>
+      <c r="B59" s="30" t="n"/>
       <c r="C59" s="18" t="n"/>
       <c r="D59" s="18" t="n"/>
       <c r="E59" s="18" t="n"/>
@@ -3522,28 +3533,28 @@
       <c r="G59" s="18" t="n"/>
       <c r="H59" s="18" t="n"/>
       <c r="I59" s="18" t="n"/>
-      <c r="J59" s="19">
+      <c r="J59" s="31">
         <f>IF(C59="","",C59-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K59" s="19">
+      <c r="K59" s="31">
         <f>IF(D59="","",D59-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B59,$A$2:$A59,"&gt;="&amp;(A59-6),$A$2:$A59,"&lt;="&amp;A59),"")</f>
         <v/>
       </c>
-      <c r="M59" s="19">
+      <c r="M59" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C59,$A$2:$A59,"&gt;="&amp;(A59-6),$A$2:$A59,"&lt;="&amp;A59),"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="n">
+      <c r="A60" s="32" t="n">
         <v>46307</v>
       </c>
-      <c r="B60" s="17" t="n"/>
+      <c r="B60" s="30" t="n"/>
       <c r="C60" s="18" t="n"/>
       <c r="D60" s="18" t="n"/>
       <c r="E60" s="18" t="n"/>
@@ -3551,28 +3562,28 @@
       <c r="G60" s="18" t="n"/>
       <c r="H60" s="18" t="n"/>
       <c r="I60" s="18" t="n"/>
-      <c r="J60" s="19">
+      <c r="J60" s="31">
         <f>IF(C60="","",C60-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K60" s="19">
+      <c r="K60" s="31">
         <f>IF(D60="","",D60-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L60" s="19">
+      <c r="L60" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B60,$A$2:$A60,"&gt;="&amp;(A60-6),$A$2:$A60,"&lt;="&amp;A60),"")</f>
         <v/>
       </c>
-      <c r="M60" s="19">
+      <c r="M60" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C60,$A$2:$A60,"&gt;="&amp;(A60-6),$A$2:$A60,"&lt;="&amp;A60),"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="20" t="n">
+      <c r="A61" s="32" t="n">
         <v>46308</v>
       </c>
-      <c r="B61" s="17" t="n"/>
+      <c r="B61" s="30" t="n"/>
       <c r="C61" s="18" t="n"/>
       <c r="D61" s="18" t="n"/>
       <c r="E61" s="18" t="n"/>
@@ -3580,28 +3591,28 @@
       <c r="G61" s="18" t="n"/>
       <c r="H61" s="18" t="n"/>
       <c r="I61" s="18" t="n"/>
-      <c r="J61" s="19">
+      <c r="J61" s="31">
         <f>IF(C61="","",C61-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K61" s="19">
+      <c r="K61" s="31">
         <f>IF(D61="","",D61-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L61" s="19">
+      <c r="L61" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B61,$A$2:$A61,"&gt;="&amp;(A61-6),$A$2:$A61,"&lt;="&amp;A61),"")</f>
         <v/>
       </c>
-      <c r="M61" s="19">
+      <c r="M61" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C61,$A$2:$A61,"&gt;="&amp;(A61-6),$A$2:$A61,"&lt;="&amp;A61),"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="20" t="n">
+      <c r="A62" s="32" t="n">
         <v>46309</v>
       </c>
-      <c r="B62" s="17" t="n"/>
+      <c r="B62" s="30" t="n"/>
       <c r="C62" s="18" t="n"/>
       <c r="D62" s="18" t="n"/>
       <c r="E62" s="18" t="n"/>
@@ -3609,28 +3620,28 @@
       <c r="G62" s="18" t="n"/>
       <c r="H62" s="18" t="n"/>
       <c r="I62" s="18" t="n"/>
-      <c r="J62" s="19">
+      <c r="J62" s="31">
         <f>IF(C62="","",C62-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K62" s="19">
+      <c r="K62" s="31">
         <f>IF(D62="","",D62-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B62,$A$2:$A62,"&gt;="&amp;(A62-6),$A$2:$A62,"&lt;="&amp;A62),"")</f>
         <v/>
       </c>
-      <c r="M62" s="19">
+      <c r="M62" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C62,$A$2:$A62,"&gt;="&amp;(A62-6),$A$2:$A62,"&lt;="&amp;A62),"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="20" t="n">
+      <c r="A63" s="32" t="n">
         <v>46310</v>
       </c>
-      <c r="B63" s="17" t="n"/>
+      <c r="B63" s="30" t="n"/>
       <c r="C63" s="18" t="n"/>
       <c r="D63" s="18" t="n"/>
       <c r="E63" s="18" t="n"/>
@@ -3638,28 +3649,28 @@
       <c r="G63" s="18" t="n"/>
       <c r="H63" s="18" t="n"/>
       <c r="I63" s="18" t="n"/>
-      <c r="J63" s="19">
+      <c r="J63" s="31">
         <f>IF(C63="","",C63-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K63" s="19">
+      <c r="K63" s="31">
         <f>IF(D63="","",D63-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B63,$A$2:$A63,"&gt;="&amp;(A63-6),$A$2:$A63,"&lt;="&amp;A63),"")</f>
         <v/>
       </c>
-      <c r="M63" s="19">
+      <c r="M63" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C63,$A$2:$A63,"&gt;="&amp;(A63-6),$A$2:$A63,"&lt;="&amp;A63),"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="20" t="n">
+      <c r="A64" s="32" t="n">
         <v>46311</v>
       </c>
-      <c r="B64" s="17" t="n"/>
+      <c r="B64" s="30" t="n"/>
       <c r="C64" s="18" t="n"/>
       <c r="D64" s="18" t="n"/>
       <c r="E64" s="18" t="n"/>
@@ -3667,28 +3678,28 @@
       <c r="G64" s="18" t="n"/>
       <c r="H64" s="18" t="n"/>
       <c r="I64" s="18" t="n"/>
-      <c r="J64" s="19">
+      <c r="J64" s="31">
         <f>IF(C64="","",C64-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K64" s="19">
+      <c r="K64" s="31">
         <f>IF(D64="","",D64-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B64,$A$2:$A64,"&gt;="&amp;(A64-6),$A$2:$A64,"&lt;="&amp;A64),"")</f>
         <v/>
       </c>
-      <c r="M64" s="19">
+      <c r="M64" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C64,$A$2:$A64,"&gt;="&amp;(A64-6),$A$2:$A64,"&lt;="&amp;A64),"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="20" t="n">
+      <c r="A65" s="32" t="n">
         <v>46312</v>
       </c>
-      <c r="B65" s="17" t="n"/>
+      <c r="B65" s="30" t="n"/>
       <c r="C65" s="18" t="n"/>
       <c r="D65" s="18" t="n"/>
       <c r="E65" s="18" t="n"/>
@@ -3696,28 +3707,28 @@
       <c r="G65" s="18" t="n"/>
       <c r="H65" s="18" t="n"/>
       <c r="I65" s="18" t="n"/>
-      <c r="J65" s="19">
+      <c r="J65" s="31">
         <f>IF(C65="","",C65-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K65" s="19">
+      <c r="K65" s="31">
         <f>IF(D65="","",D65-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L65" s="19">
+      <c r="L65" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B65,$A$2:$A65,"&gt;="&amp;(A65-6),$A$2:$A65,"&lt;="&amp;A65),"")</f>
         <v/>
       </c>
-      <c r="M65" s="19">
+      <c r="M65" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C65,$A$2:$A65,"&gt;="&amp;(A65-6),$A$2:$A65,"&lt;="&amp;A65),"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="20" t="n">
+      <c r="A66" s="32" t="n">
         <v>46313</v>
       </c>
-      <c r="B66" s="17" t="n"/>
+      <c r="B66" s="30" t="n"/>
       <c r="C66" s="18" t="n"/>
       <c r="D66" s="18" t="n"/>
       <c r="E66" s="18" t="n"/>
@@ -3725,28 +3736,28 @@
       <c r="G66" s="18" t="n"/>
       <c r="H66" s="18" t="n"/>
       <c r="I66" s="18" t="n"/>
-      <c r="J66" s="19">
+      <c r="J66" s="31">
         <f>IF(C66="","",C66-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K66" s="19">
+      <c r="K66" s="31">
         <f>IF(D66="","",D66-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L66" s="19">
+      <c r="L66" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B66,$A$2:$A66,"&gt;="&amp;(A66-6),$A$2:$A66,"&lt;="&amp;A66),"")</f>
         <v/>
       </c>
-      <c r="M66" s="19">
+      <c r="M66" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C66,$A$2:$A66,"&gt;="&amp;(A66-6),$A$2:$A66,"&lt;="&amp;A66),"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="20" t="n">
+      <c r="A67" s="32" t="n">
         <v>46314</v>
       </c>
-      <c r="B67" s="17" t="n"/>
+      <c r="B67" s="30" t="n"/>
       <c r="C67" s="18" t="n"/>
       <c r="D67" s="18" t="n"/>
       <c r="E67" s="18" t="n"/>
@@ -3754,28 +3765,28 @@
       <c r="G67" s="18" t="n"/>
       <c r="H67" s="18" t="n"/>
       <c r="I67" s="18" t="n"/>
-      <c r="J67" s="19">
+      <c r="J67" s="31">
         <f>IF(C67="","",C67-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K67" s="19">
+      <c r="K67" s="31">
         <f>IF(D67="","",D67-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B67,$A$2:$A67,"&gt;="&amp;(A67-6),$A$2:$A67,"&lt;="&amp;A67),"")</f>
         <v/>
       </c>
-      <c r="M67" s="19">
+      <c r="M67" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C67,$A$2:$A67,"&gt;="&amp;(A67-6),$A$2:$A67,"&lt;="&amp;A67),"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="20" t="n">
+      <c r="A68" s="32" t="n">
         <v>46315</v>
       </c>
-      <c r="B68" s="17" t="n"/>
+      <c r="B68" s="30" t="n"/>
       <c r="C68" s="18" t="n"/>
       <c r="D68" s="18" t="n"/>
       <c r="E68" s="18" t="n"/>
@@ -3783,28 +3794,28 @@
       <c r="G68" s="18" t="n"/>
       <c r="H68" s="18" t="n"/>
       <c r="I68" s="18" t="n"/>
-      <c r="J68" s="19">
+      <c r="J68" s="31">
         <f>IF(C68="","",C68-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K68" s="19">
+      <c r="K68" s="31">
         <f>IF(D68="","",D68-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B68,$A$2:$A68,"&gt;="&amp;(A68-6),$A$2:$A68,"&lt;="&amp;A68),"")</f>
         <v/>
       </c>
-      <c r="M68" s="19">
+      <c r="M68" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C68,$A$2:$A68,"&gt;="&amp;(A68-6),$A$2:$A68,"&lt;="&amp;A68),"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="20" t="n">
+      <c r="A69" s="32" t="n">
         <v>46316</v>
       </c>
-      <c r="B69" s="17" t="n"/>
+      <c r="B69" s="30" t="n"/>
       <c r="C69" s="18" t="n"/>
       <c r="D69" s="18" t="n"/>
       <c r="E69" s="18" t="n"/>
@@ -3812,28 +3823,28 @@
       <c r="G69" s="18" t="n"/>
       <c r="H69" s="18" t="n"/>
       <c r="I69" s="18" t="n"/>
-      <c r="J69" s="19">
+      <c r="J69" s="31">
         <f>IF(C69="","",C69-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K69" s="19">
+      <c r="K69" s="31">
         <f>IF(D69="","",D69-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L69" s="19">
+      <c r="L69" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B69,$A$2:$A69,"&gt;="&amp;(A69-6),$A$2:$A69,"&lt;="&amp;A69),"")</f>
         <v/>
       </c>
-      <c r="M69" s="19">
+      <c r="M69" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C69,$A$2:$A69,"&gt;="&amp;(A69-6),$A$2:$A69,"&lt;="&amp;A69),"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="20" t="n">
+      <c r="A70" s="32" t="n">
         <v>46317</v>
       </c>
-      <c r="B70" s="17" t="n"/>
+      <c r="B70" s="30" t="n"/>
       <c r="C70" s="18" t="n"/>
       <c r="D70" s="18" t="n"/>
       <c r="E70" s="18" t="n"/>
@@ -3841,28 +3852,28 @@
       <c r="G70" s="18" t="n"/>
       <c r="H70" s="18" t="n"/>
       <c r="I70" s="18" t="n"/>
-      <c r="J70" s="19">
+      <c r="J70" s="31">
         <f>IF(C70="","",C70-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K70" s="19">
+      <c r="K70" s="31">
         <f>IF(D70="","",D70-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L70" s="19">
+      <c r="L70" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B70,$A$2:$A70,"&gt;="&amp;(A70-6),$A$2:$A70,"&lt;="&amp;A70),"")</f>
         <v/>
       </c>
-      <c r="M70" s="19">
+      <c r="M70" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C70,$A$2:$A70,"&gt;="&amp;(A70-6),$A$2:$A70,"&lt;="&amp;A70),"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="20" t="n">
+      <c r="A71" s="32" t="n">
         <v>46318</v>
       </c>
-      <c r="B71" s="17" t="n"/>
+      <c r="B71" s="30" t="n"/>
       <c r="C71" s="18" t="n"/>
       <c r="D71" s="18" t="n"/>
       <c r="E71" s="18" t="n"/>
@@ -3870,28 +3881,28 @@
       <c r="G71" s="18" t="n"/>
       <c r="H71" s="18" t="n"/>
       <c r="I71" s="18" t="n"/>
-      <c r="J71" s="19">
+      <c r="J71" s="31">
         <f>IF(C71="","",C71-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K71" s="19">
+      <c r="K71" s="31">
         <f>IF(D71="","",D71-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B71,$A$2:$A71,"&gt;="&amp;(A71-6),$A$2:$A71,"&lt;="&amp;A71),"")</f>
         <v/>
       </c>
-      <c r="M71" s="19">
+      <c r="M71" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C71,$A$2:$A71,"&gt;="&amp;(A71-6),$A$2:$A71,"&lt;="&amp;A71),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="20" t="n">
+      <c r="A72" s="32" t="n">
         <v>46319</v>
       </c>
-      <c r="B72" s="17" t="n"/>
+      <c r="B72" s="30" t="n"/>
       <c r="C72" s="18" t="n"/>
       <c r="D72" s="18" t="n"/>
       <c r="E72" s="18" t="n"/>
@@ -3899,28 +3910,28 @@
       <c r="G72" s="18" t="n"/>
       <c r="H72" s="18" t="n"/>
       <c r="I72" s="18" t="n"/>
-      <c r="J72" s="19">
+      <c r="J72" s="31">
         <f>IF(C72="","",C72-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K72" s="19">
+      <c r="K72" s="31">
         <f>IF(D72="","",D72-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B72,$A$2:$A72,"&gt;="&amp;(A72-6),$A$2:$A72,"&lt;="&amp;A72),"")</f>
         <v/>
       </c>
-      <c r="M72" s="19">
+      <c r="M72" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C72,$A$2:$A72,"&gt;="&amp;(A72-6),$A$2:$A72,"&lt;="&amp;A72),"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="20" t="n">
+      <c r="A73" s="32" t="n">
         <v>46320</v>
       </c>
-      <c r="B73" s="17" t="n"/>
+      <c r="B73" s="30" t="n"/>
       <c r="C73" s="18" t="n"/>
       <c r="D73" s="18" t="n"/>
       <c r="E73" s="18" t="n"/>
@@ -3928,28 +3939,28 @@
       <c r="G73" s="18" t="n"/>
       <c r="H73" s="18" t="n"/>
       <c r="I73" s="18" t="n"/>
-      <c r="J73" s="19">
+      <c r="J73" s="31">
         <f>IF(C73="","",C73-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K73" s="19">
+      <c r="K73" s="31">
         <f>IF(D73="","",D73-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B73,$A$2:$A73,"&gt;="&amp;(A73-6),$A$2:$A73,"&lt;="&amp;A73),"")</f>
         <v/>
       </c>
-      <c r="M73" s="19">
+      <c r="M73" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C73,$A$2:$A73,"&gt;="&amp;(A73-6),$A$2:$A73,"&lt;="&amp;A73),"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="20" t="n">
+      <c r="A74" s="32" t="n">
         <v>46321</v>
       </c>
-      <c r="B74" s="17" t="n"/>
+      <c r="B74" s="30" t="n"/>
       <c r="C74" s="18" t="n"/>
       <c r="D74" s="18" t="n"/>
       <c r="E74" s="18" t="n"/>
@@ -3957,28 +3968,28 @@
       <c r="G74" s="18" t="n"/>
       <c r="H74" s="18" t="n"/>
       <c r="I74" s="18" t="n"/>
-      <c r="J74" s="19">
+      <c r="J74" s="31">
         <f>IF(C74="","",C74-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K74" s="19">
+      <c r="K74" s="31">
         <f>IF(D74="","",D74-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L74" s="19">
+      <c r="L74" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B74,$A$2:$A74,"&gt;="&amp;(A74-6),$A$2:$A74,"&lt;="&amp;A74),"")</f>
         <v/>
       </c>
-      <c r="M74" s="19">
+      <c r="M74" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C74,$A$2:$A74,"&gt;="&amp;(A74-6),$A$2:$A74,"&lt;="&amp;A74),"")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="20" t="n">
+      <c r="A75" s="32" t="n">
         <v>46322</v>
       </c>
-      <c r="B75" s="17" t="n"/>
+      <c r="B75" s="30" t="n"/>
       <c r="C75" s="18" t="n"/>
       <c r="D75" s="18" t="n"/>
       <c r="E75" s="18" t="n"/>
@@ -3986,28 +3997,28 @@
       <c r="G75" s="18" t="n"/>
       <c r="H75" s="18" t="n"/>
       <c r="I75" s="18" t="n"/>
-      <c r="J75" s="19">
+      <c r="J75" s="31">
         <f>IF(C75="","",C75-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K75" s="19">
+      <c r="K75" s="31">
         <f>IF(D75="","",D75-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B75,$A$2:$A75,"&gt;="&amp;(A75-6),$A$2:$A75,"&lt;="&amp;A75),"")</f>
         <v/>
       </c>
-      <c r="M75" s="19">
+      <c r="M75" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C75,$A$2:$A75,"&gt;="&amp;(A75-6),$A$2:$A75,"&lt;="&amp;A75),"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="20" t="n">
+      <c r="A76" s="32" t="n">
         <v>46323</v>
       </c>
-      <c r="B76" s="17" t="n"/>
+      <c r="B76" s="30" t="n"/>
       <c r="C76" s="18" t="n"/>
       <c r="D76" s="18" t="n"/>
       <c r="E76" s="18" t="n"/>
@@ -4015,28 +4026,28 @@
       <c r="G76" s="18" t="n"/>
       <c r="H76" s="18" t="n"/>
       <c r="I76" s="18" t="n"/>
-      <c r="J76" s="19">
+      <c r="J76" s="31">
         <f>IF(C76="","",C76-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K76" s="19">
+      <c r="K76" s="31">
         <f>IF(D76="","",D76-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L76" s="19">
+      <c r="L76" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B76,$A$2:$A76,"&gt;="&amp;(A76-6),$A$2:$A76,"&lt;="&amp;A76),"")</f>
         <v/>
       </c>
-      <c r="M76" s="19">
+      <c r="M76" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C76,$A$2:$A76,"&gt;="&amp;(A76-6),$A$2:$A76,"&lt;="&amp;A76),"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="20" t="n">
+      <c r="A77" s="32" t="n">
         <v>46324</v>
       </c>
-      <c r="B77" s="17" t="n"/>
+      <c r="B77" s="30" t="n"/>
       <c r="C77" s="18" t="n"/>
       <c r="D77" s="18" t="n"/>
       <c r="E77" s="18" t="n"/>
@@ -4044,28 +4055,28 @@
       <c r="G77" s="18" t="n"/>
       <c r="H77" s="18" t="n"/>
       <c r="I77" s="18" t="n"/>
-      <c r="J77" s="19">
+      <c r="J77" s="31">
         <f>IF(C77="","",C77-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K77" s="19">
+      <c r="K77" s="31">
         <f>IF(D77="","",D77-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B77,$A$2:$A77,"&gt;="&amp;(A77-6),$A$2:$A77,"&lt;="&amp;A77),"")</f>
         <v/>
       </c>
-      <c r="M77" s="19">
+      <c r="M77" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C77,$A$2:$A77,"&gt;="&amp;(A77-6),$A$2:$A77,"&lt;="&amp;A77),"")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="20" t="n">
+      <c r="A78" s="32" t="n">
         <v>46325</v>
       </c>
-      <c r="B78" s="17" t="n"/>
+      <c r="B78" s="30" t="n"/>
       <c r="C78" s="18" t="n"/>
       <c r="D78" s="18" t="n"/>
       <c r="E78" s="18" t="n"/>
@@ -4073,28 +4084,28 @@
       <c r="G78" s="18" t="n"/>
       <c r="H78" s="18" t="n"/>
       <c r="I78" s="18" t="n"/>
-      <c r="J78" s="19">
+      <c r="J78" s="31">
         <f>IF(C78="","",C78-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K78" s="19">
+      <c r="K78" s="31">
         <f>IF(D78="","",D78-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B78,$A$2:$A78,"&gt;="&amp;(A78-6),$A$2:$A78,"&lt;="&amp;A78),"")</f>
         <v/>
       </c>
-      <c r="M78" s="19">
+      <c r="M78" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C78,$A$2:$A78,"&gt;="&amp;(A78-6),$A$2:$A78,"&lt;="&amp;A78),"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="n">
+      <c r="A79" s="32" t="n">
         <v>46326</v>
       </c>
-      <c r="B79" s="17" t="n"/>
+      <c r="B79" s="30" t="n"/>
       <c r="C79" s="18" t="n"/>
       <c r="D79" s="18" t="n"/>
       <c r="E79" s="18" t="n"/>
@@ -4102,28 +4113,28 @@
       <c r="G79" s="18" t="n"/>
       <c r="H79" s="18" t="n"/>
       <c r="I79" s="18" t="n"/>
-      <c r="J79" s="19">
+      <c r="J79" s="31">
         <f>IF(C79="","",C79-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K79" s="19">
+      <c r="K79" s="31">
         <f>IF(D79="","",D79-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L79" s="19">
+      <c r="L79" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B79,$A$2:$A79,"&gt;="&amp;(A79-6),$A$2:$A79,"&lt;="&amp;A79),"")</f>
         <v/>
       </c>
-      <c r="M79" s="19">
+      <c r="M79" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C79,$A$2:$A79,"&gt;="&amp;(A79-6),$A$2:$A79,"&lt;="&amp;A79),"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="20" t="n">
+      <c r="A80" s="32" t="n">
         <v>46327</v>
       </c>
-      <c r="B80" s="17" t="n"/>
+      <c r="B80" s="30" t="n"/>
       <c r="C80" s="18" t="n"/>
       <c r="D80" s="18" t="n"/>
       <c r="E80" s="18" t="n"/>
@@ -4131,28 +4142,28 @@
       <c r="G80" s="18" t="n"/>
       <c r="H80" s="18" t="n"/>
       <c r="I80" s="18" t="n"/>
-      <c r="J80" s="19">
+      <c r="J80" s="31">
         <f>IF(C80="","",C80-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K80" s="19">
+      <c r="K80" s="31">
         <f>IF(D80="","",D80-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L80" s="19">
+      <c r="L80" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B80,$A$2:$A80,"&gt;="&amp;(A80-6),$A$2:$A80,"&lt;="&amp;A80),"")</f>
         <v/>
       </c>
-      <c r="M80" s="19">
+      <c r="M80" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C80,$A$2:$A80,"&gt;="&amp;(A80-6),$A$2:$A80,"&lt;="&amp;A80),"")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="n">
+      <c r="A81" s="32" t="n">
         <v>46328</v>
       </c>
-      <c r="B81" s="17" t="n"/>
+      <c r="B81" s="30" t="n"/>
       <c r="C81" s="18" t="n"/>
       <c r="D81" s="18" t="n"/>
       <c r="E81" s="18" t="n"/>
@@ -4160,28 +4171,28 @@
       <c r="G81" s="18" t="n"/>
       <c r="H81" s="18" t="n"/>
       <c r="I81" s="18" t="n"/>
-      <c r="J81" s="19">
+      <c r="J81" s="31">
         <f>IF(C81="","",C81-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K81" s="19">
+      <c r="K81" s="31">
         <f>IF(D81="","",D81-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L81" s="19">
+      <c r="L81" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B81,$A$2:$A81,"&gt;="&amp;(A81-6),$A$2:$A81,"&lt;="&amp;A81),"")</f>
         <v/>
       </c>
-      <c r="M81" s="19">
+      <c r="M81" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C81,$A$2:$A81,"&gt;="&amp;(A81-6),$A$2:$A81,"&lt;="&amp;A81),"")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="n">
+      <c r="A82" s="32" t="n">
         <v>46329</v>
       </c>
-      <c r="B82" s="17" t="n"/>
+      <c r="B82" s="30" t="n"/>
       <c r="C82" s="18" t="n"/>
       <c r="D82" s="18" t="n"/>
       <c r="E82" s="18" t="n"/>
@@ -4189,28 +4200,28 @@
       <c r="G82" s="18" t="n"/>
       <c r="H82" s="18" t="n"/>
       <c r="I82" s="18" t="n"/>
-      <c r="J82" s="19">
+      <c r="J82" s="31">
         <f>IF(C82="","",C82-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K82" s="19">
+      <c r="K82" s="31">
         <f>IF(D82="","",D82-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L82" s="19">
+      <c r="L82" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B82,$A$2:$A82,"&gt;="&amp;(A82-6),$A$2:$A82,"&lt;="&amp;A82),"")</f>
         <v/>
       </c>
-      <c r="M82" s="19">
+      <c r="M82" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C82,$A$2:$A82,"&gt;="&amp;(A82-6),$A$2:$A82,"&lt;="&amp;A82),"")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="20" t="n">
+      <c r="A83" s="32" t="n">
         <v>46330</v>
       </c>
-      <c r="B83" s="17" t="n"/>
+      <c r="B83" s="30" t="n"/>
       <c r="C83" s="18" t="n"/>
       <c r="D83" s="18" t="n"/>
       <c r="E83" s="18" t="n"/>
@@ -4218,28 +4229,28 @@
       <c r="G83" s="18" t="n"/>
       <c r="H83" s="18" t="n"/>
       <c r="I83" s="18" t="n"/>
-      <c r="J83" s="19">
+      <c r="J83" s="31">
         <f>IF(C83="","",C83-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K83" s="19">
+      <c r="K83" s="31">
         <f>IF(D83="","",D83-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L83" s="19">
+      <c r="L83" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B83,$A$2:$A83,"&gt;="&amp;(A83-6),$A$2:$A83,"&lt;="&amp;A83),"")</f>
         <v/>
       </c>
-      <c r="M83" s="19">
+      <c r="M83" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C83,$A$2:$A83,"&gt;="&amp;(A83-6),$A$2:$A83,"&lt;="&amp;A83),"")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="n">
+      <c r="A84" s="32" t="n">
         <v>46331</v>
       </c>
-      <c r="B84" s="17" t="n"/>
+      <c r="B84" s="30" t="n"/>
       <c r="C84" s="18" t="n"/>
       <c r="D84" s="18" t="n"/>
       <c r="E84" s="18" t="n"/>
@@ -4247,28 +4258,28 @@
       <c r="G84" s="18" t="n"/>
       <c r="H84" s="18" t="n"/>
       <c r="I84" s="18" t="n"/>
-      <c r="J84" s="19">
+      <c r="J84" s="31">
         <f>IF(C84="","",C84-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K84" s="19">
+      <c r="K84" s="31">
         <f>IF(D84="","",D84-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L84" s="19">
+      <c r="L84" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B84,$A$2:$A84,"&gt;="&amp;(A84-6),$A$2:$A84,"&lt;="&amp;A84),"")</f>
         <v/>
       </c>
-      <c r="M84" s="19">
+      <c r="M84" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C84,$A$2:$A84,"&gt;="&amp;(A84-6),$A$2:$A84,"&lt;="&amp;A84),"")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="n">
+      <c r="A85" s="32" t="n">
         <v>46332</v>
       </c>
-      <c r="B85" s="17" t="n"/>
+      <c r="B85" s="30" t="n"/>
       <c r="C85" s="18" t="n"/>
       <c r="D85" s="18" t="n"/>
       <c r="E85" s="18" t="n"/>
@@ -4276,28 +4287,28 @@
       <c r="G85" s="18" t="n"/>
       <c r="H85" s="18" t="n"/>
       <c r="I85" s="18" t="n"/>
-      <c r="J85" s="19">
+      <c r="J85" s="31">
         <f>IF(C85="","",C85-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K85" s="19">
+      <c r="K85" s="31">
         <f>IF(D85="","",D85-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B85,$A$2:$A85,"&gt;="&amp;(A85-6),$A$2:$A85,"&lt;="&amp;A85),"")</f>
         <v/>
       </c>
-      <c r="M85" s="19">
+      <c r="M85" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C85,$A$2:$A85,"&gt;="&amp;(A85-6),$A$2:$A85,"&lt;="&amp;A85),"")</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="n">
+      <c r="A86" s="32" t="n">
         <v>46333</v>
       </c>
-      <c r="B86" s="17" t="n"/>
+      <c r="B86" s="30" t="n"/>
       <c r="C86" s="18" t="n"/>
       <c r="D86" s="18" t="n"/>
       <c r="E86" s="18" t="n"/>
@@ -4305,28 +4316,28 @@
       <c r="G86" s="18" t="n"/>
       <c r="H86" s="18" t="n"/>
       <c r="I86" s="18" t="n"/>
-      <c r="J86" s="19">
+      <c r="J86" s="31">
         <f>IF(C86="","",C86-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K86" s="19">
+      <c r="K86" s="31">
         <f>IF(D86="","",D86-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B86,$A$2:$A86,"&gt;="&amp;(A86-6),$A$2:$A86,"&lt;="&amp;A86),"")</f>
         <v/>
       </c>
-      <c r="M86" s="19">
+      <c r="M86" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C86,$A$2:$A86,"&gt;="&amp;(A86-6),$A$2:$A86,"&lt;="&amp;A86),"")</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="20" t="n">
+      <c r="A87" s="32" t="n">
         <v>46334</v>
       </c>
-      <c r="B87" s="17" t="n"/>
+      <c r="B87" s="30" t="n"/>
       <c r="C87" s="18" t="n"/>
       <c r="D87" s="18" t="n"/>
       <c r="E87" s="18" t="n"/>
@@ -4334,28 +4345,28 @@
       <c r="G87" s="18" t="n"/>
       <c r="H87" s="18" t="n"/>
       <c r="I87" s="18" t="n"/>
-      <c r="J87" s="19">
+      <c r="J87" s="31">
         <f>IF(C87="","",C87-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K87" s="19">
+      <c r="K87" s="31">
         <f>IF(D87="","",D87-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B87,$A$2:$A87,"&gt;="&amp;(A87-6),$A$2:$A87,"&lt;="&amp;A87),"")</f>
         <v/>
       </c>
-      <c r="M87" s="19">
+      <c r="M87" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C87,$A$2:$A87,"&gt;="&amp;(A87-6),$A$2:$A87,"&lt;="&amp;A87),"")</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="20" t="n">
+      <c r="A88" s="32" t="n">
         <v>46335</v>
       </c>
-      <c r="B88" s="17" t="n"/>
+      <c r="B88" s="30" t="n"/>
       <c r="C88" s="18" t="n"/>
       <c r="D88" s="18" t="n"/>
       <c r="E88" s="18" t="n"/>
@@ -4363,28 +4374,28 @@
       <c r="G88" s="18" t="n"/>
       <c r="H88" s="18" t="n"/>
       <c r="I88" s="18" t="n"/>
-      <c r="J88" s="19">
+      <c r="J88" s="31">
         <f>IF(C88="","",C88-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K88" s="19">
+      <c r="K88" s="31">
         <f>IF(D88="","",D88-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L88" s="19">
+      <c r="L88" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B88,$A$2:$A88,"&gt;="&amp;(A88-6),$A$2:$A88,"&lt;="&amp;A88),"")</f>
         <v/>
       </c>
-      <c r="M88" s="19">
+      <c r="M88" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C88,$A$2:$A88,"&gt;="&amp;(A88-6),$A$2:$A88,"&lt;="&amp;A88),"")</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="20" t="n">
+      <c r="A89" s="32" t="n">
         <v>46336</v>
       </c>
-      <c r="B89" s="17" t="n"/>
+      <c r="B89" s="30" t="n"/>
       <c r="C89" s="18" t="n"/>
       <c r="D89" s="18" t="n"/>
       <c r="E89" s="18" t="n"/>
@@ -4392,28 +4403,28 @@
       <c r="G89" s="18" t="n"/>
       <c r="H89" s="18" t="n"/>
       <c r="I89" s="18" t="n"/>
-      <c r="J89" s="19">
+      <c r="J89" s="31">
         <f>IF(C89="","",C89-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K89" s="19">
+      <c r="K89" s="31">
         <f>IF(D89="","",D89-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L89" s="19">
+      <c r="L89" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B89,$A$2:$A89,"&gt;="&amp;(A89-6),$A$2:$A89,"&lt;="&amp;A89),"")</f>
         <v/>
       </c>
-      <c r="M89" s="19">
+      <c r="M89" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C89,$A$2:$A89,"&gt;="&amp;(A89-6),$A$2:$A89,"&lt;="&amp;A89),"")</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="20" t="n">
+      <c r="A90" s="32" t="n">
         <v>46337</v>
       </c>
-      <c r="B90" s="17" t="n"/>
+      <c r="B90" s="30" t="n"/>
       <c r="C90" s="18" t="n"/>
       <c r="D90" s="18" t="n"/>
       <c r="E90" s="18" t="n"/>
@@ -4421,28 +4432,28 @@
       <c r="G90" s="18" t="n"/>
       <c r="H90" s="18" t="n"/>
       <c r="I90" s="18" t="n"/>
-      <c r="J90" s="19">
+      <c r="J90" s="31">
         <f>IF(C90="","",C90-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K90" s="19">
+      <c r="K90" s="31">
         <f>IF(D90="","",D90-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L90" s="19">
+      <c r="L90" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B90,$A$2:$A90,"&gt;="&amp;(A90-6),$A$2:$A90,"&lt;="&amp;A90),"")</f>
         <v/>
       </c>
-      <c r="M90" s="19">
+      <c r="M90" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C90,$A$2:$A90,"&gt;="&amp;(A90-6),$A$2:$A90,"&lt;="&amp;A90),"")</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="20" t="n">
+      <c r="A91" s="32" t="n">
         <v>46338</v>
       </c>
-      <c r="B91" s="17" t="n"/>
+      <c r="B91" s="30" t="n"/>
       <c r="C91" s="18" t="n"/>
       <c r="D91" s="18" t="n"/>
       <c r="E91" s="18" t="n"/>
@@ -4450,28 +4461,28 @@
       <c r="G91" s="18" t="n"/>
       <c r="H91" s="18" t="n"/>
       <c r="I91" s="18" t="n"/>
-      <c r="J91" s="19">
+      <c r="J91" s="31">
         <f>IF(C91="","",C91-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K91" s="19">
+      <c r="K91" s="31">
         <f>IF(D91="","",D91-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L91" s="19">
+      <c r="L91" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B91,$A$2:$A91,"&gt;="&amp;(A91-6),$A$2:$A91,"&lt;="&amp;A91),"")</f>
         <v/>
       </c>
-      <c r="M91" s="19">
+      <c r="M91" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C91,$A$2:$A91,"&gt;="&amp;(A91-6),$A$2:$A91,"&lt;="&amp;A91),"")</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="20" t="n">
+      <c r="A92" s="32" t="n">
         <v>46339</v>
       </c>
-      <c r="B92" s="17" t="n"/>
+      <c r="B92" s="30" t="n"/>
       <c r="C92" s="18" t="n"/>
       <c r="D92" s="18" t="n"/>
       <c r="E92" s="18" t="n"/>
@@ -4479,28 +4490,28 @@
       <c r="G92" s="18" t="n"/>
       <c r="H92" s="18" t="n"/>
       <c r="I92" s="18" t="n"/>
-      <c r="J92" s="19">
+      <c r="J92" s="31">
         <f>IF(C92="","",C92-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K92" s="19">
+      <c r="K92" s="31">
         <f>IF(D92="","",D92-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B92,$A$2:$A92,"&gt;="&amp;(A92-6),$A$2:$A92,"&lt;="&amp;A92),"")</f>
         <v/>
       </c>
-      <c r="M92" s="19">
+      <c r="M92" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C92,$A$2:$A92,"&gt;="&amp;(A92-6),$A$2:$A92,"&lt;="&amp;A92),"")</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="20" t="n">
+      <c r="A93" s="32" t="n">
         <v>46340</v>
       </c>
-      <c r="B93" s="17" t="n"/>
+      <c r="B93" s="30" t="n"/>
       <c r="C93" s="18" t="n"/>
       <c r="D93" s="18" t="n"/>
       <c r="E93" s="18" t="n"/>
@@ -4508,28 +4519,28 @@
       <c r="G93" s="18" t="n"/>
       <c r="H93" s="18" t="n"/>
       <c r="I93" s="18" t="n"/>
-      <c r="J93" s="19">
+      <c r="J93" s="31">
         <f>IF(C93="","",C93-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K93" s="19">
+      <c r="K93" s="31">
         <f>IF(D93="","",D93-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B93,$A$2:$A93,"&gt;="&amp;(A93-6),$A$2:$A93,"&lt;="&amp;A93),"")</f>
         <v/>
       </c>
-      <c r="M93" s="19">
+      <c r="M93" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C93,$A$2:$A93,"&gt;="&amp;(A93-6),$A$2:$A93,"&lt;="&amp;A93),"")</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="20" t="n">
+      <c r="A94" s="32" t="n">
         <v>46341</v>
       </c>
-      <c r="B94" s="17" t="n"/>
+      <c r="B94" s="30" t="n"/>
       <c r="C94" s="18" t="n"/>
       <c r="D94" s="18" t="n"/>
       <c r="E94" s="18" t="n"/>
@@ -4537,28 +4548,28 @@
       <c r="G94" s="18" t="n"/>
       <c r="H94" s="18" t="n"/>
       <c r="I94" s="18" t="n"/>
-      <c r="J94" s="19">
+      <c r="J94" s="31">
         <f>IF(C94="","",C94-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K94" s="19">
+      <c r="K94" s="31">
         <f>IF(D94="","",D94-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L94" s="19">
+      <c r="L94" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B94,$A$2:$A94,"&gt;="&amp;(A94-6),$A$2:$A94,"&lt;="&amp;A94),"")</f>
         <v/>
       </c>
-      <c r="M94" s="19">
+      <c r="M94" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C94,$A$2:$A94,"&gt;="&amp;(A94-6),$A$2:$A94,"&lt;="&amp;A94),"")</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="20" t="n">
+      <c r="A95" s="32" t="n">
         <v>46342</v>
       </c>
-      <c r="B95" s="17" t="n"/>
+      <c r="B95" s="30" t="n"/>
       <c r="C95" s="18" t="n"/>
       <c r="D95" s="18" t="n"/>
       <c r="E95" s="18" t="n"/>
@@ -4566,28 +4577,28 @@
       <c r="G95" s="18" t="n"/>
       <c r="H95" s="18" t="n"/>
       <c r="I95" s="18" t="n"/>
-      <c r="J95" s="19">
+      <c r="J95" s="31">
         <f>IF(C95="","",C95-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K95" s="19">
+      <c r="K95" s="31">
         <f>IF(D95="","",D95-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L95" s="19">
+      <c r="L95" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B95,$A$2:$A95,"&gt;="&amp;(A95-6),$A$2:$A95,"&lt;="&amp;A95),"")</f>
         <v/>
       </c>
-      <c r="M95" s="19">
+      <c r="M95" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C95,$A$2:$A95,"&gt;="&amp;(A95-6),$A$2:$A95,"&lt;="&amp;A95),"")</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="20" t="n">
+      <c r="A96" s="32" t="n">
         <v>46343</v>
       </c>
-      <c r="B96" s="17" t="n"/>
+      <c r="B96" s="30" t="n"/>
       <c r="C96" s="18" t="n"/>
       <c r="D96" s="18" t="n"/>
       <c r="E96" s="18" t="n"/>
@@ -4595,28 +4606,28 @@
       <c r="G96" s="18" t="n"/>
       <c r="H96" s="18" t="n"/>
       <c r="I96" s="18" t="n"/>
-      <c r="J96" s="19">
+      <c r="J96" s="31">
         <f>IF(C96="","",C96-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K96" s="19">
+      <c r="K96" s="31">
         <f>IF(D96="","",D96-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L96" s="19">
+      <c r="L96" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B96,$A$2:$A96,"&gt;="&amp;(A96-6),$A$2:$A96,"&lt;="&amp;A96),"")</f>
         <v/>
       </c>
-      <c r="M96" s="19">
+      <c r="M96" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C96,$A$2:$A96,"&gt;="&amp;(A96-6),$A$2:$A96,"&lt;="&amp;A96),"")</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="n">
+      <c r="A97" s="32" t="n">
         <v>46344</v>
       </c>
-      <c r="B97" s="17" t="n"/>
+      <c r="B97" s="30" t="n"/>
       <c r="C97" s="18" t="n"/>
       <c r="D97" s="18" t="n"/>
       <c r="E97" s="18" t="n"/>
@@ -4624,28 +4635,28 @@
       <c r="G97" s="18" t="n"/>
       <c r="H97" s="18" t="n"/>
       <c r="I97" s="18" t="n"/>
-      <c r="J97" s="19">
+      <c r="J97" s="31">
         <f>IF(C97="","",C97-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K97" s="19">
+      <c r="K97" s="31">
         <f>IF(D97="","",D97-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L97" s="19">
+      <c r="L97" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B97,$A$2:$A97,"&gt;="&amp;(A97-6),$A$2:$A97,"&lt;="&amp;A97),"")</f>
         <v/>
       </c>
-      <c r="M97" s="19">
+      <c r="M97" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C97,$A$2:$A97,"&gt;="&amp;(A97-6),$A$2:$A97,"&lt;="&amp;A97),"")</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="n">
+      <c r="A98" s="32" t="n">
         <v>46345</v>
       </c>
-      <c r="B98" s="17" t="n"/>
+      <c r="B98" s="30" t="n"/>
       <c r="C98" s="18" t="n"/>
       <c r="D98" s="18" t="n"/>
       <c r="E98" s="18" t="n"/>
@@ -4653,28 +4664,28 @@
       <c r="G98" s="18" t="n"/>
       <c r="H98" s="18" t="n"/>
       <c r="I98" s="18" t="n"/>
-      <c r="J98" s="19">
+      <c r="J98" s="31">
         <f>IF(C98="","",C98-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K98" s="19">
+      <c r="K98" s="31">
         <f>IF(D98="","",D98-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B98,$A$2:$A98,"&gt;="&amp;(A98-6),$A$2:$A98,"&lt;="&amp;A98),"")</f>
         <v/>
       </c>
-      <c r="M98" s="19">
+      <c r="M98" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C98,$A$2:$A98,"&gt;="&amp;(A98-6),$A$2:$A98,"&lt;="&amp;A98),"")</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="n">
+      <c r="A99" s="32" t="n">
         <v>46346</v>
       </c>
-      <c r="B99" s="17" t="n"/>
+      <c r="B99" s="30" t="n"/>
       <c r="C99" s="18" t="n"/>
       <c r="D99" s="18" t="n"/>
       <c r="E99" s="18" t="n"/>
@@ -4682,28 +4693,28 @@
       <c r="G99" s="18" t="n"/>
       <c r="H99" s="18" t="n"/>
       <c r="I99" s="18" t="n"/>
-      <c r="J99" s="19">
+      <c r="J99" s="31">
         <f>IF(C99="","",C99-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K99" s="19">
+      <c r="K99" s="31">
         <f>IF(D99="","",D99-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L99" s="19">
+      <c r="L99" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B99,$A$2:$A99,"&gt;="&amp;(A99-6),$A$2:$A99,"&lt;="&amp;A99),"")</f>
         <v/>
       </c>
-      <c r="M99" s="19">
+      <c r="M99" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C99,$A$2:$A99,"&gt;="&amp;(A99-6),$A$2:$A99,"&lt;="&amp;A99),"")</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="20" t="n">
+      <c r="A100" s="32" t="n">
         <v>46347</v>
       </c>
-      <c r="B100" s="17" t="n"/>
+      <c r="B100" s="30" t="n"/>
       <c r="C100" s="18" t="n"/>
       <c r="D100" s="18" t="n"/>
       <c r="E100" s="18" t="n"/>
@@ -4711,28 +4722,28 @@
       <c r="G100" s="18" t="n"/>
       <c r="H100" s="18" t="n"/>
       <c r="I100" s="18" t="n"/>
-      <c r="J100" s="19">
+      <c r="J100" s="31">
         <f>IF(C100="","",C100-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K100" s="19">
+      <c r="K100" s="31">
         <f>IF(D100="","",D100-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L100" s="19">
+      <c r="L100" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B100,$A$2:$A100,"&gt;="&amp;(A100-6),$A$2:$A100,"&lt;="&amp;A100),"")</f>
         <v/>
       </c>
-      <c r="M100" s="19">
+      <c r="M100" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C100,$A$2:$A100,"&gt;="&amp;(A100-6),$A$2:$A100,"&lt;="&amp;A100),"")</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="20" t="n">
+      <c r="A101" s="32" t="n">
         <v>46348</v>
       </c>
-      <c r="B101" s="17" t="n"/>
+      <c r="B101" s="30" t="n"/>
       <c r="C101" s="18" t="n"/>
       <c r="D101" s="18" t="n"/>
       <c r="E101" s="18" t="n"/>
@@ -4740,28 +4751,28 @@
       <c r="G101" s="18" t="n"/>
       <c r="H101" s="18" t="n"/>
       <c r="I101" s="18" t="n"/>
-      <c r="J101" s="19">
+      <c r="J101" s="31">
         <f>IF(C101="","",C101-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K101" s="19">
+      <c r="K101" s="31">
         <f>IF(D101="","",D101-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B101,$A$2:$A101,"&gt;="&amp;(A101-6),$A$2:$A101,"&lt;="&amp;A101),"")</f>
         <v/>
       </c>
-      <c r="M101" s="19">
+      <c r="M101" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C101,$A$2:$A101,"&gt;="&amp;(A101-6),$A$2:$A101,"&lt;="&amp;A101),"")</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="n">
+      <c r="A102" s="32" t="n">
         <v>46349</v>
       </c>
-      <c r="B102" s="17" t="n"/>
+      <c r="B102" s="30" t="n"/>
       <c r="C102" s="18" t="n"/>
       <c r="D102" s="18" t="n"/>
       <c r="E102" s="18" t="n"/>
@@ -4769,28 +4780,28 @@
       <c r="G102" s="18" t="n"/>
       <c r="H102" s="18" t="n"/>
       <c r="I102" s="18" t="n"/>
-      <c r="J102" s="19">
+      <c r="J102" s="31">
         <f>IF(C102="","",C102-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K102" s="19">
+      <c r="K102" s="31">
         <f>IF(D102="","",D102-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L102" s="19">
+      <c r="L102" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B102,$A$2:$A102,"&gt;="&amp;(A102-6),$A$2:$A102,"&lt;="&amp;A102),"")</f>
         <v/>
       </c>
-      <c r="M102" s="19">
+      <c r="M102" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C102,$A$2:$A102,"&gt;="&amp;(A102-6),$A$2:$A102,"&lt;="&amp;A102),"")</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="20" t="n">
+      <c r="A103" s="32" t="n">
         <v>46350</v>
       </c>
-      <c r="B103" s="17" t="n"/>
+      <c r="B103" s="30" t="n"/>
       <c r="C103" s="18" t="n"/>
       <c r="D103" s="18" t="n"/>
       <c r="E103" s="18" t="n"/>
@@ -4798,28 +4809,28 @@
       <c r="G103" s="18" t="n"/>
       <c r="H103" s="18" t="n"/>
       <c r="I103" s="18" t="n"/>
-      <c r="J103" s="19">
+      <c r="J103" s="31">
         <f>IF(C103="","",C103-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K103" s="19">
+      <c r="K103" s="31">
         <f>IF(D103="","",D103-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L103" s="19">
+      <c r="L103" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B103,$A$2:$A103,"&gt;="&amp;(A103-6),$A$2:$A103,"&lt;="&amp;A103),"")</f>
         <v/>
       </c>
-      <c r="M103" s="19">
+      <c r="M103" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C103,$A$2:$A103,"&gt;="&amp;(A103-6),$A$2:$A103,"&lt;="&amp;A103),"")</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="n">
+      <c r="A104" s="32" t="n">
         <v>46351</v>
       </c>
-      <c r="B104" s="17" t="n"/>
+      <c r="B104" s="30" t="n"/>
       <c r="C104" s="18" t="n"/>
       <c r="D104" s="18" t="n"/>
       <c r="E104" s="18" t="n"/>
@@ -4827,28 +4838,28 @@
       <c r="G104" s="18" t="n"/>
       <c r="H104" s="18" t="n"/>
       <c r="I104" s="18" t="n"/>
-      <c r="J104" s="19">
+      <c r="J104" s="31">
         <f>IF(C104="","",C104-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K104" s="19">
+      <c r="K104" s="31">
         <f>IF(D104="","",D104-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L104" s="19">
+      <c r="L104" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B104,$A$2:$A104,"&gt;="&amp;(A104-6),$A$2:$A104,"&lt;="&amp;A104),"")</f>
         <v/>
       </c>
-      <c r="M104" s="19">
+      <c r="M104" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C104,$A$2:$A104,"&gt;="&amp;(A104-6),$A$2:$A104,"&lt;="&amp;A104),"")</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="20" t="n">
+      <c r="A105" s="32" t="n">
         <v>46352</v>
       </c>
-      <c r="B105" s="17" t="n"/>
+      <c r="B105" s="30" t="n"/>
       <c r="C105" s="18" t="n"/>
       <c r="D105" s="18" t="n"/>
       <c r="E105" s="18" t="n"/>
@@ -4856,28 +4867,28 @@
       <c r="G105" s="18" t="n"/>
       <c r="H105" s="18" t="n"/>
       <c r="I105" s="18" t="n"/>
-      <c r="J105" s="19">
+      <c r="J105" s="31">
         <f>IF(C105="","",C105-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K105" s="19">
+      <c r="K105" s="31">
         <f>IF(D105="","",D105-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L105" s="19">
+      <c r="L105" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B105,$A$2:$A105,"&gt;="&amp;(A105-6),$A$2:$A105,"&lt;="&amp;A105),"")</f>
         <v/>
       </c>
-      <c r="M105" s="19">
+      <c r="M105" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C105,$A$2:$A105,"&gt;="&amp;(A105-6),$A$2:$A105,"&lt;="&amp;A105),"")</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="20" t="n">
+      <c r="A106" s="32" t="n">
         <v>46353</v>
       </c>
-      <c r="B106" s="17" t="n"/>
+      <c r="B106" s="30" t="n"/>
       <c r="C106" s="18" t="n"/>
       <c r="D106" s="18" t="n"/>
       <c r="E106" s="18" t="n"/>
@@ -4885,28 +4896,28 @@
       <c r="G106" s="18" t="n"/>
       <c r="H106" s="18" t="n"/>
       <c r="I106" s="18" t="n"/>
-      <c r="J106" s="19">
+      <c r="J106" s="31">
         <f>IF(C106="","",C106-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K106" s="19">
+      <c r="K106" s="31">
         <f>IF(D106="","",D106-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L106" s="19">
+      <c r="L106" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B106,$A$2:$A106,"&gt;="&amp;(A106-6),$A$2:$A106,"&lt;="&amp;A106),"")</f>
         <v/>
       </c>
-      <c r="M106" s="19">
+      <c r="M106" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C106,$A$2:$A106,"&gt;="&amp;(A106-6),$A$2:$A106,"&lt;="&amp;A106),"")</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="20" t="n">
+      <c r="A107" s="32" t="n">
         <v>46354</v>
       </c>
-      <c r="B107" s="17" t="n"/>
+      <c r="B107" s="30" t="n"/>
       <c r="C107" s="18" t="n"/>
       <c r="D107" s="18" t="n"/>
       <c r="E107" s="18" t="n"/>
@@ -4914,28 +4925,28 @@
       <c r="G107" s="18" t="n"/>
       <c r="H107" s="18" t="n"/>
       <c r="I107" s="18" t="n"/>
-      <c r="J107" s="19">
+      <c r="J107" s="31">
         <f>IF(C107="","",C107-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K107" s="19">
+      <c r="K107" s="31">
         <f>IF(D107="","",D107-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L107" s="19">
+      <c r="L107" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B107,$A$2:$A107,"&gt;="&amp;(A107-6),$A$2:$A107,"&lt;="&amp;A107),"")</f>
         <v/>
       </c>
-      <c r="M107" s="19">
+      <c r="M107" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C107,$A$2:$A107,"&gt;="&amp;(A107-6),$A$2:$A107,"&lt;="&amp;A107),"")</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="20" t="n">
+      <c r="A108" s="32" t="n">
         <v>46355</v>
       </c>
-      <c r="B108" s="17" t="n"/>
+      <c r="B108" s="30" t="n"/>
       <c r="C108" s="18" t="n"/>
       <c r="D108" s="18" t="n"/>
       <c r="E108" s="18" t="n"/>
@@ -4943,28 +4954,28 @@
       <c r="G108" s="18" t="n"/>
       <c r="H108" s="18" t="n"/>
       <c r="I108" s="18" t="n"/>
-      <c r="J108" s="19">
+      <c r="J108" s="31">
         <f>IF(C108="","",C108-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K108" s="19">
+      <c r="K108" s="31">
         <f>IF(D108="","",D108-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L108" s="19">
+      <c r="L108" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B108,$A$2:$A108,"&gt;="&amp;(A108-6),$A$2:$A108,"&lt;="&amp;A108),"")</f>
         <v/>
       </c>
-      <c r="M108" s="19">
+      <c r="M108" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C108,$A$2:$A108,"&gt;="&amp;(A108-6),$A$2:$A108,"&lt;="&amp;A108),"")</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="20" t="n">
+      <c r="A109" s="32" t="n">
         <v>46356</v>
       </c>
-      <c r="B109" s="17" t="n"/>
+      <c r="B109" s="30" t="n"/>
       <c r="C109" s="18" t="n"/>
       <c r="D109" s="18" t="n"/>
       <c r="E109" s="18" t="n"/>
@@ -4972,28 +4983,28 @@
       <c r="G109" s="18" t="n"/>
       <c r="H109" s="18" t="n"/>
       <c r="I109" s="18" t="n"/>
-      <c r="J109" s="19">
+      <c r="J109" s="31">
         <f>IF(C109="","",C109-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K109" s="19">
+      <c r="K109" s="31">
         <f>IF(D109="","",D109-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L109" s="19">
+      <c r="L109" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B109,$A$2:$A109,"&gt;="&amp;(A109-6),$A$2:$A109,"&lt;="&amp;A109),"")</f>
         <v/>
       </c>
-      <c r="M109" s="19">
+      <c r="M109" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C109,$A$2:$A109,"&gt;="&amp;(A109-6),$A$2:$A109,"&lt;="&amp;A109),"")</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="20" t="n">
+      <c r="A110" s="32" t="n">
         <v>46357</v>
       </c>
-      <c r="B110" s="17" t="n"/>
+      <c r="B110" s="30" t="n"/>
       <c r="C110" s="18" t="n"/>
       <c r="D110" s="18" t="n"/>
       <c r="E110" s="18" t="n"/>
@@ -5001,28 +5012,28 @@
       <c r="G110" s="18" t="n"/>
       <c r="H110" s="18" t="n"/>
       <c r="I110" s="18" t="n"/>
-      <c r="J110" s="19">
+      <c r="J110" s="31">
         <f>IF(C110="","",C110-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K110" s="19">
+      <c r="K110" s="31">
         <f>IF(D110="","",D110-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L110" s="19">
+      <c r="L110" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B110,$A$2:$A110,"&gt;="&amp;(A110-6),$A$2:$A110,"&lt;="&amp;A110),"")</f>
         <v/>
       </c>
-      <c r="M110" s="19">
+      <c r="M110" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C110,$A$2:$A110,"&gt;="&amp;(A110-6),$A$2:$A110,"&lt;="&amp;A110),"")</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="n">
+      <c r="A111" s="32" t="n">
         <v>46358</v>
       </c>
-      <c r="B111" s="17" t="n"/>
+      <c r="B111" s="30" t="n"/>
       <c r="C111" s="18" t="n"/>
       <c r="D111" s="18" t="n"/>
       <c r="E111" s="18" t="n"/>
@@ -5030,28 +5041,28 @@
       <c r="G111" s="18" t="n"/>
       <c r="H111" s="18" t="n"/>
       <c r="I111" s="18" t="n"/>
-      <c r="J111" s="19">
+      <c r="J111" s="31">
         <f>IF(C111="","",C111-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K111" s="19">
+      <c r="K111" s="31">
         <f>IF(D111="","",D111-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L111" s="19">
+      <c r="L111" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B111,$A$2:$A111,"&gt;="&amp;(A111-6),$A$2:$A111,"&lt;="&amp;A111),"")</f>
         <v/>
       </c>
-      <c r="M111" s="19">
+      <c r="M111" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C111,$A$2:$A111,"&gt;="&amp;(A111-6),$A$2:$A111,"&lt;="&amp;A111),"")</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="20" t="n">
+      <c r="A112" s="32" t="n">
         <v>46359</v>
       </c>
-      <c r="B112" s="17" t="n"/>
+      <c r="B112" s="30" t="n"/>
       <c r="C112" s="18" t="n"/>
       <c r="D112" s="18" t="n"/>
       <c r="E112" s="18" t="n"/>
@@ -5059,28 +5070,28 @@
       <c r="G112" s="18" t="n"/>
       <c r="H112" s="18" t="n"/>
       <c r="I112" s="18" t="n"/>
-      <c r="J112" s="19">
+      <c r="J112" s="31">
         <f>IF(C112="","",C112-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K112" s="19">
+      <c r="K112" s="31">
         <f>IF(D112="","",D112-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L112" s="19">
+      <c r="L112" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B112,$A$2:$A112,"&gt;="&amp;(A112-6),$A$2:$A112,"&lt;="&amp;A112),"")</f>
         <v/>
       </c>
-      <c r="M112" s="19">
+      <c r="M112" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C112,$A$2:$A112,"&gt;="&amp;(A112-6),$A$2:$A112,"&lt;="&amp;A112),"")</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="20" t="n">
+      <c r="A113" s="32" t="n">
         <v>46360</v>
       </c>
-      <c r="B113" s="17" t="n"/>
+      <c r="B113" s="30" t="n"/>
       <c r="C113" s="18" t="n"/>
       <c r="D113" s="18" t="n"/>
       <c r="E113" s="18" t="n"/>
@@ -5088,28 +5099,28 @@
       <c r="G113" s="18" t="n"/>
       <c r="H113" s="18" t="n"/>
       <c r="I113" s="18" t="n"/>
-      <c r="J113" s="19">
+      <c r="J113" s="31">
         <f>IF(C113="","",C113-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K113" s="19">
+      <c r="K113" s="31">
         <f>IF(D113="","",D113-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L113" s="19">
+      <c r="L113" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B113,$A$2:$A113,"&gt;="&amp;(A113-6),$A$2:$A113,"&lt;="&amp;A113),"")</f>
         <v/>
       </c>
-      <c r="M113" s="19">
+      <c r="M113" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C113,$A$2:$A113,"&gt;="&amp;(A113-6),$A$2:$A113,"&lt;="&amp;A113),"")</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="20" t="n">
+      <c r="A114" s="32" t="n">
         <v>46361</v>
       </c>
-      <c r="B114" s="17" t="n"/>
+      <c r="B114" s="30" t="n"/>
       <c r="C114" s="18" t="n"/>
       <c r="D114" s="18" t="n"/>
       <c r="E114" s="18" t="n"/>
@@ -5117,19 +5128,19 @@
       <c r="G114" s="18" t="n"/>
       <c r="H114" s="18" t="n"/>
       <c r="I114" s="18" t="n"/>
-      <c r="J114" s="19">
+      <c r="J114" s="31">
         <f>IF(C114="","",C114-Targets!$B$12)</f>
         <v/>
       </c>
-      <c r="K114" s="19">
+      <c r="K114" s="31">
         <f>IF(D114="","",D114-Targets!$B$13)</f>
         <v/>
       </c>
-      <c r="L114" s="19">
+      <c r="L114" s="31">
         <f>IFERROR(AVERAGEIFS($B$2:$B114,$A$2:$A114,"&gt;="&amp;(A114-6),$A$2:$A114,"&lt;="&amp;A114),"")</f>
         <v/>
       </c>
-      <c r="M114" s="19">
+      <c r="M114" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C114,$A$2:$A114,"&gt;="&amp;(A114-6),$A$2:$A114,"&lt;="&amp;A114),"")</f>
         <v/>
       </c>
@@ -5207,24 +5218,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="32" t="n">
         <v>46250</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A2+7)),"")</f>
         <v/>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="22">
+      <c r="D2" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A2+7)),"")</f>
         <v/>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A2+7)),"")</f>
         <v/>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" s="14">
+      <c r="G2" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5238,22 +5247,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n">
+      <c r="A3" s="32" t="n">
         <v>46257</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A3+7)),"")</f>
         <v/>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="33">
         <f>IF(OR(B3="",B2=""),"",B3-B2)</f>
         <v/>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A3+7)),"")</f>
         <v/>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A3+7)),"")</f>
         <v/>
       </c>
@@ -5261,7 +5270,7 @@
         <f>IF(C3="","",IF(C3&lt;=-0.5,"On pace",IF(C3&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5275,22 +5284,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="32" t="n">
         <v>46264</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A4+7)),"")</f>
         <v/>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="33">
         <f>IF(OR(B4="",B3=""),"",B4-B3)</f>
         <v/>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A4+7)),"")</f>
         <v/>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A4+7)),"")</f>
         <v/>
       </c>
@@ -5298,7 +5307,7 @@
         <f>IF(C4="","",IF(C4&lt;=-0.5,"On pace",IF(C4&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5312,22 +5321,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="32" t="n">
         <v>46271</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A5+7)),"")</f>
         <v/>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="33">
         <f>IF(OR(B5="",B4=""),"",B5-B4)</f>
         <v/>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A5+7)),"")</f>
         <v/>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A5+7)),"")</f>
         <v/>
       </c>
@@ -5335,7 +5344,7 @@
         <f>IF(C5="","",IF(C5&lt;=-0.5,"On pace",IF(C5&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5349,22 +5358,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="32" t="n">
         <v>46278</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A6+7)),"")</f>
         <v/>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="33">
         <f>IF(OR(B6="",B5=""),"",B6-B5)</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A6+7)),"")</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A6+7)),"")</f>
         <v/>
       </c>
@@ -5372,7 +5381,7 @@
         <f>IF(C6="","",IF(C6&lt;=-0.5,"On pace",IF(C6&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5386,22 +5395,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="32" t="n">
         <v>46285</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A7,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A7+7)),"")</f>
         <v/>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="33">
         <f>IF(OR(B7="",B6=""),"",B7-B6)</f>
         <v/>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A7,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A7+7)),"")</f>
         <v/>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A7,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A7+7)),"")</f>
         <v/>
       </c>
@@ -5409,7 +5418,7 @@
         <f>IF(C7="","",IF(C7&lt;=-0.5,"On pace",IF(C7&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5423,22 +5432,22 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="32" t="n">
         <v>46292</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A8,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A8+7)),"")</f>
         <v/>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="33">
         <f>IF(OR(B8="",B7=""),"",B8-B7)</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A8,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A8+7)),"")</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A8,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A8+7)),"")</f>
         <v/>
       </c>
@@ -5446,7 +5455,7 @@
         <f>IF(C8="","",IF(C8&lt;=-0.5,"On pace",IF(C8&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5460,22 +5469,22 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="32" t="n">
         <v>46299</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A9,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A9+7)),"")</f>
         <v/>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="33">
         <f>IF(OR(B9="",B8=""),"",B9-B8)</f>
         <v/>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A9,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A9+7)),"")</f>
         <v/>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A9,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A9+7)),"")</f>
         <v/>
       </c>
@@ -5483,7 +5492,7 @@
         <f>IF(C9="","",IF(C9&lt;=-0.5,"On pace",IF(C9&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5497,22 +5506,22 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="32" t="n">
         <v>46306</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A10,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A10+7)),"")</f>
         <v/>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="33">
         <f>IF(OR(B10="",B9=""),"",B10-B9)</f>
         <v/>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A10,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A10+7)),"")</f>
         <v/>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A10,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A10+7)),"")</f>
         <v/>
       </c>
@@ -5520,7 +5529,7 @@
         <f>IF(C10="","",IF(C10&lt;=-0.5,"On pace",IF(C10&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5534,22 +5543,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="32" t="n">
         <v>46313</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A11,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A11+7)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="33">
         <f>IF(OR(B11="",B10=""),"",B11-B10)</f>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A11,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A11+7)),"")</f>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A11,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A11+7)),"")</f>
         <v/>
       </c>
@@ -5557,7 +5566,7 @@
         <f>IF(C11="","",IF(C11&lt;=-0.5,"On pace",IF(C11&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5571,22 +5580,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="32" t="n">
         <v>46320</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A12,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A12+7)),"")</f>
         <v/>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="33">
         <f>IF(OR(B12="",B11=""),"",B12-B11)</f>
         <v/>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A12,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A12+7)),"")</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A12,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A12+7)),"")</f>
         <v/>
       </c>
@@ -5594,7 +5603,7 @@
         <f>IF(C12="","",IF(C12&lt;=-0.5,"On pace",IF(C12&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5608,22 +5617,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="32" t="n">
         <v>46327</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A13,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A13+7)),"")</f>
         <v/>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="33">
         <f>IF(OR(B13="",B12=""),"",B13-B12)</f>
         <v/>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A13,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A13+7)),"")</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A13,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A13+7)),"")</f>
         <v/>
       </c>
@@ -5631,7 +5640,7 @@
         <f>IF(C13="","",IF(C13&lt;=-0.5,"On pace",IF(C13&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5645,22 +5654,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="32" t="n">
         <v>46334</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A14,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A14+7)),"")</f>
         <v/>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="33">
         <f>IF(OR(B14="",B13=""),"",B14-B13)</f>
         <v/>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A14,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A14+7)),"")</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A14,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A14+7)),"")</f>
         <v/>
       </c>
@@ -5668,7 +5677,7 @@
         <f>IF(C14="","",IF(C14&lt;=-0.5,"On pace",IF(C14&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5682,22 +5691,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="32" t="n">
         <v>46341</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A15,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A15+7)),"")</f>
         <v/>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="33">
         <f>IF(OR(B15="",B14=""),"",B15-B14)</f>
         <v/>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A15,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A15+7)),"")</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A15,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A15+7)),"")</f>
         <v/>
       </c>
@@ -5705,7 +5714,7 @@
         <f>IF(C15="","",IF(C15&lt;=-0.5,"On pace",IF(C15&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5719,22 +5728,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="32" t="n">
         <v>46348</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A16,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A16+7)),"")</f>
         <v/>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="33">
         <f>IF(OR(B16="",B15=""),"",B16-B15)</f>
         <v/>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A16,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A16+7)),"")</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A16,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A16+7)),"")</f>
         <v/>
       </c>
@@ -5742,7 +5751,7 @@
         <f>IF(C16="","",IF(C16&lt;=-0.5,"On pace",IF(C16&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5756,22 +5765,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="32" t="n">
         <v>46355</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A17,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A17+7)),"")</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="33">
         <f>IF(OR(B17="",B16=""),"",B17-B16)</f>
         <v/>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A17,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A17+7)),"")</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A17,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A17+7)),"")</f>
         <v/>
       </c>
@@ -5779,7 +5788,7 @@
         <f>IF(C17="","",IF(C17&lt;=-0.5,"On pace",IF(C17&gt;0,"Check adherence","Slower than target")))</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="28">
         <f>Targets!$B$7</f>
         <v/>
       </c>
@@ -5853,19 +5862,18 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="n">
+      <c r="A2" s="35" t="n">
         <v>46235</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A2,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="22">
+      <c r="D2" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A2,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A2,0)+1)),"")</f>
         <v/>
       </c>
@@ -5879,22 +5887,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="n">
+      <c r="A3" s="35" t="n">
         <v>46266</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A3,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="33">
         <f>IF(OR(B3="",B2=""),"",B3-B2)</f>
         <v/>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A3,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A3,0)+1)),"")</f>
         <v/>
       </c>
@@ -5908,22 +5916,22 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="n">
+      <c r="A4" s="35" t="n">
         <v>46296</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A4,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="33">
         <f>IF(OR(B4="",B3=""),"",B4-B3)</f>
         <v/>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A4,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A4,0)+1)),"")</f>
         <v/>
       </c>
@@ -5937,22 +5945,22 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="35" t="n">
         <v>46327</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A5,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="33">
         <f>IF(OR(B5="",B4=""),"",B5-B4)</f>
         <v/>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A5,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A5,0)+1)),"")</f>
         <v/>
       </c>
@@ -5966,22 +5974,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="n">
+      <c r="A6" s="35" t="n">
         <v>46357</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A6,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="33">
         <f>IF(OR(B6="",B5=""),"",B6-B5)</f>
         <v/>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$C$2:$C$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A6,0)+1)),"")</f>
         <v/>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="34">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$D$2:$D$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(EOMONTH(A6,0)+1)),"")</f>
         <v/>
       </c>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Targets" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Daily Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Weekly Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Monthly Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Training &amp; Recovery" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Monthly Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5812,6 +5813,2498 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Training &amp; Recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ring + Tonal, logged from screenshots. Blue = you fill in. Sleep hours blank until the ring actually syncs a night.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Sleep (hrs)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Resting HR</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>HRV (ms)</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>SpO2 (%)</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>BP Sys</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>BP Dia</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Tonal Volume (lbs)</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Tonal Duration (min)</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>7-day Avg RHR</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>7-day Avg HRV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>128</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>129</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>89</v>
+      </c>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>Ring (generic/TK5) synced mid-day, sleep not yet recorded. Tonal: mid-session screenshot (Standing Single-Arm Row -&gt; Standing Chest Press) — send the end-of-workout summary screen for full volume/duration/calories.</t>
+        </is>
+      </c>
+      <c r="K5" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C5,$A$5:$A5,"&gt;="&amp;(A5-6),$A$5:$A5,"&lt;="&amp;A5),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D5,$A$5:$A5,"&gt;="&amp;(A5-6),$A$5:$A5,"&lt;="&amp;A5),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="K6" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C6,$A$5:$A6,"&gt;="&amp;(A6-6),$A$5:$A6,"&lt;="&amp;A6),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D6,$A$5:$A6,"&gt;="&amp;(A6-6),$A$5:$A6,"&lt;="&amp;A6),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="K7" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C7,$A$5:$A7,"&gt;="&amp;(A7-6),$A$5:$A7,"&lt;="&amp;A7),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D7,$A$5:$A7,"&gt;="&amp;(A7-6),$A$5:$A7,"&lt;="&amp;A7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="K8" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C8,$A$5:$A8,"&gt;="&amp;(A8-6),$A$5:$A8,"&lt;="&amp;A8),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D8,$A$5:$A8,"&gt;="&amp;(A8-6),$A$5:$A8,"&lt;="&amp;A8),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="K9" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C9,$A$5:$A9,"&gt;="&amp;(A9-6),$A$5:$A9,"&lt;="&amp;A9),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D9,$A$5:$A9,"&gt;="&amp;(A9-6),$A$5:$A9,"&lt;="&amp;A9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="K10" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C10,$A$5:$A10,"&gt;="&amp;(A10-6),$A$5:$A10,"&lt;="&amp;A10),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D10,$A$5:$A10,"&gt;="&amp;(A10-6),$A$5:$A10,"&lt;="&amp;A10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="K11" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C11,$A$5:$A11,"&gt;="&amp;(A11-6),$A$5:$A11,"&lt;="&amp;A11),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D11,$A$5:$A11,"&gt;="&amp;(A11-6),$A$5:$A11,"&lt;="&amp;A11),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="K12" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C12,$A$5:$A12,"&gt;="&amp;(A12-6),$A$5:$A12,"&lt;="&amp;A12),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D12,$A$5:$A12,"&gt;="&amp;(A12-6),$A$5:$A12,"&lt;="&amp;A12),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="K13" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C13,$A$5:$A13,"&gt;="&amp;(A13-6),$A$5:$A13,"&lt;="&amp;A13),"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D13,$A$5:$A13,"&gt;="&amp;(A13-6),$A$5:$A13,"&lt;="&amp;A13),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="K14" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C14,$A$5:$A14,"&gt;="&amp;(A14-6),$A$5:$A14,"&lt;="&amp;A14),"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D14,$A$5:$A14,"&gt;="&amp;(A14-6),$A$5:$A14,"&lt;="&amp;A14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="K15" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C15,$A$5:$A15,"&gt;="&amp;(A15-6),$A$5:$A15,"&lt;="&amp;A15),"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D15,$A$5:$A15,"&gt;="&amp;(A15-6),$A$5:$A15,"&lt;="&amp;A15),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="K16" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C16,$A$5:$A16,"&gt;="&amp;(A16-6),$A$5:$A16,"&lt;="&amp;A16),"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D16,$A$5:$A16,"&gt;="&amp;(A16-6),$A$5:$A16,"&lt;="&amp;A16),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="K17" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C17,$A$5:$A17,"&gt;="&amp;(A17-6),$A$5:$A17,"&lt;="&amp;A17),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D17,$A$5:$A17,"&gt;="&amp;(A17-6),$A$5:$A17,"&lt;="&amp;A17),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="K18" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C18,$A$5:$A18,"&gt;="&amp;(A18-6),$A$5:$A18,"&lt;="&amp;A18),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D18,$A$5:$A18,"&gt;="&amp;(A18-6),$A$5:$A18,"&lt;="&amp;A18),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="K19" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C19,$A$5:$A19,"&gt;="&amp;(A19-6),$A$5:$A19,"&lt;="&amp;A19),"")</f>
+        <v/>
+      </c>
+      <c r="L19" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D19,$A$5:$A19,"&gt;="&amp;(A19-6),$A$5:$A19,"&lt;="&amp;A19),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="K20" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C20,$A$5:$A20,"&gt;="&amp;(A20-6),$A$5:$A20,"&lt;="&amp;A20),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D20,$A$5:$A20,"&gt;="&amp;(A20-6),$A$5:$A20,"&lt;="&amp;A20),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="K21" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C21,$A$5:$A21,"&gt;="&amp;(A21-6),$A$5:$A21,"&lt;="&amp;A21),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D21,$A$5:$A21,"&gt;="&amp;(A21-6),$A$5:$A21,"&lt;="&amp;A21),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="K22" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C22,$A$5:$A22,"&gt;="&amp;(A22-6),$A$5:$A22,"&lt;="&amp;A22),"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D22,$A$5:$A22,"&gt;="&amp;(A22-6),$A$5:$A22,"&lt;="&amp;A22),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="K23" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C23,$A$5:$A23,"&gt;="&amp;(A23-6),$A$5:$A23,"&lt;="&amp;A23),"")</f>
+        <v/>
+      </c>
+      <c r="L23" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D23,$A$5:$A23,"&gt;="&amp;(A23-6),$A$5:$A23,"&lt;="&amp;A23),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="K24" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C24,$A$5:$A24,"&gt;="&amp;(A24-6),$A$5:$A24,"&lt;="&amp;A24),"")</f>
+        <v/>
+      </c>
+      <c r="L24" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D24,$A$5:$A24,"&gt;="&amp;(A24-6),$A$5:$A24,"&lt;="&amp;A24),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="K25" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C25,$A$5:$A25,"&gt;="&amp;(A25-6),$A$5:$A25,"&lt;="&amp;A25),"")</f>
+        <v/>
+      </c>
+      <c r="L25" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D25,$A$5:$A25,"&gt;="&amp;(A25-6),$A$5:$A25,"&lt;="&amp;A25),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="K26" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C26,$A$5:$A26,"&gt;="&amp;(A26-6),$A$5:$A26,"&lt;="&amp;A26),"")</f>
+        <v/>
+      </c>
+      <c r="L26" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D26,$A$5:$A26,"&gt;="&amp;(A26-6),$A$5:$A26,"&lt;="&amp;A26),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="K27" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C27,$A$5:$A27,"&gt;="&amp;(A27-6),$A$5:$A27,"&lt;="&amp;A27),"")</f>
+        <v/>
+      </c>
+      <c r="L27" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D27,$A$5:$A27,"&gt;="&amp;(A27-6),$A$5:$A27,"&lt;="&amp;A27),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="K28" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C28,$A$5:$A28,"&gt;="&amp;(A28-6),$A$5:$A28,"&lt;="&amp;A28),"")</f>
+        <v/>
+      </c>
+      <c r="L28" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D28,$A$5:$A28,"&gt;="&amp;(A28-6),$A$5:$A28,"&lt;="&amp;A28),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="K29" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C29,$A$5:$A29,"&gt;="&amp;(A29-6),$A$5:$A29,"&lt;="&amp;A29),"")</f>
+        <v/>
+      </c>
+      <c r="L29" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D29,$A$5:$A29,"&gt;="&amp;(A29-6),$A$5:$A29,"&lt;="&amp;A29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="K30" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C30,$A$5:$A30,"&gt;="&amp;(A30-6),$A$5:$A30,"&lt;="&amp;A30),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D30,$A$5:$A30,"&gt;="&amp;(A30-6),$A$5:$A30,"&lt;="&amp;A30),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="K31" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C31,$A$5:$A31,"&gt;="&amp;(A31-6),$A$5:$A31,"&lt;="&amp;A31),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D31,$A$5:$A31,"&gt;="&amp;(A31-6),$A$5:$A31,"&lt;="&amp;A31),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="K32" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C32,$A$5:$A32,"&gt;="&amp;(A32-6),$A$5:$A32,"&lt;="&amp;A32),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D32,$A$5:$A32,"&gt;="&amp;(A32-6),$A$5:$A32,"&lt;="&amp;A32),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="K33" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C33,$A$5:$A33,"&gt;="&amp;(A33-6),$A$5:$A33,"&lt;="&amp;A33),"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D33,$A$5:$A33,"&gt;="&amp;(A33-6),$A$5:$A33,"&lt;="&amp;A33),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="K34" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C34,$A$5:$A34,"&gt;="&amp;(A34-6),$A$5:$A34,"&lt;="&amp;A34),"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D34,$A$5:$A34,"&gt;="&amp;(A34-6),$A$5:$A34,"&lt;="&amp;A34),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="K35" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C35,$A$5:$A35,"&gt;="&amp;(A35-6),$A$5:$A35,"&lt;="&amp;A35),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D35,$A$5:$A35,"&gt;="&amp;(A35-6),$A$5:$A35,"&lt;="&amp;A35),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="K36" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C36,$A$5:$A36,"&gt;="&amp;(A36-6),$A$5:$A36,"&lt;="&amp;A36),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D36,$A$5:$A36,"&gt;="&amp;(A36-6),$A$5:$A36,"&lt;="&amp;A36),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="18" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="K37" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C37,$A$5:$A37,"&gt;="&amp;(A37-6),$A$5:$A37,"&lt;="&amp;A37),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D37,$A$5:$A37,"&gt;="&amp;(A37-6),$A$5:$A37,"&lt;="&amp;A37),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="K38" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C38,$A$5:$A38,"&gt;="&amp;(A38-6),$A$5:$A38,"&lt;="&amp;A38),"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D38,$A$5:$A38,"&gt;="&amp;(A38-6),$A$5:$A38,"&lt;="&amp;A38),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="K39" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C39,$A$5:$A39,"&gt;="&amp;(A39-6),$A$5:$A39,"&lt;="&amp;A39),"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D39,$A$5:$A39,"&gt;="&amp;(A39-6),$A$5:$A39,"&lt;="&amp;A39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="K40" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C40,$A$5:$A40,"&gt;="&amp;(A40-6),$A$5:$A40,"&lt;="&amp;A40),"")</f>
+        <v/>
+      </c>
+      <c r="L40" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D40,$A$5:$A40,"&gt;="&amp;(A40-6),$A$5:$A40,"&lt;="&amp;A40),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="K41" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C41,$A$5:$A41,"&gt;="&amp;(A41-6),$A$5:$A41,"&lt;="&amp;A41),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D41,$A$5:$A41,"&gt;="&amp;(A41-6),$A$5:$A41,"&lt;="&amp;A41),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="K42" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C42,$A$5:$A42,"&gt;="&amp;(A42-6),$A$5:$A42,"&lt;="&amp;A42),"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D42,$A$5:$A42,"&gt;="&amp;(A42-6),$A$5:$A42,"&lt;="&amp;A42),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="18" t="n"/>
+      <c r="H43" s="18" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="K43" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C43,$A$5:$A43,"&gt;="&amp;(A43-6),$A$5:$A43,"&lt;="&amp;A43),"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D43,$A$5:$A43,"&gt;="&amp;(A43-6),$A$5:$A43,"&lt;="&amp;A43),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="18" t="n"/>
+      <c r="H44" s="18" t="n"/>
+      <c r="I44" s="18" t="n"/>
+      <c r="K44" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C44,$A$5:$A44,"&gt;="&amp;(A44-6),$A$5:$A44,"&lt;="&amp;A44),"")</f>
+        <v/>
+      </c>
+      <c r="L44" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D44,$A$5:$A44,"&gt;="&amp;(A44-6),$A$5:$A44,"&lt;="&amp;A44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="K45" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C45,$A$5:$A45,"&gt;="&amp;(A45-6),$A$5:$A45,"&lt;="&amp;A45),"")</f>
+        <v/>
+      </c>
+      <c r="L45" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D45,$A$5:$A45,"&gt;="&amp;(A45-6),$A$5:$A45,"&lt;="&amp;A45),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="18" t="n"/>
+      <c r="H46" s="18" t="n"/>
+      <c r="I46" s="18" t="n"/>
+      <c r="K46" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C46,$A$5:$A46,"&gt;="&amp;(A46-6),$A$5:$A46,"&lt;="&amp;A46),"")</f>
+        <v/>
+      </c>
+      <c r="L46" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D46,$A$5:$A46,"&gt;="&amp;(A46-6),$A$5:$A46,"&lt;="&amp;A46),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="K47" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C47,$A$5:$A47,"&gt;="&amp;(A47-6),$A$5:$A47,"&lt;="&amp;A47),"")</f>
+        <v/>
+      </c>
+      <c r="L47" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D47,$A$5:$A47,"&gt;="&amp;(A47-6),$A$5:$A47,"&lt;="&amp;A47),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="18" t="n"/>
+      <c r="I48" s="18" t="n"/>
+      <c r="K48" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C48,$A$5:$A48,"&gt;="&amp;(A48-6),$A$5:$A48,"&lt;="&amp;A48),"")</f>
+        <v/>
+      </c>
+      <c r="L48" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D48,$A$5:$A48,"&gt;="&amp;(A48-6),$A$5:$A48,"&lt;="&amp;A48),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="18" t="n"/>
+      <c r="I49" s="18" t="n"/>
+      <c r="K49" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C49,$A$5:$A49,"&gt;="&amp;(A49-6),$A$5:$A49,"&lt;="&amp;A49),"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D49,$A$5:$A49,"&gt;="&amp;(A49-6),$A$5:$A49,"&lt;="&amp;A49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="K50" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C50,$A$5:$A50,"&gt;="&amp;(A50-6),$A$5:$A50,"&lt;="&amp;A50),"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D50,$A$5:$A50,"&gt;="&amp;(A50-6),$A$5:$A50,"&lt;="&amp;A50),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="K51" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C51,$A$5:$A51,"&gt;="&amp;(A51-6),$A$5:$A51,"&lt;="&amp;A51),"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D51,$A$5:$A51,"&gt;="&amp;(A51-6),$A$5:$A51,"&lt;="&amp;A51),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="18" t="n"/>
+      <c r="H52" s="18" t="n"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="K52" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C52,$A$5:$A52,"&gt;="&amp;(A52-6),$A$5:$A52,"&lt;="&amp;A52),"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D52,$A$5:$A52,"&gt;="&amp;(A52-6),$A$5:$A52,"&lt;="&amp;A52),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="18" t="n"/>
+      <c r="K53" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C53,$A$5:$A53,"&gt;="&amp;(A53-6),$A$5:$A53,"&lt;="&amp;A53),"")</f>
+        <v/>
+      </c>
+      <c r="L53" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D53,$A$5:$A53,"&gt;="&amp;(A53-6),$A$5:$A53,"&lt;="&amp;A53),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+      <c r="K54" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C54,$A$5:$A54,"&gt;="&amp;(A54-6),$A$5:$A54,"&lt;="&amp;A54),"")</f>
+        <v/>
+      </c>
+      <c r="L54" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D54,$A$5:$A54,"&gt;="&amp;(A54-6),$A$5:$A54,"&lt;="&amp;A54),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+      <c r="K55" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C55,$A$5:$A55,"&gt;="&amp;(A55-6),$A$5:$A55,"&lt;="&amp;A55),"")</f>
+        <v/>
+      </c>
+      <c r="L55" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D55,$A$5:$A55,"&gt;="&amp;(A55-6),$A$5:$A55,"&lt;="&amp;A55),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n"/>
+      <c r="K56" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C56,$A$5:$A56,"&gt;="&amp;(A56-6),$A$5:$A56,"&lt;="&amp;A56),"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D56,$A$5:$A56,"&gt;="&amp;(A56-6),$A$5:$A56,"&lt;="&amp;A56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
+      <c r="K57" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C57,$A$5:$A57,"&gt;="&amp;(A57-6),$A$5:$A57,"&lt;="&amp;A57),"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D57,$A$5:$A57,"&gt;="&amp;(A57-6),$A$5:$A57,"&lt;="&amp;A57),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="18" t="n"/>
+      <c r="I58" s="18" t="n"/>
+      <c r="K58" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C58,$A$5:$A58,"&gt;="&amp;(A58-6),$A$5:$A58,"&lt;="&amp;A58),"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D58,$A$5:$A58,"&gt;="&amp;(A58-6),$A$5:$A58,"&lt;="&amp;A58),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n"/>
+      <c r="K59" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C59,$A$5:$A59,"&gt;="&amp;(A59-6),$A$5:$A59,"&lt;="&amp;A59),"")</f>
+        <v/>
+      </c>
+      <c r="L59" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D59,$A$5:$A59,"&gt;="&amp;(A59-6),$A$5:$A59,"&lt;="&amp;A59),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+      <c r="K60" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C60,$A$5:$A60,"&gt;="&amp;(A60-6),$A$5:$A60,"&lt;="&amp;A60),"")</f>
+        <v/>
+      </c>
+      <c r="L60" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D60,$A$5:$A60,"&gt;="&amp;(A60-6),$A$5:$A60,"&lt;="&amp;A60),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="K61" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C61,$A$5:$A61,"&gt;="&amp;(A61-6),$A$5:$A61,"&lt;="&amp;A61),"")</f>
+        <v/>
+      </c>
+      <c r="L61" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D61,$A$5:$A61,"&gt;="&amp;(A61-6),$A$5:$A61,"&lt;="&amp;A61),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n"/>
+      <c r="K62" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C62,$A$5:$A62,"&gt;="&amp;(A62-6),$A$5:$A62,"&lt;="&amp;A62),"")</f>
+        <v/>
+      </c>
+      <c r="L62" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D62,$A$5:$A62,"&gt;="&amp;(A62-6),$A$5:$A62,"&lt;="&amp;A62),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n"/>
+      <c r="K63" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C63,$A$5:$A63,"&gt;="&amp;(A63-6),$A$5:$A63,"&lt;="&amp;A63),"")</f>
+        <v/>
+      </c>
+      <c r="L63" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D63,$A$5:$A63,"&gt;="&amp;(A63-6),$A$5:$A63,"&lt;="&amp;A63),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="18" t="n"/>
+      <c r="K64" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C64,$A$5:$A64,"&gt;="&amp;(A64-6),$A$5:$A64,"&lt;="&amp;A64),"")</f>
+        <v/>
+      </c>
+      <c r="L64" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D64,$A$5:$A64,"&gt;="&amp;(A64-6),$A$5:$A64,"&lt;="&amp;A64),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="18" t="n"/>
+      <c r="K65" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C65,$A$5:$A65,"&gt;="&amp;(A65-6),$A$5:$A65,"&lt;="&amp;A65),"")</f>
+        <v/>
+      </c>
+      <c r="L65" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D65,$A$5:$A65,"&gt;="&amp;(A65-6),$A$5:$A65,"&lt;="&amp;A65),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="32" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="18" t="n"/>
+      <c r="I66" s="18" t="n"/>
+      <c r="K66" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C66,$A$5:$A66,"&gt;="&amp;(A66-6),$A$5:$A66,"&lt;="&amp;A66),"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D66,$A$5:$A66,"&gt;="&amp;(A66-6),$A$5:$A66,"&lt;="&amp;A66),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="32" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="18" t="n"/>
+      <c r="I67" s="18" t="n"/>
+      <c r="K67" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C67,$A$5:$A67,"&gt;="&amp;(A67-6),$A$5:$A67,"&lt;="&amp;A67),"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D67,$A$5:$A67,"&gt;="&amp;(A67-6),$A$5:$A67,"&lt;="&amp;A67),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="32" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="18" t="n"/>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+      <c r="K68" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C68,$A$5:$A68,"&gt;="&amp;(A68-6),$A$5:$A68,"&lt;="&amp;A68),"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D68,$A$5:$A68,"&gt;="&amp;(A68-6),$A$5:$A68,"&lt;="&amp;A68),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="32" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="18" t="n"/>
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="18" t="n"/>
+      <c r="H69" s="18" t="n"/>
+      <c r="I69" s="18" t="n"/>
+      <c r="K69" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C69,$A$5:$A69,"&gt;="&amp;(A69-6),$A$5:$A69,"&lt;="&amp;A69),"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D69,$A$5:$A69,"&gt;="&amp;(A69-6),$A$5:$A69,"&lt;="&amp;A69),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="18" t="n"/>
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="18" t="n"/>
+      <c r="H70" s="18" t="n"/>
+      <c r="I70" s="18" t="n"/>
+      <c r="K70" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C70,$A$5:$A70,"&gt;="&amp;(A70-6),$A$5:$A70,"&lt;="&amp;A70),"")</f>
+        <v/>
+      </c>
+      <c r="L70" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D70,$A$5:$A70,"&gt;="&amp;(A70-6),$A$5:$A70,"&lt;="&amp;A70),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+      <c r="K71" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C71,$A$5:$A71,"&gt;="&amp;(A71-6),$A$5:$A71,"&lt;="&amp;A71),"")</f>
+        <v/>
+      </c>
+      <c r="L71" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D71,$A$5:$A71,"&gt;="&amp;(A71-6),$A$5:$A71,"&lt;="&amp;A71),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="18" t="n"/>
+      <c r="C72" s="18" t="n"/>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="18" t="n"/>
+      <c r="I72" s="18" t="n"/>
+      <c r="K72" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C72,$A$5:$A72,"&gt;="&amp;(A72-6),$A$5:$A72,"&lt;="&amp;A72),"")</f>
+        <v/>
+      </c>
+      <c r="L72" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D72,$A$5:$A72,"&gt;="&amp;(A72-6),$A$5:$A72,"&lt;="&amp;A72),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+      <c r="H73" s="18" t="n"/>
+      <c r="I73" s="18" t="n"/>
+      <c r="K73" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C73,$A$5:$A73,"&gt;="&amp;(A73-6),$A$5:$A73,"&lt;="&amp;A73),"")</f>
+        <v/>
+      </c>
+      <c r="L73" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D73,$A$5:$A73,"&gt;="&amp;(A73-6),$A$5:$A73,"&lt;="&amp;A73),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="n"/>
+      <c r="K74" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C74,$A$5:$A74,"&gt;="&amp;(A74-6),$A$5:$A74,"&lt;="&amp;A74),"")</f>
+        <v/>
+      </c>
+      <c r="L74" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D74,$A$5:$A74,"&gt;="&amp;(A74-6),$A$5:$A74,"&lt;="&amp;A74),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="32" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="18" t="n"/>
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+      <c r="G75" s="18" t="n"/>
+      <c r="H75" s="18" t="n"/>
+      <c r="I75" s="18" t="n"/>
+      <c r="K75" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C75,$A$5:$A75,"&gt;="&amp;(A75-6),$A$5:$A75,"&lt;="&amp;A75),"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D75,$A$5:$A75,"&gt;="&amp;(A75-6),$A$5:$A75,"&lt;="&amp;A75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="n"/>
+      <c r="K76" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C76,$A$5:$A76,"&gt;="&amp;(A76-6),$A$5:$A76,"&lt;="&amp;A76),"")</f>
+        <v/>
+      </c>
+      <c r="L76" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D76,$A$5:$A76,"&gt;="&amp;(A76-6),$A$5:$A76,"&lt;="&amp;A76),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="32" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+      <c r="K77" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C77,$A$5:$A77,"&gt;="&amp;(A77-6),$A$5:$A77,"&lt;="&amp;A77),"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D77,$A$5:$A77,"&gt;="&amp;(A77-6),$A$5:$A77,"&lt;="&amp;A77),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="32" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="18" t="n"/>
+      <c r="C78" s="18" t="n"/>
+      <c r="D78" s="18" t="n"/>
+      <c r="E78" s="18" t="n"/>
+      <c r="F78" s="18" t="n"/>
+      <c r="G78" s="18" t="n"/>
+      <c r="H78" s="18" t="n"/>
+      <c r="I78" s="18" t="n"/>
+      <c r="K78" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C78,$A$5:$A78,"&gt;="&amp;(A78-6),$A$5:$A78,"&lt;="&amp;A78),"")</f>
+        <v/>
+      </c>
+      <c r="L78" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D78,$A$5:$A78,"&gt;="&amp;(A78-6),$A$5:$A78,"&lt;="&amp;A78),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="32" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="18" t="n"/>
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="18" t="n"/>
+      <c r="I79" s="18" t="n"/>
+      <c r="K79" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C79,$A$5:$A79,"&gt;="&amp;(A79-6),$A$5:$A79,"&lt;="&amp;A79),"")</f>
+        <v/>
+      </c>
+      <c r="L79" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D79,$A$5:$A79,"&gt;="&amp;(A79-6),$A$5:$A79,"&lt;="&amp;A79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B80" s="18" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+      <c r="K80" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C80,$A$5:$A80,"&gt;="&amp;(A80-6),$A$5:$A80,"&lt;="&amp;A80),"")</f>
+        <v/>
+      </c>
+      <c r="L80" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D80,$A$5:$A80,"&gt;="&amp;(A80-6),$A$5:$A80,"&lt;="&amp;A80),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B81" s="18" t="n"/>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+      <c r="K81" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C81,$A$5:$A81,"&gt;="&amp;(A81-6),$A$5:$A81,"&lt;="&amp;A81),"")</f>
+        <v/>
+      </c>
+      <c r="L81" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D81,$A$5:$A81,"&gt;="&amp;(A81-6),$A$5:$A81,"&lt;="&amp;A81),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="32" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B82" s="18" t="n"/>
+      <c r="C82" s="18" t="n"/>
+      <c r="D82" s="18" t="n"/>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="18" t="n"/>
+      <c r="I82" s="18" t="n"/>
+      <c r="K82" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C82,$A$5:$A82,"&gt;="&amp;(A82-6),$A$5:$A82,"&lt;="&amp;A82),"")</f>
+        <v/>
+      </c>
+      <c r="L82" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D82,$A$5:$A82,"&gt;="&amp;(A82-6),$A$5:$A82,"&lt;="&amp;A82),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B83" s="18" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="K83" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C83,$A$5:$A83,"&gt;="&amp;(A83-6),$A$5:$A83,"&lt;="&amp;A83),"")</f>
+        <v/>
+      </c>
+      <c r="L83" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D83,$A$5:$A83,"&gt;="&amp;(A83-6),$A$5:$A83,"&lt;="&amp;A83),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="32" t="n">
+        <v>46329</v>
+      </c>
+      <c r="B84" s="18" t="n"/>
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="K84" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C84,$A$5:$A84,"&gt;="&amp;(A84-6),$A$5:$A84,"&lt;="&amp;A84),"")</f>
+        <v/>
+      </c>
+      <c r="L84" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D84,$A$5:$A84,"&gt;="&amp;(A84-6),$A$5:$A84,"&lt;="&amp;A84),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="32" t="n">
+        <v>46330</v>
+      </c>
+      <c r="B85" s="18" t="n"/>
+      <c r="C85" s="18" t="n"/>
+      <c r="D85" s="18" t="n"/>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="18" t="n"/>
+      <c r="H85" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+      <c r="K85" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C85,$A$5:$A85,"&gt;="&amp;(A85-6),$A$5:$A85,"&lt;="&amp;A85),"")</f>
+        <v/>
+      </c>
+      <c r="L85" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D85,$A$5:$A85,"&gt;="&amp;(A85-6),$A$5:$A85,"&lt;="&amp;A85),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="32" t="n">
+        <v>46331</v>
+      </c>
+      <c r="B86" s="18" t="n"/>
+      <c r="C86" s="18" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+      <c r="K86" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C86,$A$5:$A86,"&gt;="&amp;(A86-6),$A$5:$A86,"&lt;="&amp;A86),"")</f>
+        <v/>
+      </c>
+      <c r="L86" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D86,$A$5:$A86,"&gt;="&amp;(A86-6),$A$5:$A86,"&lt;="&amp;A86),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="32" t="n">
+        <v>46332</v>
+      </c>
+      <c r="B87" s="18" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="n"/>
+      <c r="I87" s="18" t="n"/>
+      <c r="K87" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C87,$A$5:$A87,"&gt;="&amp;(A87-6),$A$5:$A87,"&lt;="&amp;A87),"")</f>
+        <v/>
+      </c>
+      <c r="L87" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D87,$A$5:$A87,"&gt;="&amp;(A87-6),$A$5:$A87,"&lt;="&amp;A87),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="32" t="n">
+        <v>46333</v>
+      </c>
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="18" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="18" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="18" t="n"/>
+      <c r="K88" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C88,$A$5:$A88,"&gt;="&amp;(A88-6),$A$5:$A88,"&lt;="&amp;A88),"")</f>
+        <v/>
+      </c>
+      <c r="L88" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D88,$A$5:$A88,"&gt;="&amp;(A88-6),$A$5:$A88,"&lt;="&amp;A88),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="32" t="n">
+        <v>46334</v>
+      </c>
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
+      <c r="K89" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C89,$A$5:$A89,"&gt;="&amp;(A89-6),$A$5:$A89,"&lt;="&amp;A89),"")</f>
+        <v/>
+      </c>
+      <c r="L89" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D89,$A$5:$A89,"&gt;="&amp;(A89-6),$A$5:$A89,"&lt;="&amp;A89),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="32" t="n">
+        <v>46335</v>
+      </c>
+      <c r="B90" s="18" t="n"/>
+      <c r="C90" s="18" t="n"/>
+      <c r="D90" s="18" t="n"/>
+      <c r="E90" s="18" t="n"/>
+      <c r="F90" s="18" t="n"/>
+      <c r="G90" s="18" t="n"/>
+      <c r="H90" s="18" t="n"/>
+      <c r="I90" s="18" t="n"/>
+      <c r="K90" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C90,$A$5:$A90,"&gt;="&amp;(A90-6),$A$5:$A90,"&lt;="&amp;A90),"")</f>
+        <v/>
+      </c>
+      <c r="L90" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D90,$A$5:$A90,"&gt;="&amp;(A90-6),$A$5:$A90,"&lt;="&amp;A90),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="32" t="n">
+        <v>46336</v>
+      </c>
+      <c r="B91" s="18" t="n"/>
+      <c r="C91" s="18" t="n"/>
+      <c r="D91" s="18" t="n"/>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+      <c r="K91" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C91,$A$5:$A91,"&gt;="&amp;(A91-6),$A$5:$A91,"&lt;="&amp;A91),"")</f>
+        <v/>
+      </c>
+      <c r="L91" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D91,$A$5:$A91,"&gt;="&amp;(A91-6),$A$5:$A91,"&lt;="&amp;A91),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="32" t="n">
+        <v>46337</v>
+      </c>
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="18" t="n"/>
+      <c r="E92" s="18" t="n"/>
+      <c r="F92" s="18" t="n"/>
+      <c r="G92" s="18" t="n"/>
+      <c r="H92" s="18" t="n"/>
+      <c r="I92" s="18" t="n"/>
+      <c r="K92" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C92,$A$5:$A92,"&gt;="&amp;(A92-6),$A$5:$A92,"&lt;="&amp;A92),"")</f>
+        <v/>
+      </c>
+      <c r="L92" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D92,$A$5:$A92,"&gt;="&amp;(A92-6),$A$5:$A92,"&lt;="&amp;A92),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="32" t="n">
+        <v>46338</v>
+      </c>
+      <c r="B93" s="18" t="n"/>
+      <c r="C93" s="18" t="n"/>
+      <c r="D93" s="18" t="n"/>
+      <c r="E93" s="18" t="n"/>
+      <c r="F93" s="18" t="n"/>
+      <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="n"/>
+      <c r="I93" s="18" t="n"/>
+      <c r="K93" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C93,$A$5:$A93,"&gt;="&amp;(A93-6),$A$5:$A93,"&lt;="&amp;A93),"")</f>
+        <v/>
+      </c>
+      <c r="L93" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D93,$A$5:$A93,"&gt;="&amp;(A93-6),$A$5:$A93,"&lt;="&amp;A93),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="32" t="n">
+        <v>46339</v>
+      </c>
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+      <c r="G94" s="18" t="n"/>
+      <c r="H94" s="18" t="n"/>
+      <c r="I94" s="18" t="n"/>
+      <c r="K94" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C94,$A$5:$A94,"&gt;="&amp;(A94-6),$A$5:$A94,"&lt;="&amp;A94),"")</f>
+        <v/>
+      </c>
+      <c r="L94" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D94,$A$5:$A94,"&gt;="&amp;(A94-6),$A$5:$A94,"&lt;="&amp;A94),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="32" t="n">
+        <v>46340</v>
+      </c>
+      <c r="B95" s="18" t="n"/>
+      <c r="C95" s="18" t="n"/>
+      <c r="D95" s="18" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
+      <c r="G95" s="18" t="n"/>
+      <c r="H95" s="18" t="n"/>
+      <c r="I95" s="18" t="n"/>
+      <c r="K95" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C95,$A$5:$A95,"&gt;="&amp;(A95-6),$A$5:$A95,"&lt;="&amp;A95),"")</f>
+        <v/>
+      </c>
+      <c r="L95" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D95,$A$5:$A95,"&gt;="&amp;(A95-6),$A$5:$A95,"&lt;="&amp;A95),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="32" t="n">
+        <v>46341</v>
+      </c>
+      <c r="B96" s="18" t="n"/>
+      <c r="C96" s="18" t="n"/>
+      <c r="D96" s="18" t="n"/>
+      <c r="E96" s="18" t="n"/>
+      <c r="F96" s="18" t="n"/>
+      <c r="G96" s="18" t="n"/>
+      <c r="H96" s="18" t="n"/>
+      <c r="I96" s="18" t="n"/>
+      <c r="K96" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C96,$A$5:$A96,"&gt;="&amp;(A96-6),$A$5:$A96,"&lt;="&amp;A96),"")</f>
+        <v/>
+      </c>
+      <c r="L96" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D96,$A$5:$A96,"&gt;="&amp;(A96-6),$A$5:$A96,"&lt;="&amp;A96),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="32" t="n">
+        <v>46342</v>
+      </c>
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="18" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+      <c r="K97" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C97,$A$5:$A97,"&gt;="&amp;(A97-6),$A$5:$A97,"&lt;="&amp;A97),"")</f>
+        <v/>
+      </c>
+      <c r="L97" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D97,$A$5:$A97,"&gt;="&amp;(A97-6),$A$5:$A97,"&lt;="&amp;A97),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="32" t="n">
+        <v>46343</v>
+      </c>
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="n"/>
+      <c r="D98" s="18" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+      <c r="K98" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C98,$A$5:$A98,"&gt;="&amp;(A98-6),$A$5:$A98,"&lt;="&amp;A98),"")</f>
+        <v/>
+      </c>
+      <c r="L98" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D98,$A$5:$A98,"&gt;="&amp;(A98-6),$A$5:$A98,"&lt;="&amp;A98),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="n">
+        <v>46344</v>
+      </c>
+      <c r="B99" s="18" t="n"/>
+      <c r="C99" s="18" t="n"/>
+      <c r="D99" s="18" t="n"/>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+      <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="n"/>
+      <c r="I99" s="18" t="n"/>
+      <c r="K99" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C99,$A$5:$A99,"&gt;="&amp;(A99-6),$A$5:$A99,"&lt;="&amp;A99),"")</f>
+        <v/>
+      </c>
+      <c r="L99" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D99,$A$5:$A99,"&gt;="&amp;(A99-6),$A$5:$A99,"&lt;="&amp;A99),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="n">
+        <v>46345</v>
+      </c>
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="18" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="18" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
+      <c r="K100" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C100,$A$5:$A100,"&gt;="&amp;(A100-6),$A$5:$A100,"&lt;="&amp;A100),"")</f>
+        <v/>
+      </c>
+      <c r="L100" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D100,$A$5:$A100,"&gt;="&amp;(A100-6),$A$5:$A100,"&lt;="&amp;A100),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="n">
+        <v>46346</v>
+      </c>
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
+      <c r="K101" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C101,$A$5:$A101,"&gt;="&amp;(A101-6),$A$5:$A101,"&lt;="&amp;A101),"")</f>
+        <v/>
+      </c>
+      <c r="L101" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D101,$A$5:$A101,"&gt;="&amp;(A101-6),$A$5:$A101,"&lt;="&amp;A101),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="32" t="n">
+        <v>46347</v>
+      </c>
+      <c r="B102" s="18" t="n"/>
+      <c r="C102" s="18" t="n"/>
+      <c r="D102" s="18" t="n"/>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="K102" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C102,$A$5:$A102,"&gt;="&amp;(A102-6),$A$5:$A102,"&lt;="&amp;A102),"")</f>
+        <v/>
+      </c>
+      <c r="L102" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D102,$A$5:$A102,"&gt;="&amp;(A102-6),$A$5:$A102,"&lt;="&amp;A102),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="32" t="n">
+        <v>46348</v>
+      </c>
+      <c r="B103" s="18" t="n"/>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+      <c r="K103" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C103,$A$5:$A103,"&gt;="&amp;(A103-6),$A$5:$A103,"&lt;="&amp;A103),"")</f>
+        <v/>
+      </c>
+      <c r="L103" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D103,$A$5:$A103,"&gt;="&amp;(A103-6),$A$5:$A103,"&lt;="&amp;A103),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="32" t="n">
+        <v>46349</v>
+      </c>
+      <c r="B104" s="18" t="n"/>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="18" t="n"/>
+      <c r="E104" s="18" t="n"/>
+      <c r="F104" s="18" t="n"/>
+      <c r="G104" s="18" t="n"/>
+      <c r="H104" s="18" t="n"/>
+      <c r="I104" s="18" t="n"/>
+      <c r="K104" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C104,$A$5:$A104,"&gt;="&amp;(A104-6),$A$5:$A104,"&lt;="&amp;A104),"")</f>
+        <v/>
+      </c>
+      <c r="L104" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D104,$A$5:$A104,"&gt;="&amp;(A104-6),$A$5:$A104,"&lt;="&amp;A104),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="32" t="n">
+        <v>46350</v>
+      </c>
+      <c r="B105" s="18" t="n"/>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="18" t="n"/>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="18" t="n"/>
+      <c r="G105" s="18" t="n"/>
+      <c r="H105" s="18" t="n"/>
+      <c r="I105" s="18" t="n"/>
+      <c r="K105" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C105,$A$5:$A105,"&gt;="&amp;(A105-6),$A$5:$A105,"&lt;="&amp;A105),"")</f>
+        <v/>
+      </c>
+      <c r="L105" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D105,$A$5:$A105,"&gt;="&amp;(A105-6),$A$5:$A105,"&lt;="&amp;A105),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="32" t="n">
+        <v>46351</v>
+      </c>
+      <c r="B106" s="18" t="n"/>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+      <c r="K106" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C106,$A$5:$A106,"&gt;="&amp;(A106-6),$A$5:$A106,"&lt;="&amp;A106),"")</f>
+        <v/>
+      </c>
+      <c r="L106" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D106,$A$5:$A106,"&gt;="&amp;(A106-6),$A$5:$A106,"&lt;="&amp;A106),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="32" t="n">
+        <v>46352</v>
+      </c>
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
+      <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="n"/>
+      <c r="I107" s="18" t="n"/>
+      <c r="K107" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C107,$A$5:$A107,"&gt;="&amp;(A107-6),$A$5:$A107,"&lt;="&amp;A107),"")</f>
+        <v/>
+      </c>
+      <c r="L107" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D107,$A$5:$A107,"&gt;="&amp;(A107-6),$A$5:$A107,"&lt;="&amp;A107),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="32" t="n">
+        <v>46353</v>
+      </c>
+      <c r="B108" s="18" t="n"/>
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="18" t="n"/>
+      <c r="G108" s="18" t="n"/>
+      <c r="H108" s="18" t="n"/>
+      <c r="I108" s="18" t="n"/>
+      <c r="K108" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C108,$A$5:$A108,"&gt;="&amp;(A108-6),$A$5:$A108,"&lt;="&amp;A108),"")</f>
+        <v/>
+      </c>
+      <c r="L108" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D108,$A$5:$A108,"&gt;="&amp;(A108-6),$A$5:$A108,"&lt;="&amp;A108),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="32" t="n">
+        <v>46354</v>
+      </c>
+      <c r="B109" s="18" t="n"/>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="18" t="n"/>
+      <c r="E109" s="18" t="n"/>
+      <c r="F109" s="18" t="n"/>
+      <c r="G109" s="18" t="n"/>
+      <c r="H109" s="18" t="n"/>
+      <c r="I109" s="18" t="n"/>
+      <c r="K109" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C109,$A$5:$A109,"&gt;="&amp;(A109-6),$A$5:$A109,"&lt;="&amp;A109),"")</f>
+        <v/>
+      </c>
+      <c r="L109" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D109,$A$5:$A109,"&gt;="&amp;(A109-6),$A$5:$A109,"&lt;="&amp;A109),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="32" t="n">
+        <v>46355</v>
+      </c>
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="18" t="n"/>
+      <c r="G110" s="18" t="n"/>
+      <c r="H110" s="18" t="n"/>
+      <c r="I110" s="18" t="n"/>
+      <c r="K110" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C110,$A$5:$A110,"&gt;="&amp;(A110-6),$A$5:$A110,"&lt;="&amp;A110),"")</f>
+        <v/>
+      </c>
+      <c r="L110" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D110,$A$5:$A110,"&gt;="&amp;(A110-6),$A$5:$A110,"&lt;="&amp;A110),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="32" t="n">
+        <v>46356</v>
+      </c>
+      <c r="B111" s="18" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+      <c r="K111" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C111,$A$5:$A111,"&gt;="&amp;(A111-6),$A$5:$A111,"&lt;="&amp;A111),"")</f>
+        <v/>
+      </c>
+      <c r="L111" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D111,$A$5:$A111,"&gt;="&amp;(A111-6),$A$5:$A111,"&lt;="&amp;A111),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="32" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B112" s="18" t="n"/>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="18" t="n"/>
+      <c r="I112" s="18" t="n"/>
+      <c r="K112" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C112,$A$5:$A112,"&gt;="&amp;(A112-6),$A$5:$A112,"&lt;="&amp;A112),"")</f>
+        <v/>
+      </c>
+      <c r="L112" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D112,$A$5:$A112,"&gt;="&amp;(A112-6),$A$5:$A112,"&lt;="&amp;A112),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="32" t="n">
+        <v>46358</v>
+      </c>
+      <c r="B113" s="18" t="n"/>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+      <c r="K113" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C113,$A$5:$A113,"&gt;="&amp;(A113-6),$A$5:$A113,"&lt;="&amp;A113),"")</f>
+        <v/>
+      </c>
+      <c r="L113" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D113,$A$5:$A113,"&gt;="&amp;(A113-6),$A$5:$A113,"&lt;="&amp;A113),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="32" t="n">
+        <v>46359</v>
+      </c>
+      <c r="B114" s="18" t="n"/>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="18" t="n"/>
+      <c r="F114" s="18" t="n"/>
+      <c r="G114" s="18" t="n"/>
+      <c r="H114" s="18" t="n"/>
+      <c r="I114" s="18" t="n"/>
+      <c r="K114" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C114,$A$5:$A114,"&gt;="&amp;(A114-6),$A$5:$A114,"&lt;="&amp;A114),"")</f>
+        <v/>
+      </c>
+      <c r="L114" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D114,$A$5:$A114,"&gt;="&amp;(A114-6),$A$5:$A114,"&lt;="&amp;A114),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="32" t="n">
+        <v>46360</v>
+      </c>
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+      <c r="K115" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C115,$A$5:$A115,"&gt;="&amp;(A115-6),$A$5:$A115,"&lt;="&amp;A115),"")</f>
+        <v/>
+      </c>
+      <c r="L115" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D115,$A$5:$A115,"&gt;="&amp;(A115-6),$A$5:$A115,"&lt;="&amp;A115),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="32" t="n">
+        <v>46361</v>
+      </c>
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+      <c r="K116" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C116,$A$5:$A116,"&gt;="&amp;(A116-6),$A$5:$A116,"&lt;="&amp;A116),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D116,$A$5:$A116,"&gt;="&amp;(A116-6),$A$5:$A116,"&lt;="&amp;A116),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="32" t="n">
+        <v>46362</v>
+      </c>
+      <c r="B117" s="18" t="n"/>
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+      <c r="G117" s="18" t="n"/>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+      <c r="K117" s="31">
+        <f>IFERROR(AVERAGEIFS($C$5:$C117,$A$5:$A117,"&gt;="&amp;(A117-6),$A$5:$A117,"&lt;="&amp;A117),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="31">
+        <f>IFERROR(AVERAGEIFS($D$5:$D117,$A$5:$A117,"&gt;="&amp;(A117-6),$A$5:$A117,"&lt;="&amp;A117),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Daily Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Weekly Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Training &amp; Recovery" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Monthly Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Advisory Board Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Monthly Summary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0;(0.0);&quot;—&quot;"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
@@ -31,6 +32,7 @@
     <numFmt numFmtId="169" formatCode="0.0;(0.0);&quot;&quot;"/>
     <numFmt numFmtId="170" formatCode="#,##0;(#,##0);&quot;&quot;"/>
     <numFmt numFmtId="171" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd;;;@"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -129,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -170,6 +172,11 @@
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8305,6 +8312,808 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Advisory Board Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1 = flagged something that day, 0 = approved, nothing to flag. Only real evaluated days get a row — nothing pre-filled ahead of time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Mark Hyman</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Benjamin Bikman</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Rena Malik</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Brad Schoenfeld</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Peter Attia</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Gary Brecka</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Andy Galpin</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Layne Norton</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Andrew Huberman</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>Arthur C. Brooks</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Chip Conley</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="n"/>
+      <c r="L19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="18" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="29" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="18" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="18" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Board Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Updates automatically as rows are added above. "Review" only triggers after 10 real logged days exist — never before.</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Days logged so far:</t>
+        </is>
+      </c>
+      <c r="D39" s="3">
+        <f>COUNT($A$5:$A$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Advisor</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Last Flagged</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Days Silent</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Mark Hyman</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,B$5:B$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="38">
+        <f>IF(B42="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B42)</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C42&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Benjamin Bikman</t>
+        </is>
+      </c>
+      <c r="B43" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,C$5:C$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="38">
+        <f>IF(B43="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B43)</f>
+        <v/>
+      </c>
+      <c r="D43" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C43&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Rena Malik</t>
+        </is>
+      </c>
+      <c r="B44" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,D$5:D$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="38">
+        <f>IF(B44="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B44)</f>
+        <v/>
+      </c>
+      <c r="D44" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C44&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Brad Schoenfeld</t>
+        </is>
+      </c>
+      <c r="B45" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,E$5:E$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="38">
+        <f>IF(B45="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B45)</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C45&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Peter Attia</t>
+        </is>
+      </c>
+      <c r="B46" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,F$5:F$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="38">
+        <f>IF(B46="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B46)</f>
+        <v/>
+      </c>
+      <c r="D46" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C46&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Gary Brecka</t>
+        </is>
+      </c>
+      <c r="B47" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,G$5:G$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="38">
+        <f>IF(B47="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B47)</f>
+        <v/>
+      </c>
+      <c r="D47" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C47&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Andy Galpin</t>
+        </is>
+      </c>
+      <c r="B48" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,H$5:H$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="38">
+        <f>IF(B48="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B48)</f>
+        <v/>
+      </c>
+      <c r="D48" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C48&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Layne Norton</t>
+        </is>
+      </c>
+      <c r="B49" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,I$5:I$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="38">
+        <f>IF(B49="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B49)</f>
+        <v/>
+      </c>
+      <c r="D49" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C49&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Huberman</t>
+        </is>
+      </c>
+      <c r="B50" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,J$5:J$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="38">
+        <f>IF(B50="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B50)</f>
+        <v/>
+      </c>
+      <c r="D50" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C50&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Arthur C. Brooks</t>
+        </is>
+      </c>
+      <c r="B51" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,K$5:K$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="38">
+        <f>IF(B51="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B51)</f>
+        <v/>
+      </c>
+      <c r="D51" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C51&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Chip Conley</t>
+        </is>
+      </c>
+      <c r="B52" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,L$5:L$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="38">
+        <f>IF(B52="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B52)</f>
+        <v/>
+      </c>
+      <c r="D52" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C52&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -8312,7 +8312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8327,6 +8327,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8343,6 +8344,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -8402,6 +8404,11 @@
       <c r="L4" s="15" t="inlineStr">
         <is>
           <t>Chip Conley</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>William Li</t>
         </is>
       </c>
     </row>
@@ -8441,6 +8448,9 @@
       </c>
       <c r="L5" s="36" t="n">
         <v>0</v>
+      </c>
+      <c r="M5" s="36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -8456,6 +8466,7 @@
       <c r="J6" s="18" t="n"/>
       <c r="K6" s="18" t="n"/>
       <c r="L6" s="18" t="n"/>
+      <c r="M6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="n"/>
@@ -8470,6 +8481,7 @@
       <c r="J7" s="18" t="n"/>
       <c r="K7" s="18" t="n"/>
       <c r="L7" s="18" t="n"/>
+      <c r="M7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="n"/>
@@ -8484,6 +8496,7 @@
       <c r="J8" s="18" t="n"/>
       <c r="K8" s="18" t="n"/>
       <c r="L8" s="18" t="n"/>
+      <c r="M8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="n"/>
@@ -8498,6 +8511,7 @@
       <c r="J9" s="18" t="n"/>
       <c r="K9" s="18" t="n"/>
       <c r="L9" s="18" t="n"/>
+      <c r="M9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="n"/>
@@ -8512,6 +8526,7 @@
       <c r="J10" s="18" t="n"/>
       <c r="K10" s="18" t="n"/>
       <c r="L10" s="18" t="n"/>
+      <c r="M10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="n"/>
@@ -8526,6 +8541,7 @@
       <c r="J11" s="18" t="n"/>
       <c r="K11" s="18" t="n"/>
       <c r="L11" s="18" t="n"/>
+      <c r="M11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="n"/>
@@ -8540,6 +8556,7 @@
       <c r="J12" s="18" t="n"/>
       <c r="K12" s="18" t="n"/>
       <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="n"/>
@@ -8554,6 +8571,7 @@
       <c r="J13" s="18" t="n"/>
       <c r="K13" s="18" t="n"/>
       <c r="L13" s="18" t="n"/>
+      <c r="M13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="n"/>
@@ -8568,6 +8586,7 @@
       <c r="J14" s="18" t="n"/>
       <c r="K14" s="18" t="n"/>
       <c r="L14" s="18" t="n"/>
+      <c r="M14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="n"/>
@@ -8582,6 +8601,7 @@
       <c r="J15" s="18" t="n"/>
       <c r="K15" s="18" t="n"/>
       <c r="L15" s="18" t="n"/>
+      <c r="M15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="n"/>
@@ -8596,6 +8616,7 @@
       <c r="J16" s="18" t="n"/>
       <c r="K16" s="18" t="n"/>
       <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="n"/>
@@ -8610,6 +8631,7 @@
       <c r="J17" s="18" t="n"/>
       <c r="K17" s="18" t="n"/>
       <c r="L17" s="18" t="n"/>
+      <c r="M17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="n"/>
@@ -8624,6 +8646,7 @@
       <c r="J18" s="18" t="n"/>
       <c r="K18" s="18" t="n"/>
       <c r="L18" s="18" t="n"/>
+      <c r="M18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="29" t="n"/>
@@ -8638,6 +8661,7 @@
       <c r="J19" s="18" t="n"/>
       <c r="K19" s="18" t="n"/>
       <c r="L19" s="18" t="n"/>
+      <c r="M19" s="18" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="29" t="n"/>
@@ -8652,6 +8676,7 @@
       <c r="J20" s="18" t="n"/>
       <c r="K20" s="18" t="n"/>
       <c r="L20" s="18" t="n"/>
+      <c r="M20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="n"/>
@@ -8666,6 +8691,7 @@
       <c r="J21" s="18" t="n"/>
       <c r="K21" s="18" t="n"/>
       <c r="L21" s="18" t="n"/>
+      <c r="M21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="n"/>
@@ -8680,6 +8706,7 @@
       <c r="J22" s="18" t="n"/>
       <c r="K22" s="18" t="n"/>
       <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="n"/>
@@ -8694,6 +8721,7 @@
       <c r="J23" s="18" t="n"/>
       <c r="K23" s="18" t="n"/>
       <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="n"/>
@@ -8708,6 +8736,7 @@
       <c r="J24" s="18" t="n"/>
       <c r="K24" s="18" t="n"/>
       <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="n"/>
@@ -8722,6 +8751,7 @@
       <c r="J25" s="18" t="n"/>
       <c r="K25" s="18" t="n"/>
       <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="29" t="n"/>
@@ -8736,6 +8766,7 @@
       <c r="J26" s="18" t="n"/>
       <c r="K26" s="18" t="n"/>
       <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="29" t="n"/>
@@ -8750,6 +8781,7 @@
       <c r="J27" s="18" t="n"/>
       <c r="K27" s="18" t="n"/>
       <c r="L27" s="18" t="n"/>
+      <c r="M27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="29" t="n"/>
@@ -8764,6 +8796,7 @@
       <c r="J28" s="18" t="n"/>
       <c r="K28" s="18" t="n"/>
       <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="29" t="n"/>
@@ -8778,6 +8811,7 @@
       <c r="J29" s="18" t="n"/>
       <c r="K29" s="18" t="n"/>
       <c r="L29" s="18" t="n"/>
+      <c r="M29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="29" t="n"/>
@@ -8792,6 +8826,7 @@
       <c r="J30" s="18" t="n"/>
       <c r="K30" s="18" t="n"/>
       <c r="L30" s="18" t="n"/>
+      <c r="M30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="29" t="n"/>
@@ -8806,6 +8841,7 @@
       <c r="J31" s="18" t="n"/>
       <c r="K31" s="18" t="n"/>
       <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="29" t="n"/>
@@ -8820,6 +8856,7 @@
       <c r="J32" s="18" t="n"/>
       <c r="K32" s="18" t="n"/>
       <c r="L32" s="18" t="n"/>
+      <c r="M32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="n"/>
@@ -8834,6 +8871,7 @@
       <c r="J33" s="18" t="n"/>
       <c r="K33" s="18" t="n"/>
       <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="n"/>
@@ -8848,7 +8886,11 @@
       <c r="J34" s="18" t="n"/>
       <c r="K34" s="18" t="n"/>
       <c r="L34" s="18" t="n"/>
-    </row>
+      <c r="M34" s="18" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
@@ -8872,6 +8914,7 @@
         <v/>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
@@ -9100,6 +9143,25 @@
       </c>
       <c r="D52" s="3">
         <f>IF($D$39&lt;10,"Collecting data",IF(C52&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>William Li</t>
+        </is>
+      </c>
+      <c r="B53" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,M$5:M$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="38">
+        <f>IF(B53="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B53)</f>
+        <v/>
+      </c>
+      <c r="D53" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C53&gt;=10,"REVIEW — notify Roberto","Active"))</f>
         <v/>
       </c>
     </row>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -8312,7 +8312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8328,6 +8328,7 @@
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8411,6 +8412,11 @@
           <t>William Li</t>
         </is>
       </c>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>Jessie Inchauspe</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="n">
@@ -8452,6 +8458,7 @@
       <c r="M5" s="36" t="n">
         <v>1</v>
       </c>
+      <c r="N5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="n"/>
@@ -8467,6 +8474,7 @@
       <c r="K6" s="18" t="n"/>
       <c r="L6" s="18" t="n"/>
       <c r="M6" s="18" t="n"/>
+      <c r="N6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="n"/>
@@ -8482,6 +8490,7 @@
       <c r="K7" s="18" t="n"/>
       <c r="L7" s="18" t="n"/>
       <c r="M7" s="18" t="n"/>
+      <c r="N7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="29" t="n"/>
@@ -8497,6 +8506,7 @@
       <c r="K8" s="18" t="n"/>
       <c r="L8" s="18" t="n"/>
       <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="n"/>
@@ -8512,6 +8522,7 @@
       <c r="K9" s="18" t="n"/>
       <c r="L9" s="18" t="n"/>
       <c r="M9" s="18" t="n"/>
+      <c r="N9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="n"/>
@@ -8527,6 +8538,7 @@
       <c r="K10" s="18" t="n"/>
       <c r="L10" s="18" t="n"/>
       <c r="M10" s="18" t="n"/>
+      <c r="N10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="n"/>
@@ -8542,6 +8554,7 @@
       <c r="K11" s="18" t="n"/>
       <c r="L11" s="18" t="n"/>
       <c r="M11" s="18" t="n"/>
+      <c r="N11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="n"/>
@@ -8557,6 +8570,7 @@
       <c r="K12" s="18" t="n"/>
       <c r="L12" s="18" t="n"/>
       <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="29" t="n"/>
@@ -8572,6 +8586,7 @@
       <c r="K13" s="18" t="n"/>
       <c r="L13" s="18" t="n"/>
       <c r="M13" s="18" t="n"/>
+      <c r="N13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="29" t="n"/>
@@ -8587,6 +8602,7 @@
       <c r="K14" s="18" t="n"/>
       <c r="L14" s="18" t="n"/>
       <c r="M14" s="18" t="n"/>
+      <c r="N14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="29" t="n"/>
@@ -8602,6 +8618,7 @@
       <c r="K15" s="18" t="n"/>
       <c r="L15" s="18" t="n"/>
       <c r="M15" s="18" t="n"/>
+      <c r="N15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="29" t="n"/>
@@ -8617,6 +8634,7 @@
       <c r="K16" s="18" t="n"/>
       <c r="L16" s="18" t="n"/>
       <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="29" t="n"/>
@@ -8632,6 +8650,7 @@
       <c r="K17" s="18" t="n"/>
       <c r="L17" s="18" t="n"/>
       <c r="M17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="29" t="n"/>
@@ -8647,6 +8666,7 @@
       <c r="K18" s="18" t="n"/>
       <c r="L18" s="18" t="n"/>
       <c r="M18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="29" t="n"/>
@@ -8662,6 +8682,7 @@
       <c r="K19" s="18" t="n"/>
       <c r="L19" s="18" t="n"/>
       <c r="M19" s="18" t="n"/>
+      <c r="N19" s="18" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="29" t="n"/>
@@ -8677,6 +8698,7 @@
       <c r="K20" s="18" t="n"/>
       <c r="L20" s="18" t="n"/>
       <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="n"/>
@@ -8692,6 +8714,7 @@
       <c r="K21" s="18" t="n"/>
       <c r="L21" s="18" t="n"/>
       <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="29" t="n"/>
@@ -8707,6 +8730,7 @@
       <c r="K22" s="18" t="n"/>
       <c r="L22" s="18" t="n"/>
       <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="29" t="n"/>
@@ -8722,6 +8746,7 @@
       <c r="K23" s="18" t="n"/>
       <c r="L23" s="18" t="n"/>
       <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="29" t="n"/>
@@ -8737,6 +8762,7 @@
       <c r="K24" s="18" t="n"/>
       <c r="L24" s="18" t="n"/>
       <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="29" t="n"/>
@@ -8752,6 +8778,7 @@
       <c r="K25" s="18" t="n"/>
       <c r="L25" s="18" t="n"/>
       <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="29" t="n"/>
@@ -8767,6 +8794,7 @@
       <c r="K26" s="18" t="n"/>
       <c r="L26" s="18" t="n"/>
       <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="29" t="n"/>
@@ -8782,6 +8810,7 @@
       <c r="K27" s="18" t="n"/>
       <c r="L27" s="18" t="n"/>
       <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="29" t="n"/>
@@ -8797,6 +8826,7 @@
       <c r="K28" s="18" t="n"/>
       <c r="L28" s="18" t="n"/>
       <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="29" t="n"/>
@@ -8812,6 +8842,7 @@
       <c r="K29" s="18" t="n"/>
       <c r="L29" s="18" t="n"/>
       <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="29" t="n"/>
@@ -8827,6 +8858,7 @@
       <c r="K30" s="18" t="n"/>
       <c r="L30" s="18" t="n"/>
       <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="29" t="n"/>
@@ -8842,6 +8874,7 @@
       <c r="K31" s="18" t="n"/>
       <c r="L31" s="18" t="n"/>
       <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="29" t="n"/>
@@ -8857,6 +8890,7 @@
       <c r="K32" s="18" t="n"/>
       <c r="L32" s="18" t="n"/>
       <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="29" t="n"/>
@@ -8872,6 +8906,7 @@
       <c r="K33" s="18" t="n"/>
       <c r="L33" s="18" t="n"/>
       <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="29" t="n"/>
@@ -8887,6 +8922,7 @@
       <c r="K34" s="18" t="n"/>
       <c r="L34" s="18" t="n"/>
       <c r="M34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
     </row>
     <row r="35"/>
     <row r="36"/>
@@ -9165,6 +9201,32 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Jessie Inchauspe</t>
+        </is>
+      </c>
+      <c r="B54" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,N$5:N$34,1),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="38">
+        <f>IF(B54="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B54)</f>
+        <v/>
+      </c>
+      <c r="D54" s="3">
+        <f>IF($D$39&lt;10,"Collecting data",IF(C54&gt;=10,"REVIEW — notify Roberto","Active"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -1308,6 +1308,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" hidden="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1315,7 +1316,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>MIN(16,MAX(1,ROUNDUP((TODAY()-DATE(2026,8,16)+1)/7,0)))</f>
+        <f>MIN(16,MAX(1,ROUNDUP((TODAY()-DATE(2026,8,15)+1)/7,0)))</f>
         <v/>
       </c>
       <c r="C4" s="2">
@@ -1342,6 +1343,7 @@
         <v/>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1495,6 +1497,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -1860,7 +1863,7 @@
     </row>
     <row r="2">
       <c r="A2" s="29" t="n">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="B2" s="30" t="n">
         <v>201.4</v>
@@ -1907,7 +1910,7 @@
     </row>
     <row r="3">
       <c r="A3" s="32" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B3" s="30" t="n"/>
       <c r="C3" s="18" t="n"/>
@@ -1936,7 +1939,7 @@
     </row>
     <row r="4">
       <c r="A4" s="32" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B4" s="30" t="n"/>
       <c r="C4" s="18" t="n"/>
@@ -1965,7 +1968,7 @@
     </row>
     <row r="5">
       <c r="A5" s="32" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B5" s="30" t="n"/>
       <c r="C5" s="18" t="n"/>
@@ -1994,7 +1997,7 @@
     </row>
     <row r="6">
       <c r="A6" s="32" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="18" t="n"/>
@@ -2023,7 +2026,7 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B7" s="30" t="n"/>
       <c r="C7" s="18" t="n"/>
@@ -2052,7 +2055,7 @@
     </row>
     <row r="8">
       <c r="A8" s="32" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="18" t="n"/>
@@ -2081,7 +2084,7 @@
     </row>
     <row r="9">
       <c r="A9" s="32" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B9" s="30" t="n"/>
       <c r="C9" s="18" t="n"/>
@@ -2110,7 +2113,7 @@
     </row>
     <row r="10">
       <c r="A10" s="32" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B10" s="30" t="n"/>
       <c r="C10" s="18" t="n"/>
@@ -2139,7 +2142,7 @@
     </row>
     <row r="11">
       <c r="A11" s="32" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B11" s="30" t="n"/>
       <c r="C11" s="18" t="n"/>
@@ -2168,7 +2171,7 @@
     </row>
     <row r="12">
       <c r="A12" s="32" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B12" s="30" t="n"/>
       <c r="C12" s="18" t="n"/>
@@ -2197,7 +2200,7 @@
     </row>
     <row r="13">
       <c r="A13" s="32" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B13" s="30" t="n"/>
       <c r="C13" s="18" t="n"/>
@@ -2226,7 +2229,7 @@
     </row>
     <row r="14">
       <c r="A14" s="32" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B14" s="30" t="n"/>
       <c r="C14" s="18" t="n"/>
@@ -2255,7 +2258,7 @@
     </row>
     <row r="15">
       <c r="A15" s="32" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B15" s="30" t="n"/>
       <c r="C15" s="18" t="n"/>
@@ -2284,7 +2287,7 @@
     </row>
     <row r="16">
       <c r="A16" s="32" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B16" s="30" t="n"/>
       <c r="C16" s="18" t="n"/>
@@ -2313,7 +2316,7 @@
     </row>
     <row r="17">
       <c r="A17" s="32" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B17" s="30" t="n"/>
       <c r="C17" s="18" t="n"/>
@@ -2342,7 +2345,7 @@
     </row>
     <row r="18">
       <c r="A18" s="32" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n"/>
@@ -2371,7 +2374,7 @@
     </row>
     <row r="19">
       <c r="A19" s="32" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B19" s="30" t="n"/>
       <c r="C19" s="18" t="n"/>
@@ -2400,7 +2403,7 @@
     </row>
     <row r="20">
       <c r="A20" s="32" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B20" s="30" t="n"/>
       <c r="C20" s="18" t="n"/>
@@ -2429,7 +2432,7 @@
     </row>
     <row r="21">
       <c r="A21" s="32" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B21" s="30" t="n"/>
       <c r="C21" s="18" t="n"/>
@@ -2458,7 +2461,7 @@
     </row>
     <row r="22">
       <c r="A22" s="32" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B22" s="30" t="n"/>
       <c r="C22" s="18" t="n"/>
@@ -2487,7 +2490,7 @@
     </row>
     <row r="23">
       <c r="A23" s="32" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B23" s="30" t="n"/>
       <c r="C23" s="18" t="n"/>
@@ -2516,7 +2519,7 @@
     </row>
     <row r="24">
       <c r="A24" s="32" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B24" s="30" t="n"/>
       <c r="C24" s="18" t="n"/>
@@ -2545,7 +2548,7 @@
     </row>
     <row r="25">
       <c r="A25" s="32" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B25" s="30" t="n"/>
       <c r="C25" s="18" t="n"/>
@@ -2574,7 +2577,7 @@
     </row>
     <row r="26">
       <c r="A26" s="32" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B26" s="30" t="n"/>
       <c r="C26" s="18" t="n"/>
@@ -2603,7 +2606,7 @@
     </row>
     <row r="27">
       <c r="A27" s="32" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B27" s="30" t="n"/>
       <c r="C27" s="18" t="n"/>
@@ -2632,7 +2635,7 @@
     </row>
     <row r="28">
       <c r="A28" s="32" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B28" s="30" t="n"/>
       <c r="C28" s="18" t="n"/>
@@ -2661,7 +2664,7 @@
     </row>
     <row r="29">
       <c r="A29" s="32" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B29" s="30" t="n"/>
       <c r="C29" s="18" t="n"/>
@@ -2690,7 +2693,7 @@
     </row>
     <row r="30">
       <c r="A30" s="32" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B30" s="30" t="n"/>
       <c r="C30" s="18" t="n"/>
@@ -2719,7 +2722,7 @@
     </row>
     <row r="31">
       <c r="A31" s="32" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B31" s="30" t="n"/>
       <c r="C31" s="18" t="n"/>
@@ -2748,7 +2751,7 @@
     </row>
     <row r="32">
       <c r="A32" s="32" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B32" s="30" t="n"/>
       <c r="C32" s="18" t="n"/>
@@ -2777,7 +2780,7 @@
     </row>
     <row r="33">
       <c r="A33" s="32" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B33" s="30" t="n"/>
       <c r="C33" s="18" t="n"/>
@@ -2806,7 +2809,7 @@
     </row>
     <row r="34">
       <c r="A34" s="32" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B34" s="30" t="n"/>
       <c r="C34" s="18" t="n"/>
@@ -2835,7 +2838,7 @@
     </row>
     <row r="35">
       <c r="A35" s="32" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B35" s="30" t="n"/>
       <c r="C35" s="18" t="n"/>
@@ -2864,7 +2867,7 @@
     </row>
     <row r="36">
       <c r="A36" s="32" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B36" s="30" t="n"/>
       <c r="C36" s="18" t="n"/>
@@ -2893,7 +2896,7 @@
     </row>
     <row r="37">
       <c r="A37" s="32" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B37" s="30" t="n"/>
       <c r="C37" s="18" t="n"/>
@@ -2922,7 +2925,7 @@
     </row>
     <row r="38">
       <c r="A38" s="32" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B38" s="30" t="n"/>
       <c r="C38" s="18" t="n"/>
@@ -2951,7 +2954,7 @@
     </row>
     <row r="39">
       <c r="A39" s="32" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B39" s="30" t="n"/>
       <c r="C39" s="18" t="n"/>
@@ -2980,7 +2983,7 @@
     </row>
     <row r="40">
       <c r="A40" s="32" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B40" s="30" t="n"/>
       <c r="C40" s="18" t="n"/>
@@ -3009,7 +3012,7 @@
     </row>
     <row r="41">
       <c r="A41" s="32" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B41" s="30" t="n"/>
       <c r="C41" s="18" t="n"/>
@@ -3038,7 +3041,7 @@
     </row>
     <row r="42">
       <c r="A42" s="32" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B42" s="30" t="n"/>
       <c r="C42" s="18" t="n"/>
@@ -3067,7 +3070,7 @@
     </row>
     <row r="43">
       <c r="A43" s="32" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B43" s="30" t="n"/>
       <c r="C43" s="18" t="n"/>
@@ -3096,7 +3099,7 @@
     </row>
     <row r="44">
       <c r="A44" s="32" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B44" s="30" t="n"/>
       <c r="C44" s="18" t="n"/>
@@ -3125,7 +3128,7 @@
     </row>
     <row r="45">
       <c r="A45" s="32" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B45" s="30" t="n"/>
       <c r="C45" s="18" t="n"/>
@@ -3154,7 +3157,7 @@
     </row>
     <row r="46">
       <c r="A46" s="32" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="B46" s="30" t="n"/>
       <c r="C46" s="18" t="n"/>
@@ -3183,7 +3186,7 @@
     </row>
     <row r="47">
       <c r="A47" s="32" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B47" s="30" t="n"/>
       <c r="C47" s="18" t="n"/>
@@ -3212,7 +3215,7 @@
     </row>
     <row r="48">
       <c r="A48" s="32" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B48" s="30" t="n"/>
       <c r="C48" s="18" t="n"/>
@@ -3241,7 +3244,7 @@
     </row>
     <row r="49">
       <c r="A49" s="32" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B49" s="30" t="n"/>
       <c r="C49" s="18" t="n"/>
@@ -3270,7 +3273,7 @@
     </row>
     <row r="50">
       <c r="A50" s="32" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B50" s="30" t="n"/>
       <c r="C50" s="18" t="n"/>
@@ -3299,7 +3302,7 @@
     </row>
     <row r="51">
       <c r="A51" s="32" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B51" s="30" t="n"/>
       <c r="C51" s="18" t="n"/>
@@ -3328,7 +3331,7 @@
     </row>
     <row r="52">
       <c r="A52" s="32" t="n">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B52" s="30" t="n"/>
       <c r="C52" s="18" t="n"/>
@@ -3357,7 +3360,7 @@
     </row>
     <row r="53">
       <c r="A53" s="32" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="B53" s="30" t="n"/>
       <c r="C53" s="18" t="n"/>
@@ -3386,7 +3389,7 @@
     </row>
     <row r="54">
       <c r="A54" s="32" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B54" s="30" t="n"/>
       <c r="C54" s="18" t="n"/>
@@ -3415,7 +3418,7 @@
     </row>
     <row r="55">
       <c r="A55" s="32" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B55" s="30" t="n"/>
       <c r="C55" s="18" t="n"/>
@@ -3444,7 +3447,7 @@
     </row>
     <row r="56">
       <c r="A56" s="32" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B56" s="30" t="n"/>
       <c r="C56" s="18" t="n"/>
@@ -3473,7 +3476,7 @@
     </row>
     <row r="57">
       <c r="A57" s="32" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B57" s="30" t="n"/>
       <c r="C57" s="18" t="n"/>
@@ -3502,7 +3505,7 @@
     </row>
     <row r="58">
       <c r="A58" s="32" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B58" s="30" t="n"/>
       <c r="C58" s="18" t="n"/>
@@ -3531,7 +3534,7 @@
     </row>
     <row r="59">
       <c r="A59" s="32" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="B59" s="30" t="n"/>
       <c r="C59" s="18" t="n"/>
@@ -3560,7 +3563,7 @@
     </row>
     <row r="60">
       <c r="A60" s="32" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B60" s="30" t="n"/>
       <c r="C60" s="18" t="n"/>
@@ -3589,7 +3592,7 @@
     </row>
     <row r="61">
       <c r="A61" s="32" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B61" s="30" t="n"/>
       <c r="C61" s="18" t="n"/>
@@ -3618,7 +3621,7 @@
     </row>
     <row r="62">
       <c r="A62" s="32" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B62" s="30" t="n"/>
       <c r="C62" s="18" t="n"/>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="63">
       <c r="A63" s="32" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B63" s="30" t="n"/>
       <c r="C63" s="18" t="n"/>
@@ -3676,7 +3679,7 @@
     </row>
     <row r="64">
       <c r="A64" s="32" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B64" s="30" t="n"/>
       <c r="C64" s="18" t="n"/>
@@ -3705,7 +3708,7 @@
     </row>
     <row r="65">
       <c r="A65" s="32" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B65" s="30" t="n"/>
       <c r="C65" s="18" t="n"/>
@@ -3734,7 +3737,7 @@
     </row>
     <row r="66">
       <c r="A66" s="32" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B66" s="30" t="n"/>
       <c r="C66" s="18" t="n"/>
@@ -3763,7 +3766,7 @@
     </row>
     <row r="67">
       <c r="A67" s="32" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B67" s="30" t="n"/>
       <c r="C67" s="18" t="n"/>
@@ -3792,7 +3795,7 @@
     </row>
     <row r="68">
       <c r="A68" s="32" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B68" s="30" t="n"/>
       <c r="C68" s="18" t="n"/>
@@ -3821,7 +3824,7 @@
     </row>
     <row r="69">
       <c r="A69" s="32" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B69" s="30" t="n"/>
       <c r="C69" s="18" t="n"/>
@@ -3850,7 +3853,7 @@
     </row>
     <row r="70">
       <c r="A70" s="32" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B70" s="30" t="n"/>
       <c r="C70" s="18" t="n"/>
@@ -3879,7 +3882,7 @@
     </row>
     <row r="71">
       <c r="A71" s="32" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B71" s="30" t="n"/>
       <c r="C71" s="18" t="n"/>
@@ -3908,7 +3911,7 @@
     </row>
     <row r="72">
       <c r="A72" s="32" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B72" s="30" t="n"/>
       <c r="C72" s="18" t="n"/>
@@ -3937,7 +3940,7 @@
     </row>
     <row r="73">
       <c r="A73" s="32" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B73" s="30" t="n"/>
       <c r="C73" s="18" t="n"/>
@@ -3966,7 +3969,7 @@
     </row>
     <row r="74">
       <c r="A74" s="32" t="n">
-        <v>46321</v>
+        <v>46320</v>
       </c>
       <c r="B74" s="30" t="n"/>
       <c r="C74" s="18" t="n"/>
@@ -3995,7 +3998,7 @@
     </row>
     <row r="75">
       <c r="A75" s="32" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B75" s="30" t="n"/>
       <c r="C75" s="18" t="n"/>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="76">
       <c r="A76" s="32" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="B76" s="30" t="n"/>
       <c r="C76" s="18" t="n"/>
@@ -4053,7 +4056,7 @@
     </row>
     <row r="77">
       <c r="A77" s="32" t="n">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="B77" s="30" t="n"/>
       <c r="C77" s="18" t="n"/>
@@ -4082,7 +4085,7 @@
     </row>
     <row r="78">
       <c r="A78" s="32" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B78" s="30" t="n"/>
       <c r="C78" s="18" t="n"/>
@@ -4111,7 +4114,7 @@
     </row>
     <row r="79">
       <c r="A79" s="32" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B79" s="30" t="n"/>
       <c r="C79" s="18" t="n"/>
@@ -4140,7 +4143,7 @@
     </row>
     <row r="80">
       <c r="A80" s="32" t="n">
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="B80" s="30" t="n"/>
       <c r="C80" s="18" t="n"/>
@@ -4169,7 +4172,7 @@
     </row>
     <row r="81">
       <c r="A81" s="32" t="n">
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="B81" s="30" t="n"/>
       <c r="C81" s="18" t="n"/>
@@ -4198,7 +4201,7 @@
     </row>
     <row r="82">
       <c r="A82" s="32" t="n">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="B82" s="30" t="n"/>
       <c r="C82" s="18" t="n"/>
@@ -4227,7 +4230,7 @@
     </row>
     <row r="83">
       <c r="A83" s="32" t="n">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="B83" s="30" t="n"/>
       <c r="C83" s="18" t="n"/>
@@ -4256,7 +4259,7 @@
     </row>
     <row r="84">
       <c r="A84" s="32" t="n">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="B84" s="30" t="n"/>
       <c r="C84" s="18" t="n"/>
@@ -4285,7 +4288,7 @@
     </row>
     <row r="85">
       <c r="A85" s="32" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B85" s="30" t="n"/>
       <c r="C85" s="18" t="n"/>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="86">
       <c r="A86" s="32" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B86" s="30" t="n"/>
       <c r="C86" s="18" t="n"/>
@@ -4343,7 +4346,7 @@
     </row>
     <row r="87">
       <c r="A87" s="32" t="n">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="B87" s="30" t="n"/>
       <c r="C87" s="18" t="n"/>
@@ -4372,7 +4375,7 @@
     </row>
     <row r="88">
       <c r="A88" s="32" t="n">
-        <v>46335</v>
+        <v>46334</v>
       </c>
       <c r="B88" s="30" t="n"/>
       <c r="C88" s="18" t="n"/>
@@ -4401,7 +4404,7 @@
     </row>
     <row r="89">
       <c r="A89" s="32" t="n">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="B89" s="30" t="n"/>
       <c r="C89" s="18" t="n"/>
@@ -4430,7 +4433,7 @@
     </row>
     <row r="90">
       <c r="A90" s="32" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B90" s="30" t="n"/>
       <c r="C90" s="18" t="n"/>
@@ -4459,7 +4462,7 @@
     </row>
     <row r="91">
       <c r="A91" s="32" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B91" s="30" t="n"/>
       <c r="C91" s="18" t="n"/>
@@ -4488,7 +4491,7 @@
     </row>
     <row r="92">
       <c r="A92" s="32" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B92" s="30" t="n"/>
       <c r="C92" s="18" t="n"/>
@@ -4517,7 +4520,7 @@
     </row>
     <row r="93">
       <c r="A93" s="32" t="n">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B93" s="30" t="n"/>
       <c r="C93" s="18" t="n"/>
@@ -4546,7 +4549,7 @@
     </row>
     <row r="94">
       <c r="A94" s="32" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B94" s="30" t="n"/>
       <c r="C94" s="18" t="n"/>
@@ -4575,7 +4578,7 @@
     </row>
     <row r="95">
       <c r="A95" s="32" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B95" s="30" t="n"/>
       <c r="C95" s="18" t="n"/>
@@ -4604,7 +4607,7 @@
     </row>
     <row r="96">
       <c r="A96" s="32" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B96" s="30" t="n"/>
       <c r="C96" s="18" t="n"/>
@@ -4633,7 +4636,7 @@
     </row>
     <row r="97">
       <c r="A97" s="32" t="n">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="B97" s="30" t="n"/>
       <c r="C97" s="18" t="n"/>
@@ -4662,7 +4665,7 @@
     </row>
     <row r="98">
       <c r="A98" s="32" t="n">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="B98" s="30" t="n"/>
       <c r="C98" s="18" t="n"/>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="99">
       <c r="A99" s="32" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B99" s="30" t="n"/>
       <c r="C99" s="18" t="n"/>
@@ -4720,7 +4723,7 @@
     </row>
     <row r="100">
       <c r="A100" s="32" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B100" s="30" t="n"/>
       <c r="C100" s="18" t="n"/>
@@ -4749,7 +4752,7 @@
     </row>
     <row r="101">
       <c r="A101" s="32" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="B101" s="30" t="n"/>
       <c r="C101" s="18" t="n"/>
@@ -4778,7 +4781,7 @@
     </row>
     <row r="102">
       <c r="A102" s="32" t="n">
-        <v>46349</v>
+        <v>46348</v>
       </c>
       <c r="B102" s="30" t="n"/>
       <c r="C102" s="18" t="n"/>
@@ -4807,7 +4810,7 @@
     </row>
     <row r="103">
       <c r="A103" s="32" t="n">
-        <v>46350</v>
+        <v>46349</v>
       </c>
       <c r="B103" s="30" t="n"/>
       <c r="C103" s="18" t="n"/>
@@ -4836,7 +4839,7 @@
     </row>
     <row r="104">
       <c r="A104" s="32" t="n">
-        <v>46351</v>
+        <v>46350</v>
       </c>
       <c r="B104" s="30" t="n"/>
       <c r="C104" s="18" t="n"/>
@@ -4865,7 +4868,7 @@
     </row>
     <row r="105">
       <c r="A105" s="32" t="n">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="B105" s="30" t="n"/>
       <c r="C105" s="18" t="n"/>
@@ -4894,7 +4897,7 @@
     </row>
     <row r="106">
       <c r="A106" s="32" t="n">
-        <v>46353</v>
+        <v>46352</v>
       </c>
       <c r="B106" s="30" t="n"/>
       <c r="C106" s="18" t="n"/>
@@ -4923,7 +4926,7 @@
     </row>
     <row r="107">
       <c r="A107" s="32" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B107" s="30" t="n"/>
       <c r="C107" s="18" t="n"/>
@@ -4952,7 +4955,7 @@
     </row>
     <row r="108">
       <c r="A108" s="32" t="n">
-        <v>46355</v>
+        <v>46354</v>
       </c>
       <c r="B108" s="30" t="n"/>
       <c r="C108" s="18" t="n"/>
@@ -4981,7 +4984,7 @@
     </row>
     <row r="109">
       <c r="A109" s="32" t="n">
-        <v>46356</v>
+        <v>46355</v>
       </c>
       <c r="B109" s="30" t="n"/>
       <c r="C109" s="18" t="n"/>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="110">
       <c r="A110" s="32" t="n">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="B110" s="30" t="n"/>
       <c r="C110" s="18" t="n"/>
@@ -5039,7 +5042,7 @@
     </row>
     <row r="111">
       <c r="A111" s="32" t="n">
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="B111" s="30" t="n"/>
       <c r="C111" s="18" t="n"/>
@@ -5068,7 +5071,7 @@
     </row>
     <row r="112">
       <c r="A112" s="32" t="n">
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="B112" s="30" t="n"/>
       <c r="C112" s="18" t="n"/>
@@ -5097,7 +5100,7 @@
     </row>
     <row r="113">
       <c r="A113" s="32" t="n">
-        <v>46360</v>
+        <v>46359</v>
       </c>
       <c r="B113" s="30" t="n"/>
       <c r="C113" s="18" t="n"/>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="114">
       <c r="A114" s="32" t="n">
-        <v>46361</v>
+        <v>46360</v>
       </c>
       <c r="B114" s="30" t="n"/>
       <c r="C114" s="18" t="n"/>
@@ -5227,7 +5230,7 @@
     </row>
     <row r="2">
       <c r="A2" s="32" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B2" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A2+7)),"")</f>
@@ -5256,7 +5259,7 @@
     </row>
     <row r="3">
       <c r="A3" s="32" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B3" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A3+7)),"")</f>
@@ -5293,7 +5296,7 @@
     </row>
     <row r="4">
       <c r="A4" s="32" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B4" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A4+7)),"")</f>
@@ -5330,7 +5333,7 @@
     </row>
     <row r="5">
       <c r="A5" s="32" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B5" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A5+7)),"")</f>
@@ -5367,7 +5370,7 @@
     </row>
     <row r="6">
       <c r="A6" s="32" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B6" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A6+7)),"")</f>
@@ -5404,7 +5407,7 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B7" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A7,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A7+7)),"")</f>
@@ -5441,7 +5444,7 @@
     </row>
     <row r="8">
       <c r="A8" s="32" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B8" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A8,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A8+7)),"")</f>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="9">
       <c r="A9" s="32" t="n">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B9" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A9,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A9+7)),"")</f>
@@ -5515,7 +5518,7 @@
     </row>
     <row r="10">
       <c r="A10" s="32" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="B10" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A10,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A10+7)),"")</f>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="11">
       <c r="A11" s="32" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B11" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A11,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A11+7)),"")</f>
@@ -5589,7 +5592,7 @@
     </row>
     <row r="12">
       <c r="A12" s="32" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B12" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A12,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A12+7)),"")</f>
@@ -5626,7 +5629,7 @@
     </row>
     <row r="13">
       <c r="A13" s="32" t="n">
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="B13" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A13,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A13+7)),"")</f>
@@ -5663,7 +5666,7 @@
     </row>
     <row r="14">
       <c r="A14" s="32" t="n">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="B14" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A14,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A14+7)),"")</f>
@@ -5700,7 +5703,7 @@
     </row>
     <row r="15">
       <c r="A15" s="32" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B15" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A15,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A15+7)),"")</f>
@@ -5737,7 +5740,7 @@
     </row>
     <row r="16">
       <c r="A16" s="32" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="B16" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A16,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A16+7)),"")</f>
@@ -5774,7 +5777,7 @@
     </row>
     <row r="17">
       <c r="A17" s="32" t="n">
-        <v>46355</v>
+        <v>46354</v>
       </c>
       <c r="B17" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A17,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A17+7)),"")</f>
@@ -5851,6 +5854,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -5915,7 +5919,7 @@
     </row>
     <row r="5">
       <c r="A5" s="29" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B5" s="18" t="n"/>
       <c r="C5" s="18" t="n">
@@ -5951,7 +5955,7 @@
     </row>
     <row r="6">
       <c r="A6" s="32" t="n">
-        <v>46251</v>
+        <v>46250</v>
       </c>
       <c r="B6" s="18" t="n"/>
       <c r="C6" s="18" t="n"/>
@@ -5972,7 +5976,7 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B7" s="18" t="n"/>
       <c r="C7" s="18" t="n"/>
@@ -5993,7 +5997,7 @@
     </row>
     <row r="8">
       <c r="A8" s="32" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="18" t="n"/>
       <c r="C8" s="18" t="n"/>
@@ -6014,7 +6018,7 @@
     </row>
     <row r="9">
       <c r="A9" s="32" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="18" t="n"/>
       <c r="C9" s="18" t="n"/>
@@ -6035,7 +6039,7 @@
     </row>
     <row r="10">
       <c r="A10" s="32" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B10" s="18" t="n"/>
       <c r="C10" s="18" t="n"/>
@@ -6056,7 +6060,7 @@
     </row>
     <row r="11">
       <c r="A11" s="32" t="n">
-        <v>46256</v>
+        <v>46255</v>
       </c>
       <c r="B11" s="18" t="n"/>
       <c r="C11" s="18" t="n"/>
@@ -6077,7 +6081,7 @@
     </row>
     <row r="12">
       <c r="A12" s="32" t="n">
-        <v>46257</v>
+        <v>46256</v>
       </c>
       <c r="B12" s="18" t="n"/>
       <c r="C12" s="18" t="n"/>
@@ -6098,7 +6102,7 @@
     </row>
     <row r="13">
       <c r="A13" s="32" t="n">
-        <v>46258</v>
+        <v>46257</v>
       </c>
       <c r="B13" s="18" t="n"/>
       <c r="C13" s="18" t="n"/>
@@ -6119,7 +6123,7 @@
     </row>
     <row r="14">
       <c r="A14" s="32" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="18" t="n"/>
@@ -6140,7 +6144,7 @@
     </row>
     <row r="15">
       <c r="A15" s="32" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B15" s="18" t="n"/>
       <c r="C15" s="18" t="n"/>
@@ -6161,7 +6165,7 @@
     </row>
     <row r="16">
       <c r="A16" s="32" t="n">
-        <v>46261</v>
+        <v>46260</v>
       </c>
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="18" t="n"/>
@@ -6182,7 +6186,7 @@
     </row>
     <row r="17">
       <c r="A17" s="32" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B17" s="18" t="n"/>
       <c r="C17" s="18" t="n"/>
@@ -6203,7 +6207,7 @@
     </row>
     <row r="18">
       <c r="A18" s="32" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B18" s="18" t="n"/>
       <c r="C18" s="18" t="n"/>
@@ -6224,7 +6228,7 @@
     </row>
     <row r="19">
       <c r="A19" s="32" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B19" s="18" t="n"/>
       <c r="C19" s="18" t="n"/>
@@ -6245,7 +6249,7 @@
     </row>
     <row r="20">
       <c r="A20" s="32" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B20" s="18" t="n"/>
       <c r="C20" s="18" t="n"/>
@@ -6266,7 +6270,7 @@
     </row>
     <row r="21">
       <c r="A21" s="32" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B21" s="18" t="n"/>
       <c r="C21" s="18" t="n"/>
@@ -6287,7 +6291,7 @@
     </row>
     <row r="22">
       <c r="A22" s="32" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B22" s="18" t="n"/>
       <c r="C22" s="18" t="n"/>
@@ -6308,7 +6312,7 @@
     </row>
     <row r="23">
       <c r="A23" s="32" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B23" s="18" t="n"/>
       <c r="C23" s="18" t="n"/>
@@ -6329,7 +6333,7 @@
     </row>
     <row r="24">
       <c r="A24" s="32" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B24" s="18" t="n"/>
       <c r="C24" s="18" t="n"/>
@@ -6350,7 +6354,7 @@
     </row>
     <row r="25">
       <c r="A25" s="32" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B25" s="18" t="n"/>
       <c r="C25" s="18" t="n"/>
@@ -6371,7 +6375,7 @@
     </row>
     <row r="26">
       <c r="A26" s="32" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B26" s="18" t="n"/>
       <c r="C26" s="18" t="n"/>
@@ -6392,7 +6396,7 @@
     </row>
     <row r="27">
       <c r="A27" s="32" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B27" s="18" t="n"/>
       <c r="C27" s="18" t="n"/>
@@ -6413,7 +6417,7 @@
     </row>
     <row r="28">
       <c r="A28" s="32" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B28" s="18" t="n"/>
       <c r="C28" s="18" t="n"/>
@@ -6434,7 +6438,7 @@
     </row>
     <row r="29">
       <c r="A29" s="32" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B29" s="18" t="n"/>
       <c r="C29" s="18" t="n"/>
@@ -6455,7 +6459,7 @@
     </row>
     <row r="30">
       <c r="A30" s="32" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B30" s="18" t="n"/>
       <c r="C30" s="18" t="n"/>
@@ -6476,7 +6480,7 @@
     </row>
     <row r="31">
       <c r="A31" s="32" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="18" t="n"/>
       <c r="C31" s="18" t="n"/>
@@ -6497,7 +6501,7 @@
     </row>
     <row r="32">
       <c r="A32" s="32" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="18" t="n"/>
       <c r="C32" s="18" t="n"/>
@@ -6518,7 +6522,7 @@
     </row>
     <row r="33">
       <c r="A33" s="32" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B33" s="18" t="n"/>
       <c r="C33" s="18" t="n"/>
@@ -6539,7 +6543,7 @@
     </row>
     <row r="34">
       <c r="A34" s="32" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B34" s="18" t="n"/>
       <c r="C34" s="18" t="n"/>
@@ -6560,7 +6564,7 @@
     </row>
     <row r="35">
       <c r="A35" s="32" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B35" s="18" t="n"/>
       <c r="C35" s="18" t="n"/>
@@ -6581,7 +6585,7 @@
     </row>
     <row r="36">
       <c r="A36" s="32" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B36" s="18" t="n"/>
       <c r="C36" s="18" t="n"/>
@@ -6602,7 +6606,7 @@
     </row>
     <row r="37">
       <c r="A37" s="32" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B37" s="18" t="n"/>
       <c r="C37" s="18" t="n"/>
@@ -6623,7 +6627,7 @@
     </row>
     <row r="38">
       <c r="A38" s="32" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="18" t="n"/>
@@ -6644,7 +6648,7 @@
     </row>
     <row r="39">
       <c r="A39" s="32" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B39" s="18" t="n"/>
       <c r="C39" s="18" t="n"/>
@@ -6665,7 +6669,7 @@
     </row>
     <row r="40">
       <c r="A40" s="32" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B40" s="18" t="n"/>
       <c r="C40" s="18" t="n"/>
@@ -6686,7 +6690,7 @@
     </row>
     <row r="41">
       <c r="A41" s="32" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B41" s="18" t="n"/>
       <c r="C41" s="18" t="n"/>
@@ -6707,7 +6711,7 @@
     </row>
     <row r="42">
       <c r="A42" s="32" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B42" s="18" t="n"/>
       <c r="C42" s="18" t="n"/>
@@ -6728,7 +6732,7 @@
     </row>
     <row r="43">
       <c r="A43" s="32" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B43" s="18" t="n"/>
       <c r="C43" s="18" t="n"/>
@@ -6749,7 +6753,7 @@
     </row>
     <row r="44">
       <c r="A44" s="32" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B44" s="18" t="n"/>
       <c r="C44" s="18" t="n"/>
@@ -6770,7 +6774,7 @@
     </row>
     <row r="45">
       <c r="A45" s="32" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B45" s="18" t="n"/>
       <c r="C45" s="18" t="n"/>
@@ -6791,7 +6795,7 @@
     </row>
     <row r="46">
       <c r="A46" s="32" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B46" s="18" t="n"/>
       <c r="C46" s="18" t="n"/>
@@ -6812,7 +6816,7 @@
     </row>
     <row r="47">
       <c r="A47" s="32" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B47" s="18" t="n"/>
       <c r="C47" s="18" t="n"/>
@@ -6833,7 +6837,7 @@
     </row>
     <row r="48">
       <c r="A48" s="32" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="B48" s="18" t="n"/>
       <c r="C48" s="18" t="n"/>
@@ -6854,7 +6858,7 @@
     </row>
     <row r="49">
       <c r="A49" s="32" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B49" s="18" t="n"/>
       <c r="C49" s="18" t="n"/>
@@ -6875,7 +6879,7 @@
     </row>
     <row r="50">
       <c r="A50" s="32" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B50" s="18" t="n"/>
       <c r="C50" s="18" t="n"/>
@@ -6896,7 +6900,7 @@
     </row>
     <row r="51">
       <c r="A51" s="32" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="B51" s="18" t="n"/>
       <c r="C51" s="18" t="n"/>
@@ -6917,7 +6921,7 @@
     </row>
     <row r="52">
       <c r="A52" s="32" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B52" s="18" t="n"/>
       <c r="C52" s="18" t="n"/>
@@ -6938,7 +6942,7 @@
     </row>
     <row r="53">
       <c r="A53" s="32" t="n">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="B53" s="18" t="n"/>
       <c r="C53" s="18" t="n"/>
@@ -6959,7 +6963,7 @@
     </row>
     <row r="54">
       <c r="A54" s="32" t="n">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B54" s="18" t="n"/>
       <c r="C54" s="18" t="n"/>
@@ -6980,7 +6984,7 @@
     </row>
     <row r="55">
       <c r="A55" s="32" t="n">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="B55" s="18" t="n"/>
       <c r="C55" s="18" t="n"/>
@@ -7001,7 +7005,7 @@
     </row>
     <row r="56">
       <c r="A56" s="32" t="n">
-        <v>46301</v>
+        <v>46300</v>
       </c>
       <c r="B56" s="18" t="n"/>
       <c r="C56" s="18" t="n"/>
@@ -7022,7 +7026,7 @@
     </row>
     <row r="57">
       <c r="A57" s="32" t="n">
-        <v>46302</v>
+        <v>46301</v>
       </c>
       <c r="B57" s="18" t="n"/>
       <c r="C57" s="18" t="n"/>
@@ -7043,7 +7047,7 @@
     </row>
     <row r="58">
       <c r="A58" s="32" t="n">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="B58" s="18" t="n"/>
       <c r="C58" s="18" t="n"/>
@@ -7064,7 +7068,7 @@
     </row>
     <row r="59">
       <c r="A59" s="32" t="n">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="B59" s="18" t="n"/>
       <c r="C59" s="18" t="n"/>
@@ -7085,7 +7089,7 @@
     </row>
     <row r="60">
       <c r="A60" s="32" t="n">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="B60" s="18" t="n"/>
       <c r="C60" s="18" t="n"/>
@@ -7106,7 +7110,7 @@
     </row>
     <row r="61">
       <c r="A61" s="32" t="n">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="B61" s="18" t="n"/>
       <c r="C61" s="18" t="n"/>
@@ -7127,7 +7131,7 @@
     </row>
     <row r="62">
       <c r="A62" s="32" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B62" s="18" t="n"/>
       <c r="C62" s="18" t="n"/>
@@ -7148,7 +7152,7 @@
     </row>
     <row r="63">
       <c r="A63" s="32" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B63" s="18" t="n"/>
       <c r="C63" s="18" t="n"/>
@@ -7169,7 +7173,7 @@
     </row>
     <row r="64">
       <c r="A64" s="32" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B64" s="18" t="n"/>
       <c r="C64" s="18" t="n"/>
@@ -7190,7 +7194,7 @@
     </row>
     <row r="65">
       <c r="A65" s="32" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B65" s="18" t="n"/>
       <c r="C65" s="18" t="n"/>
@@ -7211,7 +7215,7 @@
     </row>
     <row r="66">
       <c r="A66" s="32" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B66" s="18" t="n"/>
       <c r="C66" s="18" t="n"/>
@@ -7232,7 +7236,7 @@
     </row>
     <row r="67">
       <c r="A67" s="32" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B67" s="18" t="n"/>
       <c r="C67" s="18" t="n"/>
@@ -7253,7 +7257,7 @@
     </row>
     <row r="68">
       <c r="A68" s="32" t="n">
-        <v>46313</v>
+        <v>46312</v>
       </c>
       <c r="B68" s="18" t="n"/>
       <c r="C68" s="18" t="n"/>
@@ -7274,7 +7278,7 @@
     </row>
     <row r="69">
       <c r="A69" s="32" t="n">
-        <v>46314</v>
+        <v>46313</v>
       </c>
       <c r="B69" s="18" t="n"/>
       <c r="C69" s="18" t="n"/>
@@ -7295,7 +7299,7 @@
     </row>
     <row r="70">
       <c r="A70" s="32" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B70" s="18" t="n"/>
       <c r="C70" s="18" t="n"/>
@@ -7316,7 +7320,7 @@
     </row>
     <row r="71">
       <c r="A71" s="32" t="n">
-        <v>46316</v>
+        <v>46315</v>
       </c>
       <c r="B71" s="18" t="n"/>
       <c r="C71" s="18" t="n"/>
@@ -7337,7 +7341,7 @@
     </row>
     <row r="72">
       <c r="A72" s="32" t="n">
-        <v>46317</v>
+        <v>46316</v>
       </c>
       <c r="B72" s="18" t="n"/>
       <c r="C72" s="18" t="n"/>
@@ -7358,7 +7362,7 @@
     </row>
     <row r="73">
       <c r="A73" s="32" t="n">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="B73" s="18" t="n"/>
       <c r="C73" s="18" t="n"/>
@@ -7379,7 +7383,7 @@
     </row>
     <row r="74">
       <c r="A74" s="32" t="n">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="B74" s="18" t="n"/>
       <c r="C74" s="18" t="n"/>
@@ -7400,7 +7404,7 @@
     </row>
     <row r="75">
       <c r="A75" s="32" t="n">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="B75" s="18" t="n"/>
       <c r="C75" s="18" t="n"/>
@@ -7421,7 +7425,7 @@
     </row>
     <row r="76">
       <c r="A76" s="32" t="n">
-        <v>46321</v>
+        <v>46320</v>
       </c>
       <c r="B76" s="18" t="n"/>
       <c r="C76" s="18" t="n"/>
@@ -7442,7 +7446,7 @@
     </row>
     <row r="77">
       <c r="A77" s="32" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="B77" s="18" t="n"/>
       <c r="C77" s="18" t="n"/>
@@ -7463,7 +7467,7 @@
     </row>
     <row r="78">
       <c r="A78" s="32" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="B78" s="18" t="n"/>
       <c r="C78" s="18" t="n"/>
@@ -7484,7 +7488,7 @@
     </row>
     <row r="79">
       <c r="A79" s="32" t="n">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="B79" s="18" t="n"/>
       <c r="C79" s="18" t="n"/>
@@ -7505,7 +7509,7 @@
     </row>
     <row r="80">
       <c r="A80" s="32" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="B80" s="18" t="n"/>
       <c r="C80" s="18" t="n"/>
@@ -7526,7 +7530,7 @@
     </row>
     <row r="81">
       <c r="A81" s="32" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="B81" s="18" t="n"/>
       <c r="C81" s="18" t="n"/>
@@ -7547,7 +7551,7 @@
     </row>
     <row r="82">
       <c r="A82" s="32" t="n">
-        <v>46327</v>
+        <v>46326</v>
       </c>
       <c r="B82" s="18" t="n"/>
       <c r="C82" s="18" t="n"/>
@@ -7568,7 +7572,7 @@
     </row>
     <row r="83">
       <c r="A83" s="32" t="n">
-        <v>46328</v>
+        <v>46327</v>
       </c>
       <c r="B83" s="18" t="n"/>
       <c r="C83" s="18" t="n"/>
@@ -7589,7 +7593,7 @@
     </row>
     <row r="84">
       <c r="A84" s="32" t="n">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="B84" s="18" t="n"/>
       <c r="C84" s="18" t="n"/>
@@ -7610,7 +7614,7 @@
     </row>
     <row r="85">
       <c r="A85" s="32" t="n">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="B85" s="18" t="n"/>
       <c r="C85" s="18" t="n"/>
@@ -7631,7 +7635,7 @@
     </row>
     <row r="86">
       <c r="A86" s="32" t="n">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="B86" s="18" t="n"/>
       <c r="C86" s="18" t="n"/>
@@ -7652,7 +7656,7 @@
     </row>
     <row r="87">
       <c r="A87" s="32" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="B87" s="18" t="n"/>
       <c r="C87" s="18" t="n"/>
@@ -7673,7 +7677,7 @@
     </row>
     <row r="88">
       <c r="A88" s="32" t="n">
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="B88" s="18" t="n"/>
       <c r="C88" s="18" t="n"/>
@@ -7694,7 +7698,7 @@
     </row>
     <row r="89">
       <c r="A89" s="32" t="n">
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="B89" s="18" t="n"/>
       <c r="C89" s="18" t="n"/>
@@ -7715,7 +7719,7 @@
     </row>
     <row r="90">
       <c r="A90" s="32" t="n">
-        <v>46335</v>
+        <v>46334</v>
       </c>
       <c r="B90" s="18" t="n"/>
       <c r="C90" s="18" t="n"/>
@@ -7736,7 +7740,7 @@
     </row>
     <row r="91">
       <c r="A91" s="32" t="n">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="B91" s="18" t="n"/>
       <c r="C91" s="18" t="n"/>
@@ -7757,7 +7761,7 @@
     </row>
     <row r="92">
       <c r="A92" s="32" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="B92" s="18" t="n"/>
       <c r="C92" s="18" t="n"/>
@@ -7778,7 +7782,7 @@
     </row>
     <row r="93">
       <c r="A93" s="32" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="B93" s="18" t="n"/>
       <c r="C93" s="18" t="n"/>
@@ -7799,7 +7803,7 @@
     </row>
     <row r="94">
       <c r="A94" s="32" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="B94" s="18" t="n"/>
       <c r="C94" s="18" t="n"/>
@@ -7820,7 +7824,7 @@
     </row>
     <row r="95">
       <c r="A95" s="32" t="n">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="B95" s="18" t="n"/>
       <c r="C95" s="18" t="n"/>
@@ -7841,7 +7845,7 @@
     </row>
     <row r="96">
       <c r="A96" s="32" t="n">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="B96" s="18" t="n"/>
       <c r="C96" s="18" t="n"/>
@@ -7862,7 +7866,7 @@
     </row>
     <row r="97">
       <c r="A97" s="32" t="n">
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="B97" s="18" t="n"/>
       <c r="C97" s="18" t="n"/>
@@ -7883,7 +7887,7 @@
     </row>
     <row r="98">
       <c r="A98" s="32" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="B98" s="18" t="n"/>
       <c r="C98" s="18" t="n"/>
@@ -7904,7 +7908,7 @@
     </row>
     <row r="99">
       <c r="A99" s="32" t="n">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="B99" s="18" t="n"/>
       <c r="C99" s="18" t="n"/>
@@ -7925,7 +7929,7 @@
     </row>
     <row r="100">
       <c r="A100" s="32" t="n">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="B100" s="18" t="n"/>
       <c r="C100" s="18" t="n"/>
@@ -7946,7 +7950,7 @@
     </row>
     <row r="101">
       <c r="A101" s="32" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="B101" s="18" t="n"/>
       <c r="C101" s="18" t="n"/>
@@ -7967,7 +7971,7 @@
     </row>
     <row r="102">
       <c r="A102" s="32" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="B102" s="18" t="n"/>
       <c r="C102" s="18" t="n"/>
@@ -7988,7 +7992,7 @@
     </row>
     <row r="103">
       <c r="A103" s="32" t="n">
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="B103" s="18" t="n"/>
       <c r="C103" s="18" t="n"/>
@@ -8009,7 +8013,7 @@
     </row>
     <row r="104">
       <c r="A104" s="32" t="n">
-        <v>46349</v>
+        <v>46348</v>
       </c>
       <c r="B104" s="18" t="n"/>
       <c r="C104" s="18" t="n"/>
@@ -8030,7 +8034,7 @@
     </row>
     <row r="105">
       <c r="A105" s="32" t="n">
-        <v>46350</v>
+        <v>46349</v>
       </c>
       <c r="B105" s="18" t="n"/>
       <c r="C105" s="18" t="n"/>
@@ -8051,7 +8055,7 @@
     </row>
     <row r="106">
       <c r="A106" s="32" t="n">
-        <v>46351</v>
+        <v>46350</v>
       </c>
       <c r="B106" s="18" t="n"/>
       <c r="C106" s="18" t="n"/>
@@ -8072,7 +8076,7 @@
     </row>
     <row r="107">
       <c r="A107" s="32" t="n">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="B107" s="18" t="n"/>
       <c r="C107" s="18" t="n"/>
@@ -8093,7 +8097,7 @@
     </row>
     <row r="108">
       <c r="A108" s="32" t="n">
-        <v>46353</v>
+        <v>46352</v>
       </c>
       <c r="B108" s="18" t="n"/>
       <c r="C108" s="18" t="n"/>
@@ -8114,7 +8118,7 @@
     </row>
     <row r="109">
       <c r="A109" s="32" t="n">
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="B109" s="18" t="n"/>
       <c r="C109" s="18" t="n"/>
@@ -8135,7 +8139,7 @@
     </row>
     <row r="110">
       <c r="A110" s="32" t="n">
-        <v>46355</v>
+        <v>46354</v>
       </c>
       <c r="B110" s="18" t="n"/>
       <c r="C110" s="18" t="n"/>
@@ -8156,7 +8160,7 @@
     </row>
     <row r="111">
       <c r="A111" s="32" t="n">
-        <v>46356</v>
+        <v>46355</v>
       </c>
       <c r="B111" s="18" t="n"/>
       <c r="C111" s="18" t="n"/>
@@ -8177,7 +8181,7 @@
     </row>
     <row r="112">
       <c r="A112" s="32" t="n">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="B112" s="18" t="n"/>
       <c r="C112" s="18" t="n"/>
@@ -8198,7 +8202,7 @@
     </row>
     <row r="113">
       <c r="A113" s="32" t="n">
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="B113" s="18" t="n"/>
       <c r="C113" s="18" t="n"/>
@@ -8219,7 +8223,7 @@
     </row>
     <row r="114">
       <c r="A114" s="32" t="n">
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="B114" s="18" t="n"/>
       <c r="C114" s="18" t="n"/>
@@ -8240,7 +8244,7 @@
     </row>
     <row r="115">
       <c r="A115" s="32" t="n">
-        <v>46360</v>
+        <v>46359</v>
       </c>
       <c r="B115" s="18" t="n"/>
       <c r="C115" s="18" t="n"/>
@@ -8261,7 +8265,7 @@
     </row>
     <row r="116">
       <c r="A116" s="32" t="n">
-        <v>46361</v>
+        <v>46360</v>
       </c>
       <c r="B116" s="18" t="n"/>
       <c r="C116" s="18" t="n"/>
@@ -8282,7 +8286,7 @@
     </row>
     <row r="117">
       <c r="A117" s="32" t="n">
-        <v>46362</v>
+        <v>46361</v>
       </c>
       <c r="B117" s="18" t="n"/>
       <c r="C117" s="18" t="n"/>
@@ -8312,7 +8316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8420,7 +8424,7 @@
     </row>
     <row r="5">
       <c r="A5" s="29" t="n">
-        <v>46250</v>
+        <v>46249</v>
       </c>
       <c r="B5" s="36" t="n">
         <v>1</v>
@@ -9220,13 +9224,6 @@
         <v/>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -1308,7 +1308,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" hidden="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1343,7 +1342,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1497,7 +1495,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -1942,13 +1939,29 @@
         <v>46250</v>
       </c>
       <c r="B4" s="30" t="n"/>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" s="18" t="n"/>
-      <c r="H4" s="18" t="n"/>
-      <c r="I4" s="18" t="n"/>
+      <c r="C4" s="18" t="n">
+        <v>845</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>78</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="18" t="inlineStr">
+        <is>
+          <t>Latte; 2 hard-boiled eggs+smoked salmon+mango; whole branzino Mediterranean+broccoli. Travel day — light overall, protein/fiber well under target.</t>
+        </is>
+      </c>
       <c r="J4" s="31">
         <f>IF(C4="","",C4-Targets!$B$12)</f>
         <v/>
@@ -5854,7 +5867,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -8349,7 +8361,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -8465,20 +8476,48 @@
       <c r="N5" s="18" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="n"/>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="18" t="n"/>
-      <c r="J6" s="18" t="n"/>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="18" t="n"/>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="18" t="n"/>
+      <c r="A6" s="29" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="n"/>
@@ -8928,9 +8967,6 @@
       <c r="M34" s="18" t="n"/>
       <c r="N34" s="18" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
@@ -8954,7 +8990,6 @@
         <v/>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -1984,13 +1984,29 @@
         <v>46251</v>
       </c>
       <c r="B5" s="30" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="18" t="n"/>
+      <c r="C5" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>125</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>69</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>Late lunch 3:30p: Cuban lentejas (60%), grilled chicken w/ cream sauce, maduros. Dinner: 6oz filet mignon medium rare, grilled veg+broccoli.</t>
+        </is>
+      </c>
       <c r="J5" s="31">
         <f>IF(C5="","",C5-Targets!$B$12)</f>
         <v/>
@@ -8520,20 +8536,48 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="n"/>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="18" t="n"/>
+      <c r="A7" s="29" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Weekly Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Training &amp; Recovery" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Advisory Board Log" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Monthly Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Bloodwork" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Monthly Summary" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -131,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +178,11 @@
     </xf>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5852,13 +5858,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -5867,6 +5873,7 @@
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5944,6 +5951,11 @@
           <t>7-day Avg HRV</t>
         </is>
       </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="n">
@@ -5980,6 +5992,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D5,$A$5:$A5,"&gt;="&amp;(A5-6),$A$5:$A5,"&lt;="&amp;A5),"")</f>
         <v/>
       </c>
+      <c r="M5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="32" t="n">
@@ -6001,6 +6014,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D6,$A$5:$A6,"&gt;="&amp;(A6-6),$A$5:$A6,"&lt;="&amp;A6),"")</f>
         <v/>
       </c>
+      <c r="M6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="32" t="n">
@@ -6022,6 +6036,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D7,$A$5:$A7,"&gt;="&amp;(A7-6),$A$5:$A7,"&lt;="&amp;A7),"")</f>
         <v/>
       </c>
+      <c r="M7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="32" t="n">
@@ -6043,6 +6058,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D8,$A$5:$A8,"&gt;="&amp;(A8-6),$A$5:$A8,"&lt;="&amp;A8),"")</f>
         <v/>
       </c>
+      <c r="M8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="32" t="n">
@@ -6064,6 +6080,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D9,$A$5:$A9,"&gt;="&amp;(A9-6),$A$5:$A9,"&lt;="&amp;A9),"")</f>
         <v/>
       </c>
+      <c r="M9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="32" t="n">
@@ -6085,6 +6102,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D10,$A$5:$A10,"&gt;="&amp;(A10-6),$A$5:$A10,"&lt;="&amp;A10),"")</f>
         <v/>
       </c>
+      <c r="M10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="32" t="n">
@@ -6106,6 +6124,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D11,$A$5:$A11,"&gt;="&amp;(A11-6),$A$5:$A11,"&lt;="&amp;A11),"")</f>
         <v/>
       </c>
+      <c r="M11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="32" t="n">
@@ -6127,6 +6146,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D12,$A$5:$A12,"&gt;="&amp;(A12-6),$A$5:$A12,"&lt;="&amp;A12),"")</f>
         <v/>
       </c>
+      <c r="M12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="32" t="n">
@@ -6148,6 +6168,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D13,$A$5:$A13,"&gt;="&amp;(A13-6),$A$5:$A13,"&lt;="&amp;A13),"")</f>
         <v/>
       </c>
+      <c r="M13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="32" t="n">
@@ -6169,6 +6190,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D14,$A$5:$A14,"&gt;="&amp;(A14-6),$A$5:$A14,"&lt;="&amp;A14),"")</f>
         <v/>
       </c>
+      <c r="M14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="32" t="n">
@@ -6190,6 +6212,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D15,$A$5:$A15,"&gt;="&amp;(A15-6),$A$5:$A15,"&lt;="&amp;A15),"")</f>
         <v/>
       </c>
+      <c r="M15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="32" t="n">
@@ -6211,6 +6234,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D16,$A$5:$A16,"&gt;="&amp;(A16-6),$A$5:$A16,"&lt;="&amp;A16),"")</f>
         <v/>
       </c>
+      <c r="M16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="32" t="n">
@@ -6232,6 +6256,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D17,$A$5:$A17,"&gt;="&amp;(A17-6),$A$5:$A17,"&lt;="&amp;A17),"")</f>
         <v/>
       </c>
+      <c r="M17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="32" t="n">
@@ -6253,6 +6278,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D18,$A$5:$A18,"&gt;="&amp;(A18-6),$A$5:$A18,"&lt;="&amp;A18),"")</f>
         <v/>
       </c>
+      <c r="M18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="32" t="n">
@@ -6274,6 +6300,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D19,$A$5:$A19,"&gt;="&amp;(A19-6),$A$5:$A19,"&lt;="&amp;A19),"")</f>
         <v/>
       </c>
+      <c r="M19" s="18" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="32" t="n">
@@ -6295,6 +6322,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D20,$A$5:$A20,"&gt;="&amp;(A20-6),$A$5:$A20,"&lt;="&amp;A20),"")</f>
         <v/>
       </c>
+      <c r="M20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="32" t="n">
@@ -6316,6 +6344,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D21,$A$5:$A21,"&gt;="&amp;(A21-6),$A$5:$A21,"&lt;="&amp;A21),"")</f>
         <v/>
       </c>
+      <c r="M21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="32" t="n">
@@ -6337,6 +6366,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D22,$A$5:$A22,"&gt;="&amp;(A22-6),$A$5:$A22,"&lt;="&amp;A22),"")</f>
         <v/>
       </c>
+      <c r="M22" s="18" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="32" t="n">
@@ -6358,6 +6388,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D23,$A$5:$A23,"&gt;="&amp;(A23-6),$A$5:$A23,"&lt;="&amp;A23),"")</f>
         <v/>
       </c>
+      <c r="M23" s="18" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="32" t="n">
@@ -6379,6 +6410,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D24,$A$5:$A24,"&gt;="&amp;(A24-6),$A$5:$A24,"&lt;="&amp;A24),"")</f>
         <v/>
       </c>
+      <c r="M24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="32" t="n">
@@ -6400,6 +6432,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D25,$A$5:$A25,"&gt;="&amp;(A25-6),$A$5:$A25,"&lt;="&amp;A25),"")</f>
         <v/>
       </c>
+      <c r="M25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="32" t="n">
@@ -6421,6 +6454,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D26,$A$5:$A26,"&gt;="&amp;(A26-6),$A$5:$A26,"&lt;="&amp;A26),"")</f>
         <v/>
       </c>
+      <c r="M26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="32" t="n">
@@ -6442,6 +6476,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D27,$A$5:$A27,"&gt;="&amp;(A27-6),$A$5:$A27,"&lt;="&amp;A27),"")</f>
         <v/>
       </c>
+      <c r="M27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="32" t="n">
@@ -6463,6 +6498,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D28,$A$5:$A28,"&gt;="&amp;(A28-6),$A$5:$A28,"&lt;="&amp;A28),"")</f>
         <v/>
       </c>
+      <c r="M28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="32" t="n">
@@ -6484,6 +6520,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D29,$A$5:$A29,"&gt;="&amp;(A29-6),$A$5:$A29,"&lt;="&amp;A29),"")</f>
         <v/>
       </c>
+      <c r="M29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="32" t="n">
@@ -6505,6 +6542,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D30,$A$5:$A30,"&gt;="&amp;(A30-6),$A$5:$A30,"&lt;="&amp;A30),"")</f>
         <v/>
       </c>
+      <c r="M30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="32" t="n">
@@ -6526,6 +6564,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D31,$A$5:$A31,"&gt;="&amp;(A31-6),$A$5:$A31,"&lt;="&amp;A31),"")</f>
         <v/>
       </c>
+      <c r="M31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="32" t="n">
@@ -6547,6 +6586,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D32,$A$5:$A32,"&gt;="&amp;(A32-6),$A$5:$A32,"&lt;="&amp;A32),"")</f>
         <v/>
       </c>
+      <c r="M32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="32" t="n">
@@ -6568,6 +6608,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D33,$A$5:$A33,"&gt;="&amp;(A33-6),$A$5:$A33,"&lt;="&amp;A33),"")</f>
         <v/>
       </c>
+      <c r="M33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="32" t="n">
@@ -6589,6 +6630,7 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D34,$A$5:$A34,"&gt;="&amp;(A34-6),$A$5:$A34,"&lt;="&amp;A34),"")</f>
         <v/>
       </c>
+      <c r="M34" s="18" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="32" t="n">
@@ -6654,8 +6696,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n">
-        <v>46282</v>
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>Field Status</t>
+        </is>
       </c>
       <c r="B38" s="18" t="n"/>
       <c r="C38" s="18" t="n"/>
@@ -6675,8 +6719,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="n">
-        <v>46283</v>
+      <c r="A39" s="40" t="inlineStr">
+        <is>
+          <t>Supplementary fields only — core nutrition/weight logging is never questioned. A field silent 10+ days flips to "REVIEW", which means: ask Roberto whether to keep watching for it or retire it from the dashboard.</t>
+        </is>
       </c>
       <c r="B39" s="18" t="n"/>
       <c r="C39" s="18" t="n"/>
@@ -6717,12 +6763,26 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>Last Logged</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Days Idle</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
       <c r="E41" s="18" t="n"/>
       <c r="F41" s="18" t="n"/>
       <c r="G41" s="18" t="n"/>
@@ -6738,12 +6798,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="18" t="n"/>
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>Recovery Reading (ring)</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,$C$5:$C$34,"&lt;&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="38">
+        <f>IF(B42="","",TODAY()-B42)</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>IF(B42="","no data yet",IF(C42&gt;=10,"REVIEW — ask Roberto","Active"))</f>
+        <v/>
+      </c>
       <c r="E42" s="18" t="n"/>
       <c r="F42" s="18" t="n"/>
       <c r="G42" s="18" t="n"/>
@@ -6759,12 +6830,23 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="B43" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,$M$5:$M$34,"&lt;&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="38">
+        <f>IF(B43="","",TODAY()-B43)</f>
+        <v/>
+      </c>
+      <c r="D43" s="3">
+        <f>IF(B43="","no data yet",IF(C43&gt;=10,"REVIEW — ask Roberto","Active"))</f>
+        <v/>
+      </c>
       <c r="E43" s="18" t="n"/>
       <c r="F43" s="18" t="n"/>
       <c r="G43" s="18" t="n"/>
@@ -6780,12 +6862,23 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Tonal Training</t>
+        </is>
+      </c>
+      <c r="B44" s="37">
+        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,$H$5:$H$34,"&lt;&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="38">
+        <f>IF(B44="","",TODAY()-B44)</f>
+        <v/>
+      </c>
+      <c r="D44" s="3">
+        <f>IF(B44="","no data yet",IF(C44&gt;=10,"REVIEW — ask Roberto","Active"))</f>
+        <v/>
+      </c>
       <c r="E44" s="18" t="n"/>
       <c r="F44" s="18" t="n"/>
       <c r="G44" s="18" t="n"/>
@@ -6801,12 +6894,23 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Bloodwork</t>
+        </is>
+      </c>
+      <c r="B45" s="37">
+        <f>IFERROR(IF(MAX(Bloodwork!$A$5:$A$16)=0,"",MAX(Bloodwork!$A$5:$A$16)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="38">
+        <f>IF(B45="","",TODAY()-B45)</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>IF(B45="","no data yet",IF(C45&gt;=10,"REVIEW — ask Roberto","Active"))</f>
+        <v/>
+      </c>
       <c r="E45" s="18" t="n"/>
       <c r="F45" s="18" t="n"/>
       <c r="G45" s="18" t="n"/>
@@ -9314,6 +9418,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bloodwork</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>One row per panel drawn. Blank until real results land — nothing pre-filled or estimated. First panel expected ~2026-08-26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Date Drawn</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Total Chol</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>LDL</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>HDL</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Triglycerides</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>ApoB</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>hs-CRP</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>A1C</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Fasting Glucose</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Vitamin D</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>Testosterone</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" t="n"/>
+      <c r="F5" s="18" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="18" t="n"/>
+      <c r="I5" s="18" t="n"/>
+      <c r="J5" s="18" t="n"/>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="18" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="18" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="18" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="18" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="18" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -1314,6 +1314,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" hidden="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1321,7 +1322,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>MIN(16,MAX(1,ROUNDUP((TODAY()-DATE(2026,8,15)+1)/7,0)))</f>
+        <f>MIN(16,MAX(1,ROUNDUP((TODAY()-DATE(2026,8,9)+1)/7,0)))</f>
         <v/>
       </c>
       <c r="C4" s="2">
@@ -1348,6 +1349,7 @@
         <v/>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1501,6 +1503,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -5265,7 +5268,7 @@
     </row>
     <row r="2">
       <c r="A2" s="32" t="n">
-        <v>46249</v>
+        <v>46243</v>
       </c>
       <c r="B2" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A2,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A2+7)),"")</f>
@@ -5294,7 +5297,7 @@
     </row>
     <row r="3">
       <c r="A3" s="32" t="n">
-        <v>46256</v>
+        <v>46250</v>
       </c>
       <c r="B3" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A3,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A3+7)),"")</f>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="4">
       <c r="A4" s="32" t="n">
-        <v>46263</v>
+        <v>46257</v>
       </c>
       <c r="B4" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A4,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A4+7)),"")</f>
@@ -5368,7 +5371,7 @@
     </row>
     <row r="5">
       <c r="A5" s="32" t="n">
-        <v>46270</v>
+        <v>46264</v>
       </c>
       <c r="B5" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A5,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A5+7)),"")</f>
@@ -5405,7 +5408,7 @@
     </row>
     <row r="6">
       <c r="A6" s="32" t="n">
-        <v>46277</v>
+        <v>46271</v>
       </c>
       <c r="B6" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A6,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A6+7)),"")</f>
@@ -5442,7 +5445,7 @@
     </row>
     <row r="7">
       <c r="A7" s="32" t="n">
-        <v>46284</v>
+        <v>46278</v>
       </c>
       <c r="B7" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A7,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A7+7)),"")</f>
@@ -5479,7 +5482,7 @@
     </row>
     <row r="8">
       <c r="A8" s="32" t="n">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="B8" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A8,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A8+7)),"")</f>
@@ -5516,7 +5519,7 @@
     </row>
     <row r="9">
       <c r="A9" s="32" t="n">
-        <v>46298</v>
+        <v>46292</v>
       </c>
       <c r="B9" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A9,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A9+7)),"")</f>
@@ -5553,7 +5556,7 @@
     </row>
     <row r="10">
       <c r="A10" s="32" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="B10" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A10,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A10+7)),"")</f>
@@ -5590,7 +5593,7 @@
     </row>
     <row r="11">
       <c r="A11" s="32" t="n">
-        <v>46312</v>
+        <v>46306</v>
       </c>
       <c r="B11" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A11,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A11+7)),"")</f>
@@ -5627,7 +5630,7 @@
     </row>
     <row r="12">
       <c r="A12" s="32" t="n">
-        <v>46319</v>
+        <v>46313</v>
       </c>
       <c r="B12" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A12,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A12+7)),"")</f>
@@ -5664,7 +5667,7 @@
     </row>
     <row r="13">
       <c r="A13" s="32" t="n">
-        <v>46326</v>
+        <v>46320</v>
       </c>
       <c r="B13" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A13,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A13+7)),"")</f>
@@ -5701,7 +5704,7 @@
     </row>
     <row r="14">
       <c r="A14" s="32" t="n">
-        <v>46333</v>
+        <v>46327</v>
       </c>
       <c r="B14" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A14,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A14+7)),"")</f>
@@ -5738,7 +5741,7 @@
     </row>
     <row r="15">
       <c r="A15" s="32" t="n">
-        <v>46340</v>
+        <v>46334</v>
       </c>
       <c r="B15" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A15,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A15+7)),"")</f>
@@ -5775,7 +5778,7 @@
     </row>
     <row r="16">
       <c r="A16" s="32" t="n">
-        <v>46347</v>
+        <v>46341</v>
       </c>
       <c r="B16" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A16,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A16+7)),"")</f>
@@ -5812,7 +5815,7 @@
     </row>
     <row r="17">
       <c r="A17" s="32" t="n">
-        <v>46354</v>
+        <v>46348</v>
       </c>
       <c r="B17" s="33">
         <f>IFERROR(AVERAGEIFS('Daily Log'!$B$2:$B$114,'Daily Log'!$A$2:$A$114,"&gt;="&amp;A17,'Daily Log'!$A$2:$A$114,"&lt;"&amp;(A17+7)),"")</f>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="171" formatCode="mmm yyyy"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd;;;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +81,11 @@
       <name val="Arial"/>
       <i val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
     </font>
   </fonts>
   <fills count="5">
@@ -132,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +188,7 @@
     <xf numFmtId="167" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1314,7 +1320,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" hidden="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1349,7 +1354,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1503,7 +1507,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
@@ -8451,7 +8454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8484,6 +8487,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -9118,6 +9122,9 @@
       <c r="M34" s="18" t="n"/>
       <c r="N34" s="18" t="n"/>
     </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
@@ -9141,6 +9148,7 @@
         <v/>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
@@ -9177,9 +9185,10 @@
         <f>IF(B42="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B42)</f>
         <v/>
       </c>
-      <c r="D42" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C42&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -9215,9 +9224,10 @@
         <f>IF(B44="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B44)</f>
         <v/>
       </c>
-      <c r="D44" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C44&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -9291,9 +9301,10 @@
         <f>IF(B48="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B48)</f>
         <v/>
       </c>
-      <c r="D48" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C48&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
+      <c r="D48" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -9348,9 +9359,10 @@
         <f>IF(B51="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B51)</f>
         <v/>
       </c>
-      <c r="D51" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C51&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -9367,9 +9379,10 @@
         <f>IF(B52="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B52)</f>
         <v/>
       </c>
-      <c r="D52" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C52&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -9386,9 +9399,10 @@
         <f>IF(B53="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B53)</f>
         <v/>
       </c>
-      <c r="D53" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C53&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -9405,11 +9419,18 @@
         <f>IF(B54="",IF($D$39&gt;=1,TODAY()-INDEX($A$5:$A$34,1),""),TODAY()-B54)</f>
         <v/>
       </c>
-      <c r="D54" s="3">
-        <f>IF($D$39&lt;10,"Collecting data",IF(C54&gt;=10,"REVIEW — notify Roberto","Active"))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-18 (history preserved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -1921,14 +1921,32 @@
       <c r="A3" s="32" t="n">
         <v>46249</v>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="18" t="n"/>
-      <c r="G3" s="18" t="n"/>
-      <c r="H3" s="18" t="n"/>
-      <c r="I3" s="18" t="n"/>
+      <c r="B3" s="30" t="n">
+        <v>201</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>1565</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <v>114</v>
+      </c>
+      <c r="E3" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>74</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18" t="inlineStr">
+        <is>
+          <t>Egg scramble (salmon, broccoli, cottage cheese); banana + peanut butter; NY strip (fat trimmed), sweet potato, arugula/avocado salad. Fat over budget (3 stacked sources), carbs starch-heavy.</t>
+        </is>
+      </c>
       <c r="J3" s="31">
         <f>IF(C3="","",C3-Targets!$B$12)</f>
         <v/>
@@ -8454,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8487,7 +8505,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -9122,9 +9139,6 @@
       <c r="M34" s="18" t="n"/>
       <c r="N34" s="18" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
@@ -9148,7 +9162,6 @@
         <v/>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
@@ -9425,12 +9438,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -9543,18 +9543,58 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="18" t="n"/>
-      <c r="I5" s="18" t="n"/>
-      <c r="J5" s="18" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="18" t="n"/>
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>631</v>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>Preliminary LabCorp panel (collected 8/13, reported 8/15, still preliminary as of 8/18 — ApoB, cardiac hs-CRP, IGF-1 marked "Will Follow"). No lipid panel (Chol/LDL/HDL/Trig) drawn this round. Glucose 104 mg/dL flagged High by lab, but fasting status not recorded on the requisition — not conclusive on its own. A1C 5.6% sits at the top of normal (ref 4.8-5.6). Free testosterone (direct) 10.2 pg/mL alongside total 631 ng/dL. TSH/T4/kidney/liver/CBC all in range. Flag glucose + full panel to Dr. Aldrich once ApoB/hs-CRP post.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2059,13 +2059,29 @@
         <v>46252</v>
       </c>
       <c r="B6" s="30" t="n"/>
-      <c r="C6" s="18" t="n"/>
-      <c r="D6" s="18" t="n"/>
-      <c r="E6" s="18" t="n"/>
-      <c r="F6" s="18" t="n"/>
-      <c r="G6" s="18" t="n"/>
-      <c r="H6" s="18" t="n"/>
-      <c r="I6" s="18" t="n"/>
+      <c r="C6" s="18" t="n">
+        <v>975</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 1 egg+2 egg whites (spinach, onion), pickled jalapenos, Oikos yogurt. Lunch ~2pm: grilled chicken chopped salad (butter lettuce/kale/radicchio, blue cheese, walnuts, dried cranberries, pumpkin seeds, vinaigrette). Fat running high (50/57g) on cheese+nuts+dressing stack — go lean at dinner, no added fat. Day in progress.</t>
+        </is>
+      </c>
       <c r="J6" s="31">
         <f>IF(C6="","",C6-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2060,26 +2060,26 @@
       </c>
       <c r="B6" s="30" t="n"/>
       <c r="C6" s="18" t="n">
-        <v>975</v>
+        <v>1545</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 1 egg+2 egg whites (spinach, onion), pickled jalapenos, Oikos yogurt. Lunch ~2pm: grilled chicken chopped salad (butter lettuce/kale/radicchio, blue cheese, walnuts, dried cranberries, pumpkin seeds, vinaigrette). Fat running high (50/57g) on cheese+nuts+dressing stack — go lean at dinner, no added fat. Day in progress.</t>
+          <t>Breakfast: 1 egg+2 egg whites (spinach, onion), pickled jalapenos, Oikos yogurt. Lunch ~2pm: grilled chicken chopped salad (blue cheese, walnuts, cranberries, vinaigrette). Dinner: Wendy's chicken sandwich no bun, 5 fries, medium sweet tea. Fat finished the day over target (68/57g, mostly cheese+nuts+fried chicken); protein came up short (107 of 187g) despite calories landing under budget (1545/1825) - a lean-but-low-protein day overall.</t>
         </is>
       </c>
       <c r="J6" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="171" formatCode="mmm yyyy"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd;;;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +87,9 @@
       <i val="1"/>
       <color rgb="00888888"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -137,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,6 +192,9 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1785,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1869,6 +1875,11 @@
           <t>7-day Avg Calories</t>
         </is>
       </c>
+      <c r="N1" s="43" t="inlineStr">
+        <is>
+          <t>Waist (in)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="29" t="n">
@@ -2103,14 +2114,20 @@
       <c r="A7" s="32" t="n">
         <v>46253</v>
       </c>
-      <c r="B7" s="30" t="n"/>
+      <c r="B7" s="30" t="n">
+        <v>198</v>
+      </c>
       <c r="C7" s="18" t="n"/>
       <c r="D7" s="18" t="n"/>
       <c r="E7" s="18" t="n"/>
       <c r="F7" s="18" t="n"/>
       <c r="G7" s="18" t="n"/>
       <c r="H7" s="18" t="n"/>
-      <c r="I7" s="18" t="n"/>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>Weighed in 198.0 lb at 7am after Miami trip (down from 201.0 on 8/15). First waist reading: 40in. No food logged yet as of 7am.</t>
+        </is>
+      </c>
       <c r="J7" s="31">
         <f>IF(C7="","",C7-Targets!$B$12)</f>
         <v/>
@@ -2126,6 +2143,9 @@
       <c r="M7" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C7,$A$2:$A7,"&gt;="&amp;(A7-6),$A$2:$A7,"&lt;="&amp;A7),"")</f>
         <v/>
+      </c>
+      <c r="N7" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -6970,10 +6990,26 @@
         <v>46290</v>
       </c>
       <c r="B46" s="18" t="n"/>
-      <c r="C46" s="18" t="n"/>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="18" t="n"/>
-      <c r="F46" s="18" t="n"/>
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>Last Logged</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="inlineStr">
+        <is>
+          <t>Days Idle</t>
+        </is>
+      </c>
+      <c r="F46" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
       <c r="G46" s="18" t="n"/>
       <c r="H46" s="18" t="n"/>
       <c r="I46" s="18" t="n"/>
@@ -6991,10 +7027,23 @@
         <v>46291</v>
       </c>
       <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-      <c r="E47" s="18" t="n"/>
-      <c r="F47" s="18" t="n"/>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Waist</t>
+        </is>
+      </c>
+      <c r="D47" s="18">
+        <f>IFERROR(_xlfn.MAXIFS('Daily Log'!$A$2:$A$200,'Daily Log'!$N$2:$N$200,"&lt;&gt;"),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="18">
+        <f>IF(D47="","",TODAY()-D47)</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>IF(D47="","no data yet",IF(E47&gt;=10,"REVIEW — ask Roberto","Active"))</f>
+        <v/>
+      </c>
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="18" t="n"/>
       <c r="I47" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2117,15 +2117,25 @@
       <c r="B7" s="30" t="n">
         <v>198</v>
       </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
+      <c r="C7" s="18" t="n">
+        <v>213</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 198.0 lb at 7am after Miami trip (down from 201.0 on 8/15). First waist reading: 40in. No food logged yet as of 7am.</t>
+          <t>Weighed in 198.0 lb at 7am, waist 40in (first reading). Breakfast 8:19am (about to eat): 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber, lean high-protein start. Lunch prepped (not yet eaten): 50g canned refried beans + 150g chile verde (pork, potatoes, green chile) - approx 346kcal/24g protein/21g carb/20g fat/5g fiber, staged for later, not included in today's totals until confirmed eaten.</t>
         </is>
       </c>
       <c r="J7" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2118,24 +2118,24 @@
         <v>198</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>213</v>
+        <v>381</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 198.0 lb at 7am, waist 40in (first reading). Breakfast 8:19am (about to eat): 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber, lean high-protein start. Lunch prepped (not yet eaten): 50g canned refried beans + 150g chile verde (pork, potatoes, green chile) - approx 346kcal/24g protein/21g carb/20g fat/5g fiber, staged for later, not included in today's totals until confirmed eaten.</t>
+          <t>Weighed in 198.0 lb at 7am, waist 40in (first reading). Breakfast 8:19am: 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (prepped for work): Siggi's plain 0% skyr ~157g, blueberries ~57g, chia seeds ~5g, honey ~7g (scale reading illegible in photo; used his stated ~150g yogurt/50g blueberries plus a 14g overage split evenly between the two) - approx 168kcal/19g protein/22g carb/2g fat/3g fiber, ~6g added sugar from honey. Running total (breakfast+snack): 381kcal/49g protein/27g carb/10g fat/4g fiber. Lunch prepped (not yet eaten): 50g canned refried beans + 150g chile verde (pork, potatoes, green chile) - approx 346kcal/24g protein/21g carb/20g fat/5g fiber, staged for later, not included in totals until confirmed eaten.</t>
         </is>
       </c>
       <c r="J7" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2118,24 +2118,24 @@
         <v>198</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>381</v>
+        <v>727</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 198.0 lb at 7am, waist 40in (first reading). Breakfast 8:19am: 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (prepped for work): Siggi's plain 0% skyr ~157g, blueberries ~57g, chia seeds ~5g, honey ~7g (scale reading illegible in photo; used his stated ~150g yogurt/50g blueberries plus a 14g overage split evenly between the two) - approx 168kcal/19g protein/22g carb/2g fat/3g fiber, ~6g added sugar from honey. Running total (breakfast+snack): 381kcal/49g protein/27g carb/10g fat/4g fiber. Lunch prepped (not yet eaten): 50g canned refried beans + 150g chile verde (pork, potatoes, green chile) - approx 346kcal/24g protein/21g carb/20g fat/5g fiber, staged for later, not included in totals until confirmed eaten.</t>
+          <t>Weighed in 198.0 lb at 7am, waist 40in (first reading). Breakfast 8:19am: 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (eaten at work): Siggi's plain 0% skyr ~157g, blueberries ~57g, chia seeds ~5g, honey ~7g (scale reading illegible in photo; estimate) - approx 168kcal/19g protein/22g carb/2g fat/3g fiber. Lunch, confirmed eaten 2:12pm: 50g canned refried beans + 150g chile verde (pork, potatoes, green chile) - approx 346kcal/24g protein/21g carb/20g fat/5g fiber, same estimate given at prep time, no re-estimate. Day total so far: 727kcal/73g protein/48g carb/30g fat/9g fiber.</t>
         </is>
       </c>
       <c r="J7" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6140,8 +6140,17 @@
       <c r="E9" s="18" t="n"/>
       <c r="F9" s="18" t="n"/>
       <c r="G9" s="18" t="n"/>
-      <c r="H9" s="18" t="n"/>
-      <c r="I9" s="18" t="n"/>
+      <c r="H9" s="18" t="n">
+        <v>4792</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Tonal end-of-workout summary, 7:20pm. Volume 4,792 lbs, Duration 14:16, Movement Target 100%, Calories Burned 101, Work 9.8 kJ, Time Under Tension 6:06, Coaching Cues 0. Strong volume day - highest of the Last-8-Days view (Fri 4,960 lbs, Sat 4,438 lbs, today 4,792 lbs).</t>
+        </is>
+      </c>
       <c r="K9" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C9,$A$5:$A9,"&gt;="&amp;(A9-6),$A$5:$A9,"&lt;="&amp;A9),"")</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2118,24 +2118,24 @@
         <v>198</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>727</v>
+        <v>1157</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 198.0 lb at 7am, waist 40in (first reading). Breakfast 8:19am: 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (eaten at work): Siggi's plain 0% skyr ~157g, blueberries ~57g, chia seeds ~5g, honey ~7g (scale reading illegible in photo; estimate) - approx 168kcal/19g protein/22g carb/2g fat/3g fiber. Lunch, confirmed eaten 2:12pm: 50g canned refried beans + 150g chile verde (pork, potatoes, green chile) - approx 346kcal/24g protein/21g carb/20g fat/5g fiber, same estimate given at prep time, no re-estimate. Day total so far: 727kcal/73g protein/48g carb/30g fat/9g fiber.</t>
+          <t>Weighed in 198.0 lb at 7am, waist 40in. Breakfast 8:19am: 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (eaten at work): Siggi's skyr ~157g, blueberries ~57g, chia ~5g, honey ~7g - approx 168kcal/19g protein/22g carb/2g fat/3g fiber. Lunch 2:12pm: 50g refried beans + 150g chile verde - approx 346kcal/24g protein/21g carb/20g fat/5g fiber. Dinner (photo, no caption): arugula/radicchio salad, red onion, ~100g diced avocado, ~2.5 hard-boiled eggs, a crunchy topping (fried onion or nut/seed clusters, unclear), small red garnish (likely beet, unclear) - approx 430kcal/20g protein/20g carb/32g fat/9g fiber, estimate. Day total: 1,157kcal/93g protein/68g carb/62g fat/18g fiber. Fat finished 5g over target (62/57g) - avocado+eggs+topping stacked. Protein at 93g, well under 187g target if the day is done.</t>
         </is>
       </c>
       <c r="J7" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2118,16 +2118,16 @@
         <v>198</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>1157</v>
+        <v>1280</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>18</v>
@@ -2135,7 +2135,7 @@
       <c r="H7" s="18" t="n"/>
       <c r="I7" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 198.0 lb at 7am, waist 40in. Breakfast 8:19am: 50g cottage cheese, 50g spinach, 50g whole egg, 150g egg whites - 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (eaten at work): Siggi's skyr ~157g, blueberries ~57g, chia ~5g, honey ~7g - approx 168kcal/19g protein/22g carb/2g fat/3g fiber. Lunch 2:12pm: 50g refried beans + 150g chile verde - approx 346kcal/24g protein/21g carb/20g fat/5g fiber. Dinner (photo, no caption): arugula/radicchio salad, red onion, ~100g diced avocado, ~2.5 hard-boiled eggs, a crunchy topping (fried onion or nut/seed clusters, unclear), small red garnish (likely beet, unclear) - approx 430kcal/20g protein/20g carb/32g fat/9g fiber, estimate. Day total: 1,157kcal/93g protein/68g carb/62g fat/18g fiber. Fat finished 5g over target (62/57g) - avocado+eggs+topping stacked. Protein at 93g, well under 187g target if the day is done.</t>
+          <t>Weighed in 198.0 lb at 7am, waist 40in. Breakfast 8:19am: 213kcal/30g protein/5g carb/8g fat/1g fiber. Snack (work): 168kcal/19g protein/22g carb/2g fat/3g fiber. Lunch 2:12pm: 346kcal/24g protein/21g carb/20g fat/5g fiber. Dinner (photo, salad w/ avocado+eggs): 430kcal/20g protein/20g carb/32g fat/9g fiber. Latte (1 shot espresso, 2% milk, ~12oz): approx 123kcal/8g protein/11g carb/5g fat. Day total: 1,280kcal/101g protein/79g carb/67g fat/18g fiber. Fat now 10g over target (67/57g). Protein at 101g, still well under 187g target if the day is done.</t>
         </is>
       </c>
       <c r="J7" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2163,13 +2163,29 @@
         <v>46254</v>
       </c>
       <c r="B8" s="30" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
+      <c r="C8" s="18" t="n">
+        <v>373</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g, estimated), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. A small white item in the photo (possibly yogurt/sour cream) wasn't mentioned in his caption and wasn't counted - flagged for him to confirm. Strong high-protein start to the day.</t>
+        </is>
+      </c>
       <c r="J8" s="31">
         <f>IF(C8="","",C8-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2164,26 +2164,26 @@
       </c>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="18" t="n">
-        <v>373</v>
+        <v>931</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g, estimated), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. A small white item in the photo (possibly yogurt/sour cream) wasn't mentioned in his caption and wasn't counted - flagged for him to confirm. Strong high-protein start to the day.</t>
+          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. Lunch: 180g salmon, 150g sweet potato, 145g brussels sprouts - approx 558kcal/46g protein/42g carb/22g fat/11g fiber, gram-measured, well-balanced (no lentils needed). Day total: 931kcal/83g protein/69g carb/35g fat/16g fiber. Fiber already at 16g by lunch, well ahead of pace.</t>
         </is>
       </c>
       <c r="J8" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -9668,15 +9668,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
+      <c r="F5" s="18" t="n">
+        <v>130</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.84</v>
       </c>
       <c r="H5" s="18" t="n">
         <v>5.6</v>
@@ -9692,7 +9688,7 @@
       </c>
       <c r="L5" s="18" t="inlineStr">
         <is>
-          <t>Preliminary LabCorp panel (collected 8/13, reported 8/15, still preliminary as of 8/18 — ApoB, cardiac hs-CRP, IGF-1 marked "Will Follow"). No lipid panel (Chol/LDL/HDL/Trig) drawn this round. Glucose 104 mg/dL flagged High by lab, but fasting status not recorded on the requisition — not conclusive on its own. A1C 5.6% sits at the top of normal (ref 4.8-5.6). Free testosterone (direct) 10.2 pg/mL alongside total 631 ng/dL. TSH/T4/kidney/liver/CBC all in range. Flag glucose + full panel to Dr. Aldrich once ApoB/hs-CRP post.</t>
+          <t>FINAL LabCorp panel (collected 8/13, finalized 8/19). No lipid panel (Chol/LDL/HDL/Trig) drawn this round. ApoB 130 mg/dL - flagged HIGH by lab (desirable &lt;90, high 100-130, very high &gt;130) - this is the headline finding: ApoB is the primary cardiovascular risk marker in the Attia-influenced coaching style this dashboard uses, and 130 sits at the top of the High band. Cardiac hs-CRP 0.84 mg/L - Low risk (&lt;1.00), good news, low inflammation. IGF-1 167 ng/mL - normal (ref 64-240). Glucose 104 mg/dL flagged High, fasting status not recorded - not conclusive alone. A1C 5.6% at top of normal. Vitamin D 30.8, testosterone 631 (free 10.2) - both normal. TSH/T4/kidney/liver/CBC all in range. Flag ApoB + glucose to Dr. Aldrich - not medical advice.</t>
         </is>
       </c>
     </row>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2164,26 +2164,26 @@
       </c>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="18" t="n">
-        <v>931</v>
+        <v>1407</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. Lunch: 180g salmon, 150g sweet potato, 145g brussels sprouts - approx 558kcal/46g protein/42g carb/22g fat/11g fiber, gram-measured, well-balanced (no lentils needed). Day total: 931kcal/83g protein/69g carb/35g fat/16g fiber. Fiber already at 16g by lunch, well ahead of pace.</t>
+          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. Lunch: 180g salmon, 150g sweet potato, 145g brussels sprouts - approx 558kcal/46g protein/42g carb/22g fat/11g fiber. Dinner: turkey taco salad bowl - 175g extra-lean ground turkey, 75g arugula, 75g black beans, 75g pico de gallo, 40g avocado, 40g plain Greek yogurt, 25g white onion, cilantro+jalapeno, 1/2 lime - approx 476kcal/64g protein/33g carb/11g fat/12g fiber, gram-measured, excellent macro profile. Day total: 1,407kcal/147g protein/102g carb/46g fat/28g fiber - best day logged so far, well within every target with room to spare.</t>
         </is>
       </c>
       <c r="J8" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2164,26 +2164,26 @@
       </c>
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="18" t="n">
-        <v>1407</v>
+        <v>1456</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. Lunch: 180g salmon, 150g sweet potato, 145g brussels sprouts - approx 558kcal/46g protein/42g carb/22g fat/11g fiber. Dinner: turkey taco salad bowl - 175g extra-lean ground turkey, 75g arugula, 75g black beans, 75g pico de gallo, 40g avocado, 40g plain Greek yogurt, 25g white onion, cilantro+jalapeno, 1/2 lime - approx 476kcal/64g protein/33g carb/11g fat/12g fiber, gram-measured, excellent macro profile. Day total: 1,407kcal/147g protein/102g carb/46g fat/28g fiber - best day logged so far, well within every target with room to spare.</t>
+          <t>Breakfast: 150g egg whites, 2 whole eggs, 50g spinach, 50g cottage cheese, salsa, blueberries (~130g), espresso no sugar - approx 373kcal/37g protein/27g carb/13g fat/5g fiber. Lunch: 180g salmon, 150g sweet potato, 145g brussels sprouts - approx 558kcal/46g protein/42g carb/22g fat/11g fiber. Dinner: turkey taco salad bowl (175g ground turkey, arugula, black beans, pico, avocado, Greek yogurt) - approx 476kcal/64g protein/33g carb/11g fat/12g fiber. Snack: 15 pistachios (~9g) - approx 49kcal/2g protein/2g carb/4g fat/1g fiber. Day total: 1,456kcal/149g protein/104g carb/50g fat/29g fiber - best day logged so far, every macro within target.</t>
         </is>
       </c>
       <c r="J8" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2208,13 +2208,29 @@
         <v>46255</v>
       </c>
       <c r="B9" s="30" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
-      <c r="H9" s="18" t="n"/>
-      <c r="I9" s="18" t="n"/>
+      <c r="C9" s="18" t="n">
+        <v>457</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>44</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 30g spinach, 75g mushrooms, 150g egg whites, 1 whole egg, 50g low-fat cottage cheese, 75g berries, 10g chia seeds, latte (2 espresso shots, 2% milk) - approx 457kcal/44g protein/35g carb/15g fat/7g fiber. Strong high-protein, high-fiber start again.</t>
+        </is>
+      </c>
       <c r="J9" s="31">
         <f>IF(C9="","",C9-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2209,26 +2209,26 @@
       </c>
       <c r="B9" s="30" t="n"/>
       <c r="C9" s="18" t="n">
-        <v>457</v>
+        <v>968</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 30g spinach, 75g mushrooms, 150g egg whites, 1 whole egg, 50g low-fat cottage cheese, 75g berries, 10g chia seeds, latte (2 espresso shots, 2% milk) - approx 457kcal/44g protein/35g carb/15g fat/7g fiber. Strong high-protein, high-fiber start again.</t>
+          <t>Breakfast: 30g spinach, 75g mushrooms, 150g egg whites, 1 whole egg, 50g low-fat cottage cheese, 75g berries, 10g chia seeds, latte (2 espresso shots, 2% milk) - approx 457kcal/44g protein/35g carb/15g fat/7g fiber. Lunch: 150g lean ground turkey, 100g cooked lentils, 100g sweet potato, 30g arugula, 53g cherry tomatoes, 40g Greek yogurt/lime crema - approx 511kcal/57g protein/46g carb/11g fat/12g fiber, gram-measured, excellent macro profile. Day total: 968kcal/101g protein/81g carb/26g fat/19g fiber - on pace, well balanced.</t>
         </is>
       </c>
       <c r="J9" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6225,8 +6225,17 @@
       <c r="E11" s="18" t="n"/>
       <c r="F11" s="18" t="n"/>
       <c r="G11" s="18" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
+      <c r="H11" s="18" t="n">
+        <v>4078</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Tonal end-of-workout summary, 7:28pm. Volume 4,078 lbs, Duration 14:28, Movement Target 100%, Calories Burned 67, Work 9.9 kJ, Time Under Tension 6:47, Coaching Cues 0. Lighter volume than Wed (4,792 lbs) but still 100% movement target, clean form throughout.</t>
+        </is>
+      </c>
       <c r="K11" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C11,$A$5:$A11,"&gt;="&amp;(A11-6),$A$5:$A11,"&lt;="&amp;A11),"")</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2209,26 +2209,26 @@
       </c>
       <c r="B9" s="30" t="n"/>
       <c r="C9" s="18" t="n">
-        <v>968</v>
+        <v>1266</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="F9" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <v>26</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>19</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 30g spinach, 75g mushrooms, 150g egg whites, 1 whole egg, 50g low-fat cottage cheese, 75g berries, 10g chia seeds, latte (2 espresso shots, 2% milk) - approx 457kcal/44g protein/35g carb/15g fat/7g fiber. Lunch: 150g lean ground turkey, 100g cooked lentils, 100g sweet potato, 30g arugula, 53g cherry tomatoes, 40g Greek yogurt/lime crema - approx 511kcal/57g protein/46g carb/11g fat/12g fiber, gram-measured, excellent macro profile. Day total: 968kcal/101g protein/81g carb/26g fat/19g fiber - on pace, well balanced.</t>
+          <t>Breakfast: 30g spinach, 75g mushrooms, 150g egg whites, 1 whole egg, 50g low-fat cottage cheese, 75g berries, 10g chia seeds, latte (2 espresso shots, 2% milk) - approx 457kcal/44g protein/35g carb/15g fat/7g fiber. Lunch: 150g lean ground turkey, 100g cooked lentils, 100g sweet potato, 30g arugula, 53g cherry tomatoes, 40g Greek yogurt/lime crema - approx 511kcal/57g protein/46g carb/11g fat/12g fiber. Snack: 170g plain Greek yogurt (0-2%), 50g blackberries, 50g blueberries, 10g chia seeds, 5g honey, 1/2 scoop protein powder - approx 298kcal/32g protein/28g carb/8g fat/7g fiber. Day total: 1,266kcal/133g protein/109g carb/34g fat/26g fiber - excellent pace, fourth strong day running.</t>
         </is>
       </c>
       <c r="J9" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -8833,64 +8833,120 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n"/>
+      <c r="A8" s="29" t="n">
+        <v>46252</v>
+      </c>
       <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
+      <c r="C8" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
+      <c r="E8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
+      <c r="I8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K8" s="18" t="n"/>
       <c r="L8" s="18" t="n"/>
       <c r="M8" s="18" t="n"/>
       <c r="N8" s="18" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n"/>
+      <c r="A9" s="29" t="n">
+        <v>46253</v>
+      </c>
       <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
+      <c r="E9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="18" t="n"/>
-      <c r="I9" s="18" t="n"/>
-      <c r="J9" s="18" t="n"/>
+      <c r="I9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K9" s="18" t="n"/>
       <c r="L9" s="18" t="n"/>
       <c r="M9" s="18" t="n"/>
       <c r="N9" s="18" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n"/>
+      <c r="A10" s="29" t="n">
+        <v>46254</v>
+      </c>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
+      <c r="C10" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
+      <c r="E10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
-      <c r="J10" s="18" t="n"/>
+      <c r="I10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K10" s="18" t="n"/>
       <c r="L10" s="18" t="n"/>
       <c r="M10" s="18" t="n"/>
       <c r="N10" s="18" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n"/>
+      <c r="A11" s="29" t="n">
+        <v>46255</v>
+      </c>
       <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
+      <c r="E11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="18" t="n"/>
+      <c r="I11" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" s="18" t="n"/>
       <c r="L11" s="18" t="n"/>
       <c r="M11" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -5960,7 +5960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6053,11 +6053,6 @@
           <t>7-day Avg HRV</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="n">
@@ -6094,7 +6089,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D5,$A$5:$A5,"&gt;="&amp;(A5-6),$A$5:$A5,"&lt;="&amp;A5),"")</f>
         <v/>
       </c>
-      <c r="M5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="32" t="n">
@@ -6116,7 +6110,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D6,$A$5:$A6,"&gt;="&amp;(A6-6),$A$5:$A6,"&lt;="&amp;A6),"")</f>
         <v/>
       </c>
-      <c r="M6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="32" t="n">
@@ -6138,7 +6131,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D7,$A$5:$A7,"&gt;="&amp;(A7-6),$A$5:$A7,"&lt;="&amp;A7),"")</f>
         <v/>
       </c>
-      <c r="M7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="32" t="n">
@@ -6160,7 +6152,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D8,$A$5:$A8,"&gt;="&amp;(A8-6),$A$5:$A8,"&lt;="&amp;A8),"")</f>
         <v/>
       </c>
-      <c r="M8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="32" t="n">
@@ -6191,7 +6182,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D9,$A$5:$A9,"&gt;="&amp;(A9-6),$A$5:$A9,"&lt;="&amp;A9),"")</f>
         <v/>
       </c>
-      <c r="M9" s="18" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="32" t="n">
@@ -6213,7 +6203,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D10,$A$5:$A10,"&gt;="&amp;(A10-6),$A$5:$A10,"&lt;="&amp;A10),"")</f>
         <v/>
       </c>
-      <c r="M10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="32" t="n">
@@ -6244,7 +6233,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D11,$A$5:$A11,"&gt;="&amp;(A11-6),$A$5:$A11,"&lt;="&amp;A11),"")</f>
         <v/>
       </c>
-      <c r="M11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="32" t="n">
@@ -6266,7 +6254,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D12,$A$5:$A12,"&gt;="&amp;(A12-6),$A$5:$A12,"&lt;="&amp;A12),"")</f>
         <v/>
       </c>
-      <c r="M12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="32" t="n">
@@ -6288,7 +6275,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D13,$A$5:$A13,"&gt;="&amp;(A13-6),$A$5:$A13,"&lt;="&amp;A13),"")</f>
         <v/>
       </c>
-      <c r="M13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="32" t="n">
@@ -6310,7 +6296,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D14,$A$5:$A14,"&gt;="&amp;(A14-6),$A$5:$A14,"&lt;="&amp;A14),"")</f>
         <v/>
       </c>
-      <c r="M14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="32" t="n">
@@ -6332,7 +6317,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D15,$A$5:$A15,"&gt;="&amp;(A15-6),$A$5:$A15,"&lt;="&amp;A15),"")</f>
         <v/>
       </c>
-      <c r="M15" s="18" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="32" t="n">
@@ -6354,7 +6338,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D16,$A$5:$A16,"&gt;="&amp;(A16-6),$A$5:$A16,"&lt;="&amp;A16),"")</f>
         <v/>
       </c>
-      <c r="M16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="32" t="n">
@@ -6376,7 +6359,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D17,$A$5:$A17,"&gt;="&amp;(A17-6),$A$5:$A17,"&lt;="&amp;A17),"")</f>
         <v/>
       </c>
-      <c r="M17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="32" t="n">
@@ -6398,7 +6380,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D18,$A$5:$A18,"&gt;="&amp;(A18-6),$A$5:$A18,"&lt;="&amp;A18),"")</f>
         <v/>
       </c>
-      <c r="M18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="32" t="n">
@@ -6420,7 +6401,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D19,$A$5:$A19,"&gt;="&amp;(A19-6),$A$5:$A19,"&lt;="&amp;A19),"")</f>
         <v/>
       </c>
-      <c r="M19" s="18" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="32" t="n">
@@ -6442,7 +6422,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D20,$A$5:$A20,"&gt;="&amp;(A20-6),$A$5:$A20,"&lt;="&amp;A20),"")</f>
         <v/>
       </c>
-      <c r="M20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="32" t="n">
@@ -6464,7 +6443,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D21,$A$5:$A21,"&gt;="&amp;(A21-6),$A$5:$A21,"&lt;="&amp;A21),"")</f>
         <v/>
       </c>
-      <c r="M21" s="18" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="32" t="n">
@@ -6486,7 +6464,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D22,$A$5:$A22,"&gt;="&amp;(A22-6),$A$5:$A22,"&lt;="&amp;A22),"")</f>
         <v/>
       </c>
-      <c r="M22" s="18" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="32" t="n">
@@ -6508,7 +6485,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D23,$A$5:$A23,"&gt;="&amp;(A23-6),$A$5:$A23,"&lt;="&amp;A23),"")</f>
         <v/>
       </c>
-      <c r="M23" s="18" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="32" t="n">
@@ -6530,7 +6506,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D24,$A$5:$A24,"&gt;="&amp;(A24-6),$A$5:$A24,"&lt;="&amp;A24),"")</f>
         <v/>
       </c>
-      <c r="M24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="32" t="n">
@@ -6552,7 +6527,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D25,$A$5:$A25,"&gt;="&amp;(A25-6),$A$5:$A25,"&lt;="&amp;A25),"")</f>
         <v/>
       </c>
-      <c r="M25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="32" t="n">
@@ -6574,7 +6548,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D26,$A$5:$A26,"&gt;="&amp;(A26-6),$A$5:$A26,"&lt;="&amp;A26),"")</f>
         <v/>
       </c>
-      <c r="M26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="32" t="n">
@@ -6596,7 +6569,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D27,$A$5:$A27,"&gt;="&amp;(A27-6),$A$5:$A27,"&lt;="&amp;A27),"")</f>
         <v/>
       </c>
-      <c r="M27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="32" t="n">
@@ -6618,7 +6590,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D28,$A$5:$A28,"&gt;="&amp;(A28-6),$A$5:$A28,"&lt;="&amp;A28),"")</f>
         <v/>
       </c>
-      <c r="M28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="32" t="n">
@@ -6640,7 +6611,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D29,$A$5:$A29,"&gt;="&amp;(A29-6),$A$5:$A29,"&lt;="&amp;A29),"")</f>
         <v/>
       </c>
-      <c r="M29" s="18" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="32" t="n">
@@ -6662,7 +6632,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D30,$A$5:$A30,"&gt;="&amp;(A30-6),$A$5:$A30,"&lt;="&amp;A30),"")</f>
         <v/>
       </c>
-      <c r="M30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="32" t="n">
@@ -6684,7 +6653,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D31,$A$5:$A31,"&gt;="&amp;(A31-6),$A$5:$A31,"&lt;="&amp;A31),"")</f>
         <v/>
       </c>
-      <c r="M31" s="18" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="32" t="n">
@@ -6706,7 +6674,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D32,$A$5:$A32,"&gt;="&amp;(A32-6),$A$5:$A32,"&lt;="&amp;A32),"")</f>
         <v/>
       </c>
-      <c r="M32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="32" t="n">
@@ -6728,7 +6695,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D33,$A$5:$A33,"&gt;="&amp;(A33-6),$A$5:$A33,"&lt;="&amp;A33),"")</f>
         <v/>
       </c>
-      <c r="M33" s="18" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="32" t="n">
@@ -6750,7 +6716,6 @@
         <f>IFERROR(AVERAGEIFS($D$5:$D34,$A$5:$A34,"&gt;="&amp;(A34-6),$A$5:$A34,"&lt;="&amp;A34),"")</f>
         <v/>
       </c>
-      <c r="M34" s="18" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="32" t="n">
@@ -6955,17 +6920,12 @@
           <t>Steps</t>
         </is>
       </c>
-      <c r="B43" s="37">
-        <f>IFERROR(_xlfn.MAXIFS($A$5:$A$34,$M$5:$M$34,"&lt;&gt;"),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="38">
-        <f>IF(B43="","",TODAY()-B43)</f>
-        <v/>
-      </c>
-      <c r="D43" s="3">
-        <f>IF(B43="","no data yet",IF(C43&gt;=10,"REVIEW — ask Roberto","Active"))</f>
-        <v/>
+      <c r="B43" s="37" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Retired 2026-08-21 (never logged in ~a week on the dashboard — dropped per Roberto's review, no data lost)</t>
+        </is>
       </c>
       <c r="E43" s="18" t="n"/>
       <c r="F43" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -35,7 +35,7 @@
     <numFmt numFmtId="171" formatCode="mmm yyyy"/>
     <numFmt numFmtId="172" formatCode="yyyy-mm-dd;;;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +90,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="000000FF"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -140,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +198,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1684,11 +1689,14 @@
           <t>Calorie target (kcal/day)</t>
         </is>
       </c>
-      <c r="B12" s="13">
-        <f>B10-B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="B12" s="44" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Revised 2026-08-22 (manual) — working range 1,800-1,900. Was 1,825 (formula-derived).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1696,13 +1704,12 @@
           <t>Protein target (g/day)</t>
         </is>
       </c>
-      <c r="B13" s="13">
-        <f>ROUND(B7*1,0)</f>
-        <v/>
+      <c r="B13" s="44" t="n">
+        <v>155</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>≈ 1g per lb of GOAL bodyweight — Attia/Lyon-style heuristic to preserve muscle during the cut.</t>
+          <t>Revised 2026-08-22 (manual) — working range 150-160g. Was 187g (~1g/lb goal weight heuristic).</t>
         </is>
       </c>
     </row>
@@ -1712,13 +1719,12 @@
           <t>Fat target (g/day)</t>
         </is>
       </c>
-      <c r="B14" s="13">
-        <f>ROUND(B12*0.28/9,0)</f>
-        <v/>
+      <c r="B14" s="44" t="n">
+        <v>65</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>≈ 28% of calories from fat.</t>
+          <t>Revised 2026-08-22 (manual) — working range 55-65g. Was 57g (~28% of calories).</t>
         </is>
       </c>
     </row>
@@ -1728,13 +1734,12 @@
           <t>Carb target (g/day)</t>
         </is>
       </c>
-      <c r="B15" s="13">
-        <f>ROUND((B12-B13*4-B14*9)/4,0)</f>
-        <v/>
+      <c r="B15" s="44" t="n">
+        <v>160</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Whatever calories remain after protein + fat.</t>
+          <t>Revised 2026-08-22 (manual) — working range 145-175g. Was 141g (remainder-of-calories calc).</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1754,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Elevated vs the standard 14g/1000kcal DV — Attia-style gut/metabolic health target.</t>
+          <t>Working range 30-40g. Unchanged in the 2026-08-22 revision.</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1767,26 @@
       <c r="B17" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="C17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Revised 2026-08-22: ceiling 20-25g, lower preferred. Was a flat &lt;25g ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Saturated fat ceiling (g/day)</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New 2026-08-22 — lower is better within a balanced diet.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2277,13 +2277,29 @@
         <v>46256</v>
       </c>
       <c r="B10" s="30" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="18" t="n"/>
-      <c r="F10" s="18" t="n"/>
-      <c r="G10" s="18" t="n"/>
-      <c r="H10" s="18" t="n"/>
-      <c r="I10" s="18" t="n"/>
+      <c r="C10" s="18" t="n">
+        <v>351</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 75g black beans (drained/rinsed), 120g egg whites, 2 whole eggs, 100g pico de gallo (divided 50g+50g), 40g 0% Greek yogurt, 5-10g cilantro chopped - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Another high-protein, high-fiber start.</t>
+        </is>
+      </c>
       <c r="J10" s="31">
         <f>IF(C10="","",C10-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2278,26 +2278,26 @@
       </c>
       <c r="B10" s="30" t="n"/>
       <c r="C10" s="18" t="n">
-        <v>351</v>
+        <v>725</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F10" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="G10" s="18" t="n">
         <v>11</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>8</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 75g black beans (drained/rinsed), 120g egg whites, 2 whole eggs, 100g pico de gallo (divided 50g+50g), 40g 0% Greek yogurt, 5-10g cilantro chopped - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Another high-protein, high-fiber start.</t>
+          <t>Breakfast: 75g black beans, 120g egg whites, 2 whole eggs, 100g pico de gallo, 40g 0% Greek yogurt, cilantro - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Lunch: turkey burger lettuce wrap - 170g 99% lean ground turkey (2 patties), 1 thin cheese slice (~20g), grilled onion 50g, jalapeno 15-20g, tomato 50g, pickles, lettuce wrap (no bun), mustard, Greek yogurt burger sauce - approx 374kcal/58g protein/11g carb/10g fat/3g fiber, gram-measured, excellent low-carb high-protein profile. Day total: 725kcal/96g protein/36g carb/21g fat/11g fiber.</t>
         </is>
       </c>
       <c r="J10" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2278,26 +2278,26 @@
       </c>
       <c r="B10" s="30" t="n"/>
       <c r="C10" s="18" t="n">
-        <v>725</v>
+        <v>1081</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 75g black beans, 120g egg whites, 2 whole eggs, 100g pico de gallo, 40g 0% Greek yogurt, cilantro - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Lunch: turkey burger lettuce wrap - 170g 99% lean ground turkey (2 patties), 1 thin cheese slice (~20g), grilled onion 50g, jalapeno 15-20g, tomato 50g, pickles, lettuce wrap (no bun), mustard, Greek yogurt burger sauce - approx 374kcal/58g protein/11g carb/10g fat/3g fiber, gram-measured, excellent low-carb high-protein profile. Day total: 725kcal/96g protein/36g carb/21g fat/11g fiber.</t>
+          <t>Breakfast: 75g black beans, 120g egg whites, 2 whole eggs, 100g pico de gallo, 40g 0% Greek yogurt, cilantro - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Lunch: turkey burger lettuce wrap (170g 99% lean ground turkey, cheese, grilled onion, jalapeno, tomato, pickles, mustard, Greek yogurt sauce) - approx 374kcal/58g protein/11g carb/10g fat/3g fiber. Snack: 200g Greek yogurt, 75g blueberries, 75g blackberries, 50g banana, 12g chia seeds, 1/2 scoop protein powder - approx 356kcal/36g protein/43g carb/6g fat/11g fiber. Day total: 1,081kcal/132g protein/79g carb/27g fat/22g fiber.</t>
         </is>
       </c>
       <c r="J10" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2278,26 +2278,26 @@
       </c>
       <c r="B10" s="30" t="n"/>
       <c r="C10" s="18" t="n">
-        <v>1081</v>
+        <v>1162</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 75g black beans, 120g egg whites, 2 whole eggs, 100g pico de gallo, 40g 0% Greek yogurt, cilantro - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Lunch: turkey burger lettuce wrap (170g 99% lean ground turkey, cheese, grilled onion, jalapeno, tomato, pickles, mustard, Greek yogurt sauce) - approx 374kcal/58g protein/11g carb/10g fat/3g fiber. Snack: 200g Greek yogurt, 75g blueberries, 75g blackberries, 50g banana, 12g chia seeds, 1/2 scoop protein powder - approx 356kcal/36g protein/43g carb/6g fat/11g fiber. Day total: 1,081kcal/132g protein/79g carb/27g fat/22g fiber.</t>
+          <t>Breakfast: 75g black beans, 120g egg whites, 2 whole eggs, 100g pico de gallo, 40g 0% Greek yogurt, cilantro - approx 351kcal/38g protein/25g carb/11g fat/8g fiber. Lunch: turkey burger lettuce wrap - approx 374kcal/58g protein/11g carb/10g fat/3g fiber. Snack 1: 200g Greek yogurt, 75g blueberries, 75g blackberries, 50g banana, 12g chia seeds, 1/2 scoop protein powder - approx 356kcal/36g protein/43g carb/6g fat/11g fiber. Snack 2: 25 pistachios (~14g) - approx 81kcal/3g protein/4g carb/7g fat/2g fiber. Day total: 1,162kcal/135g protein/83g carb/34g fat/24g fiber.</t>
         </is>
       </c>
       <c r="J10" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2322,13 +2322,29 @@
         <v>46257</v>
       </c>
       <c r="B11" s="30" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
+      <c r="C11" s="18" t="n">
+        <v>245</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, black pepper/garlic powder/smoked paprika, cooking spray, squeeze of lime - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. First day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
+        </is>
+      </c>
       <c r="J11" s="31">
         <f>IF(C11="","",C11-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6321,8 +6321,17 @@
       <c r="E13" s="18" t="n"/>
       <c r="F13" s="18" t="n"/>
       <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
+      <c r="H13" s="18" t="n">
+        <v>4717</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Tonal end-of-workout summary (logged via text, photo upload issue). Volume 4,717 lbs, Duration 16:39, Movement Target 100%, Calories Burned 112, Work 9.3 kJ, Time Under Tension 6:00, 6 movements. Heaviest volume of the week so far vs Wed 4,792 / Fri 4,078.</t>
+        </is>
+      </c>
       <c r="K13" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C13,$A$5:$A13,"&gt;="&amp;(A13-6),$A$5:$A13,"&lt;="&amp;A13),"")</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2323,26 +2323,26 @@
       </c>
       <c r="B11" s="30" t="n"/>
       <c r="C11" s="18" t="n">
-        <v>245</v>
+        <v>427</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, black pepper/garlic powder/smoked paprika, cooking spray, squeeze of lime - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. First day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, black pepper/garlic powder/smoked paprika, cooking spray, squeeze of lime - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Day total so far: 427kcal/33g protein/25g carb/23g fat/9g fiber. First day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
         </is>
       </c>
       <c r="J11" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2323,26 +2323,26 @@
       </c>
       <c r="B11" s="30" t="n"/>
       <c r="C11" s="18" t="n">
-        <v>427</v>
+        <v>958</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, black pepper/garlic powder/smoked paprika, cooking spray, squeeze of lime - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Day total so far: 427kcal/33g protein/25g carb/23g fat/9g fiber. First day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, cooking spray - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Lunch: turkey-lentil marinara skillet - 150g cooked lean turkey, 100g cooked lentils, 100-120g marinara, 75g fresh tomatoes, 75-100g mushrooms, 50g spinach, 20g onion, 1 garlic clove, 1 tbsp tomato paste, 15g mozzarella, 8-10g Parmesan, oregano/basil/pepper/red-pepper flakes - approx 531kcal/67g protein/41g carb/12g fat/13g fiber. Day total so far: 958kcal/100g protein/66g carb/35g fat/22g fiber. First day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
         </is>
       </c>
       <c r="J11" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2323,26 +2323,26 @@
       </c>
       <c r="B11" s="30" t="n"/>
       <c r="C11" s="18" t="n">
-        <v>958</v>
+        <v>1350</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, cooking spray - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Lunch: turkey-lentil marinara skillet - 150g cooked lean turkey, 100g cooked lentils, 100-120g marinara, 75g fresh tomatoes, 75-100g mushrooms, 50g spinach, 20g onion, 1 garlic clove, 1 tbsp tomato paste, 15g mozzarella, 8-10g Parmesan, oregano/basil/pepper/red-pepper flakes - approx 531kcal/67g protein/41g carb/12g fat/13g fiber. Day total so far: 958kcal/100g protein/66g carb/35g fat/22g fiber. First day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, cooking spray - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Lunch: turkey-lentil marinara skillet - 150g cooked lean turkey, 100g cooked lentils, 100-120g marinara, 75g fresh tomatoes, 75-100g mushrooms, 50g spinach, 20g onion, garlic, tomato paste, 15g mozzarella, 8-10g Parmesan - approx 531kcal/67g protein/41g carb/12g fat/13g fiber. Dinner: 170-180g cod (lemon, garlic, pepper, paprika, oregano), 100g sauteed spinach, 100g mushrooms, ~100g tomato+onion, 75g cooked lentils, 1 tsp olive oil, lemon juice/herbs/red pepper flakes - approx 392kcal/54g protein/29g carb/8g fat/11g fiber. Day total: 1,350kcal/154g protein/95g carb/43g fat/33g fiber - excellent full day, protein 1g shy of the 155g floor, fiber 33 of 35g target. First complete day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
         </is>
       </c>
       <c r="J11" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2323,26 +2323,26 @@
       </c>
       <c r="B11" s="30" t="n"/>
       <c r="C11" s="18" t="n">
-        <v>1350</v>
+        <v>1510</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, cooking spray - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Lunch: turkey-lentil marinara skillet - 150g cooked lean turkey, 100g cooked lentils, 100-120g marinara, 75g fresh tomatoes, 75-100g mushrooms, 50g spinach, 20g onion, garlic, tomato paste, 15g mozzarella, 8-10g Parmesan - approx 531kcal/67g protein/41g carb/12g fat/13g fiber. Dinner: 170-180g cod (lemon, garlic, pepper, paprika, oregano), 100g sauteed spinach, 100g mushrooms, ~100g tomato+onion, 75g cooked lentils, 1 tsp olive oil, lemon juice/herbs/red pepper flakes - approx 392kcal/54g protein/29g carb/8g fat/11g fiber. Day total: 1,350kcal/154g protein/95g carb/43g fat/33g fiber - excellent full day, protein 1g shy of the 155g floor, fiber 33 of 35g target. First complete day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 60g black beans (drained/rinsed), 30g spinach, 75g pico de gallo, 20-30g onion diced, 10-15g jalapeno, cilantro, cooking spray - approx 245kcal/28g protein/19g carb/6g fat/6g fiber. Snack 1: 15g walnuts (~7 halves), 15g pistachios (~24-25 kernels) - approx 182kcal/5g protein/6g carb/17g fat/3g fiber. Lunch: turkey-lentil marinara skillet - 150g cooked lean turkey, 100g cooked lentils, 100-120g marinara, 75g fresh tomatoes, 75-100g mushrooms, 50g spinach, 20g onion, garlic, tomato paste, 15g mozzarella, 8-10g Parmesan - approx 531kcal/67g protein/41g carb/12g fat/13g fiber. Dinner: 170-180g cod (lemon, garlic, pepper, paprika, oregano), 100g sauteed spinach, 100g mushrooms, ~100g tomato+onion, 75g cooked lentils, 1 tsp olive oil, lemon juice/herbs/red pepper flakes - approx 392kcal/54g protein/29g carb/8g fat/11g fiber. Snack 2: protein carrot cake bar - 160kcal/10g protein/18g carb/6g fat/4g fiber. Day total: 1,510kcal/164g protein/113g carb/49g fat/37g fiber - protein and fiber both cleared their floors (164 of 155g, 37 of 35g). First complete day of new tracking week (Sun 8/23-Sat 8/29); prior week (8/16-8/22) closed at 9,054kcal/828g protein total.</t>
         </is>
       </c>
       <c r="J11" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6316,11 +6316,21 @@
         <v>46257</v>
       </c>
       <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
+      <c r="C13" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>97</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>131</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>92</v>
+      </c>
       <c r="H13" s="18" t="n">
         <v>4717</v>
       </c>
@@ -6329,7 +6339,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Tonal end-of-workout summary (logged via text, photo upload issue). Volume 4,717 lbs, Duration 16:39, Movement Target 100%, Calories Burned 112, Work 9.3 kJ, Time Under Tension 6:00, 6 movements. Heaviest volume of the week so far vs Wed 4,792 / Fri 4,078.</t>
+          <t>Tonal end-of-workout summary (logged via text, photo upload issue). Volume 4,717 lbs, Duration 16:39, Movement Target 100%, Calories Burned 112, Work 9.3 kJ, Time Under Tension 6:00, 6 movements. Heaviest volume of the week so far vs Wed 4,792 / Fri 4,078. | Ring sync 8:47am: HR 98bpm (up from 84), HRV 40ms (down sharply from 128), SpO2 97%, BP 131/92 (up from 129/89 watch, diastolic now Stage 2), sleep not captured (0h00, sync error icon), ring proprietary "pressure" score 47 (first time logged, no baseline yet). Two BP watches in a row on the same side plus HRV drop worth mentioning to Dr. Aldrich, not a diagnosis.</t>
         </is>
       </c>
       <c r="K13" s="31">
@@ -8978,32 +8988,60 @@
       <c r="N11" s="18" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="n"/>
+      <c r="A12" s="29" t="n">
+        <v>46256</v>
+      </c>
       <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
+      <c r="E12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="18" t="n"/>
+      <c r="I12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" s="18" t="n"/>
       <c r="L12" s="18" t="n"/>
       <c r="M12" s="18" t="n"/>
       <c r="N12" s="18" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n"/>
+      <c r="A13" s="29" t="n">
+        <v>46257</v>
+      </c>
       <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
+      <c r="E13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
-      <c r="J13" s="18" t="n"/>
+      <c r="I13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" s="18" t="n"/>
       <c r="L13" s="18" t="n"/>
       <c r="M13" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2367,13 +2367,27 @@
         <v>46258</v>
       </c>
       <c r="B12" s="30" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
+      <c r="C12" s="18" t="n">
+        <v>343</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>5</v>
+      </c>
       <c r="H12" s="18" t="n"/>
-      <c r="I12" s="18" t="n"/>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Day 2 of tracking week (Sun 8/23-Sat 8/29).</t>
+        </is>
+      </c>
       <c r="J12" s="31">
         <f>IF(C12="","",C12-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2366,7 +2366,9 @@
       <c r="A12" s="32" t="n">
         <v>46258</v>
       </c>
-      <c r="B12" s="30" t="n"/>
+      <c r="B12" s="30" t="n">
+        <v>197</v>
+      </c>
       <c r="C12" s="18" t="n">
         <v>343</v>
       </c>
@@ -2385,7 +2387,7 @@
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Day 2 of tracking week (Sun 8/23-Sat 8/29).</t>
+          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29).</t>
         </is>
       </c>
       <c r="J12" s="31">
@@ -2403,6 +2405,9 @@
       <c r="M12" s="31">
         <f>IFERROR(AVERAGEIFS($C$2:$C12,$A$2:$A12,"&gt;="&amp;(A12-6),$A$2:$A12,"&lt;="&amp;A12),"")</f>
         <v/>
+      </c>
+      <c r="N12" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2370,24 +2370,24 @@
         <v>197</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>343</v>
+        <v>658</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29).</t>
+          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29). Lunch: 100g cod, 100g lentils, 100g Brussels sprouts - approx 315kcal/34g protein/28g carb/3g fat/9g fiber (Roberto's own estimate, 300-330kcal/32-35g protein/25-30g carb/8-10g fiber/very little fat). Day total so far: 658kcal/73g protein/61g carb/10g fat/14g fiber.</t>
         </is>
       </c>
       <c r="J12" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2370,24 +2370,24 @@
         <v>197</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>658</v>
+        <v>834</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29). Lunch: 100g cod, 100g lentils, 100g Brussels sprouts - approx 315kcal/34g protein/28g carb/3g fat/9g fiber (Roberto's own estimate, 300-330kcal/32-35g protein/25-30g carb/8-10g fiber/very little fat). Day total so far: 658kcal/73g protein/61g carb/10g fat/14g fiber.</t>
+          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29). Lunch: 100g cod, 100g lentils, 100g Brussels sprouts - approx 315kcal/34g protein/28g carb/3g fat/9g fiber (Roberto's own estimate, 300-330kcal/32-35g protein/25-30g carb/8-10g fiber/very little fat). Day total so far: 658kcal/73g protein/61g carb/10g fat/14g fiber. Snack: 100g Siggis plain yogurt, 12g protein powder, 6g chia seeds, 80g mixed blueberries/blackberries - approx 176kcal/21g protein/17g carb/3g fat/5g fiber. Day total so far: 834kcal/94g protein/78g carb/13g fat/19g fiber.</t>
         </is>
       </c>
       <c r="J12" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6380,8 +6380,17 @@
       <c r="E14" s="18" t="n"/>
       <c r="F14" s="18" t="n"/>
       <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
+      <c r="H14" s="18" t="n">
+        <v>4629</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Tonal end-of-workout summary. Volume 4,629 lbs, Duration 17:15, Movement Target 100%, Calories Burned 70, Work 7.9 kJ, Time Under Tension 5:49, Coaching Cues 1. Slightly lighter volume than yesterday (4,717 lbs) but still 100% movement target.</t>
+        </is>
+      </c>
       <c r="K14" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C14,$A$5:$A14,"&gt;="&amp;(A14-6),$A$5:$A14,"&lt;="&amp;A14),"")</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2370,24 +2370,24 @@
         <v>197</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>834</v>
+        <v>1396</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>94</v>
+        <v>160</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H12" s="18" t="n"/>
       <c r="I12" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29). Lunch: 100g cod, 100g lentils, 100g Brussels sprouts - approx 315kcal/34g protein/28g carb/3g fat/9g fiber (Roberto's own estimate, 300-330kcal/32-35g protein/25-30g carb/8-10g fiber/very little fat). Day total so far: 658kcal/73g protein/61g carb/10g fat/14g fiber. Snack: 100g Siggis plain yogurt, 12g protein powder, 6g chia seeds, 80g mixed blueberries/blackberries - approx 176kcal/21g protein/17g carb/3g fat/5g fiber. Day total so far: 834kcal/94g protein/78g carb/13g fat/19g fiber.</t>
+          <t>Weighed in 197.0 lb, waist 39in (down 1in from 40in on Aug 19). Breakfast: Kodiak protein pancakes - 40g Kodiak protein pancake mix, 60-70g egg whites mixed into batter, water, cinnamon, vanilla extract, 50g blueberries/blackberries, 1 tsp pure maple syrup - approx 219kcal/22g protein/32g carb/2g fat/5g fiber. Plus 1 whole egg, 100g egg whites on the side - approx 124kcal/17g protein/1g carb/5g fat. Meal total approx 343kcal/39g protein/33g carb/7g fat/5g fiber. Down 4.0 lb from the Aug 15 start (201.0), running ahead of the ~1lb/week pace. Day 2 of tracking week (Sun 8/23-Sat 8/29). Lunch: 100g cod, 100g lentils, 100g Brussels sprouts - approx 315kcal/34g protein/28g carb/3g fat/9g fiber (Roberto's own estimate, 300-330kcal/32-35g protein/25-30g carb/8-10g fiber/very little fat). Day total so far: 658kcal/73g protein/61g carb/10g fat/14g fiber. Snack: 100g Siggis plain yogurt, 12g protein powder, 6g chia seeds, 80g mixed blueberries/blackberries - approx 176kcal/21g protein/17g carb/3g fat/5g fiber. Day total so far: 834kcal/94g protein/78g carb/13g fat/19g fiber. Dinner: 160g chicken, 70g black beans (drained/rinsed), 50g avocado, 80g cottage cheese, 60g arugula, 60g cherry tomatoes, 60g pico de gallo, 1 tsp olive oil - approx 562kcal/66g protein/26g carb/21g fat/10g fiber. Day total: 1,396kcal/160g protein/104g carb/34g fat/29g fiber - protein cleared the 155g floor, fiber 6g shy of 35g. Strong second day of the new tracking week.</t>
         </is>
       </c>
       <c r="J12" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6404,14 +6404,31 @@
       <c r="A15" s="32" t="n">
         <v>46259</v>
       </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
+      <c r="B15" s="18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>83</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>108</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>127</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>89</v>
+      </c>
       <c r="H15" s="18" t="n"/>
       <c r="I15" s="18" t="n"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Ring sync 9:48am. Sleep 8h36m (first real capture since Aug 15 — prior syncs missed it). HR 83bpm, HRV 108ms (up sharply from 40ms yesterday, back near the 128ms Aug 15 baseline - confirms yesterday's drop was likely noise, not a real trend). BP 127/89 (down from 131/92 yesterday, close to the 129/89 Aug 15 reading). SpO2 98%. Ring pressure score 53 (up from 47 yesterday).</t>
+        </is>
+      </c>
       <c r="K15" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C15,$A$5:$A15,"&gt;="&amp;(A15-6),$A$5:$A15,"&lt;="&amp;A15),"")</f>
         <v/>
@@ -9076,32 +9093,60 @@
       <c r="N13" s="18" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="n"/>
+      <c r="A14" s="29" t="n">
+        <v>46258</v>
+      </c>
       <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
+      <c r="C14" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-      <c r="J14" s="18" t="n"/>
+      <c r="I14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K14" s="18" t="n"/>
       <c r="L14" s="18" t="n"/>
       <c r="M14" s="18" t="n"/>
       <c r="N14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n"/>
+      <c r="A15" s="29" t="n">
+        <v>46259</v>
+      </c>
       <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
+      <c r="E15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-      <c r="J15" s="18" t="n"/>
+      <c r="I15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="K15" s="18" t="n"/>
       <c r="L15" s="18" t="n"/>
       <c r="M15" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2415,13 +2415,27 @@
         <v>46259</v>
       </c>
       <c r="B13" s="30" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
+      <c r="C13" s="18" t="n">
+        <v>268</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>2</v>
+      </c>
       <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%.</t>
+        </is>
+      </c>
       <c r="J13" s="31">
         <f>IF(C13="","",C13-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6419,13 +6419,13 @@
         <v>46259</v>
       </c>
       <c r="B15" s="18" t="n">
-        <v>8.6</v>
+        <v>5.18</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="E15" s="18" t="n">
         <v>98</v>
@@ -6434,13 +6434,13 @@
         <v>127</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" s="18" t="n"/>
       <c r="I15" s="18" t="n"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Ring sync 9:48am. Sleep 8h36m (first real capture since Aug 15 — prior syncs missed it). HR 83bpm, HRV 108ms (up sharply from 40ms yesterday, back near the 128ms Aug 15 baseline - confirms yesterday's drop was likely noise, not a real trend). BP 127/89 (down from 131/92 yesterday, close to the 129/89 Aug 15 reading). SpO2 98%. Ring pressure score 53 (up from 47 yesterday).</t>
+          <t>Ring sync 9:48am. Sleep 8h36m (first real capture since Aug 15 — prior syncs missed it). HR 83bpm, HRV 108ms (up sharply from 40ms yesterday, back near the 128ms Aug 15 baseline - confirms yesterday's drop was likely noise, not a real trend). BP 127/89 (down from 131/92 yesterday, close to the 129/89 Aug 15 reading). SpO2 98%. Ring pressure score 53 (up from 47 yesterday). | Second sync 11:16am same day: Sleep now reads 5h11m (down from the 8h36m at 9:48am - real discrepancy between the two syncs, not reconciled, logging the later/most-recent read as current). HR 91 (up from 83). HRV back down to 40ms (matches the Aug 23 low exactly) - two low HRV readings now, not just one, so the "probably noise" read from this morning is less certain. BP 127/90 (essentially flat vs 127/89). SpO2 98%. Pressure score 47 (down from 53, matches Aug 23 exactly).</t>
         </is>
       </c>
       <c r="K15" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2416,24 +2416,24 @@
       </c>
       <c r="B13" s="30" t="n"/>
       <c r="C13" s="18" t="n">
-        <v>268</v>
+        <v>906</v>
       </c>
       <c r="D13" s="18" t="n">
+        <v>93</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>35</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>7</v>
-      </c>
       <c r="G13" s="18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H13" s="18" t="n"/>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%.</t>
+          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%. Lunch: turkey lettuce wrap - 170g lean turkey, cheese slice, peppers/onion, avocado (40g), yogurt-based sauce (80-100g), plus 100g raw sweet potato fries on the side - Roberto's own estimate 600-675kcal/55-60g protein/35-40g carb/25-30g fat, logged at midpoint approx 638kcal/58g protein/38g carb/28g fat/~6g fiber (fiber estimated). Day total so far: 906kcal/93g protein/51g carb/35g fat/8g fiber.</t>
         </is>
       </c>
       <c r="J13" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2416,24 +2416,24 @@
       </c>
       <c r="B13" s="30" t="n"/>
       <c r="C13" s="18" t="n">
-        <v>906</v>
+        <v>1341</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H13" s="18" t="n"/>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%. Lunch: turkey lettuce wrap - 170g lean turkey, cheese slice, peppers/onion, avocado (40g), yogurt-based sauce (80-100g), plus 100g raw sweet potato fries on the side - Roberto's own estimate 600-675kcal/55-60g protein/35-40g carb/25-30g fat, logged at midpoint approx 638kcal/58g protein/38g carb/28g fat/~6g fiber (fiber estimated). Day total so far: 906kcal/93g protein/51g carb/35g fat/8g fiber.</t>
+          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%. Lunch: turkey lettuce wrap - 170g lean turkey, cheese slice, peppers/onion, avocado (40g), yogurt-based sauce (80-100g), plus 100g raw sweet potato fries on the side - Roberto's own estimate 600-675kcal/55-60g protein/35-40g carb/25-30g fat, logged at midpoint approx 638kcal/58g protein/38g carb/28g fat/~6g fiber (fiber estimated). Day total so far: 906kcal/93g protein/51g carb/35g fat/8g fiber. Dinner: ground beef/spinach/marinara/lentil bowl - 130g lean ground beef (90/10), 100g spinach, 125g marinara, 120g cooked lentils - approx 435kcal/49g protein/35g carb/13g fat/14g fiber. Day total: 1,341kcal/142g protein/86g carb/48g fat/22g fiber - fiber caught up nicely from the light morning. Third strong full day of the new tracking week.</t>
         </is>
       </c>
       <c r="J13" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2433,7 +2433,7 @@
       <c r="H13" s="18" t="n"/>
       <c r="I13" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%. Lunch: turkey lettuce wrap - 170g lean turkey, cheese slice, peppers/onion, avocado (40g), yogurt-based sauce (80-100g), plus 100g raw sweet potato fries on the side - Roberto's own estimate 600-675kcal/55-60g protein/35-40g carb/25-30g fat, logged at midpoint approx 638kcal/58g protein/38g carb/28g fat/~6g fiber (fiber estimated). Day total so far: 906kcal/93g protein/51g carb/35g fat/8g fiber. Dinner: ground beef/spinach/marinara/lentil bowl - 130g lean ground beef (90/10), 100g spinach, 125g marinara, 120g cooked lentils - approx 435kcal/49g protein/35g carb/13g fat/14g fiber. Day total: 1,341kcal/142g protein/86g carb/48g fat/22g fiber - fiber caught up nicely from the light morning. Third strong full day of the new tracking week.</t>
+          <t>Breakfast: 1 whole egg, 150g egg whites, 75g cottage cheese, 100g mushrooms, 30-40g onion, 15g spinach, 50-60g pico de gallo - approx 268kcal/35g protein/13g carb/7g fat/2g fiber. Day 3 of tracking week (Sun 8/23-Sat 8/29). Ring synced this morning: sleep 8h36m (first real capture since Aug 15), HR 83, HRV 108ms (rebounded from 40ms Sunday), BP 127/89 (down from 131/92 Sunday), SpO2 98%. Dinner: turkey lettuce wrap - 170g lean turkey, cheese slice, peppers/onion, avocado (40g), yogurt-based sauce (80-100g), plus 100g raw sweet potato fries on the side - Roberto's own estimate 600-675kcal/55-60g protein/35-40g carb/25-30g fat, logged at midpoint approx 638kcal/58g protein/38g carb/28g fat/~6g fiber (fiber estimated). Day total so far: 906kcal/93g protein/51g carb/35g fat/8g fiber. Lunch: ground beef/spinach/marinara/lentil bowl - 130g lean ground beef (90/10), 100g spinach, 125g marinara, 120g cooked lentils - approx 435kcal/49g protein/35g carb/13g fat/14g fiber. Day total: 1,341kcal/142g protein/86g carb/48g fat/22g fiber - fiber caught up nicely from the light morning. Third strong full day of the new tracking week.</t>
         </is>
       </c>
       <c r="J13" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6456,14 +6456,31 @@
       <c r="A16" s="32" t="n">
         <v>46260</v>
       </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
+      <c r="B16" s="18" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>43</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>97</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>135</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>91</v>
+      </c>
       <c r="H16" s="18" t="n"/>
       <c r="I16" s="18" t="n"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ring sync 9:01am. Sleep 5h11m (same figure as yesterday's 11:16am sync - coincidental or a stale cached read, not reconciled). HR 66bpm (well within normal, lower than recent readings). BP 135/91 - highest systolic yet in this stretch (prior: 129/89, 131/92, 127/89, 127/90), diastolic still Stage 2. HRV 43ms - third low reading out of four total this week (40, 108, 40, now 43) - the 108ms looks like the outlier, not the low readings. SpO2 97%. Pressure score 30 (lowest yet; prior 47, 53, 47).</t>
+        </is>
+      </c>
       <c r="K16" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C16,$A$5:$A16,"&gt;="&amp;(A16-6),$A$5:$A16,"&lt;="&amp;A16),"")</f>
         <v/>
@@ -9167,16 +9184,30 @@
       <c r="N15" s="18" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="n"/>
+      <c r="A16" s="29" t="n">
+        <v>46260</v>
+      </c>
       <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
+      <c r="C16" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
+      <c r="E16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
+      <c r="I16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" s="18" t="n"/>
       <c r="L16" s="18" t="n"/>
       <c r="M16" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2457,14 +2457,20 @@
       <c r="A14" s="32" t="n">
         <v>46260</v>
       </c>
-      <c r="B14" s="30" t="n"/>
+      <c r="B14" s="30" t="n">
+        <v>196</v>
+      </c>
       <c r="C14" s="18" t="n"/>
       <c r="D14" s="18" t="n"/>
       <c r="E14" s="18" t="n"/>
       <c r="F14" s="18" t="n"/>
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target.</t>
+        </is>
+      </c>
       <c r="J14" s="31">
         <f>IF(C14="","",C14-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2460,15 +2460,25 @@
       <c r="B14" s="30" t="n">
         <v>196</v>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
+      <c r="C14" s="18" t="n">
+        <v>419</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>7</v>
+      </c>
       <c r="H14" s="18" t="n"/>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target.</t>
+          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target. Breakfast: 185g egg whites, 1 whole egg, 53g Kodiak protein pancake mix, 75g berries, 10g pure maple syrup, double espresso (black) - approx 419kcal/41g protein/45g carb/8g fat/7g fiber. Day 4 of tracking week (Sun 8/23-Sat 8/29).</t>
         </is>
       </c>
       <c r="J14" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2461,24 +2461,24 @@
         <v>196</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>419</v>
+        <v>843</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H14" s="18" t="n"/>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target. Breakfast: 185g egg whites, 1 whole egg, 53g Kodiak protein pancake mix, 75g berries, 10g pure maple syrup, double espresso (black) - approx 419kcal/41g protein/45g carb/8g fat/7g fiber. Day 4 of tracking week (Sun 8/23-Sat 8/29).</t>
+          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target. Breakfast: 185g egg whites, 1 whole egg, 53g Kodiak protein pancake mix, 75g berries, 10g pure maple syrup, double espresso (black) - approx 419kcal/41g protein/45g carb/8g fat/7g fiber. Day 4 of tracking week (Sun 8/23-Sat 8/29). Lunch: 140g grilled chicken breast, 100g black beans (drained), 60g arugula, 100g cherry tomatoes, 40g avocado, cilantro, lime juice, black pepper/cumin/chili powder - approx 424kcal/52g protein/27g carb/12g fat/11g fiber. Day total so far: 843kcal/93g protein/72g carb/20g fat/18g fiber.</t>
         </is>
       </c>
       <c r="J14" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6490,11 +6490,15 @@
       <c r="G16" s="18" t="n">
         <v>91</v>
       </c>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
+      <c r="H16" s="18" t="n">
+        <v>2920</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>14.63</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Ring sync 9:01am. Sleep 5h11m (same figure as yesterday's 11:16am sync - coincidental or a stale cached read, not reconciled). HR 66bpm (well within normal, lower than recent readings). BP 135/91 - highest systolic yet in this stretch (prior: 129/89, 131/92, 127/89, 127/90), diastolic still Stage 2. HRV 43ms - third low reading out of four total this week (40, 108, 40, now 43) - the 108ms looks like the outlier, not the low readings. SpO2 97%. Pressure score 30 (lowest yet; prior 47, 53, 47).</t>
+          <t>Ring sync 9:01am. Sleep 5h11m (same figure as yesterday's 11:16am sync - coincidental or a stale cached read, not reconciled). HR 66bpm (well within normal, lower than recent readings). BP 135/91 - highest systolic yet in this stretch (prior: 129/89, 131/92, 127/89, 127/90), diastolic still Stage 2. HRV 43ms - third low reading out of four total this week (40, 108, 40, now 43) - the 108ms looks like the outlier, not the low readings. SpO2 97%. Pressure score 30 (lowest yet; prior 47, 53, 47). | Tonal end-of-workout summary, 7:19pm. Volume 2,920 lbs, Duration 14:38, Movement Target 100%, Calories Burned 46, Work 7.2 kJ, Time Under Tension 4:52, Coaching Cues 0. App compared to same workout on 8/3/26: volume -348 lbs, duration -0:26, work -1.5kJ, TUT +0:15, calories -1, cues -1. Lightest volume of the week by a wide margin (prior: 4,792, 4,078, 4,717, 4,629 lbs) - likely a different/lighter workout program, still 100% movement target.</t>
         </is>
       </c>
       <c r="K16" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2461,24 +2461,24 @@
         <v>196</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>843</v>
+        <v>1370</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H14" s="18" t="n"/>
       <c r="I14" s="18" t="inlineStr">
         <is>
-          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target. Breakfast: 185g egg whites, 1 whole egg, 53g Kodiak protein pancake mix, 75g berries, 10g pure maple syrup, double espresso (black) - approx 419kcal/41g protein/45g carb/8g fat/7g fiber. Day 4 of tracking week (Sun 8/23-Sat 8/29). Lunch: 140g grilled chicken breast, 100g black beans (drained), 60g arugula, 100g cherry tomatoes, 40g avocado, cilantro, lime juice, black pepper/cumin/chili powder - approx 424kcal/52g protein/27g carb/12g fat/11g fiber. Day total so far: 843kcal/93g protein/72g carb/20g fat/18g fiber.</t>
+          <t>Weighed in 196.0 lb (down 5.0 lb from Aug 15 start, down 1.0 lb from Aug 24). Third consecutive drop (198.0 -&gt; 197.0 -&gt; 196.0), pace still running well ahead of the ~1lb/week target. Breakfast: 185g egg whites, 1 whole egg, 53g Kodiak protein pancake mix, 75g berries, 10g pure maple syrup, double espresso (black) - approx 419kcal/41g protein/45g carb/8g fat/7g fiber. Day 4 of tracking week (Sun 8/23-Sat 8/29). Lunch: 140g grilled chicken breast, 100g black beans (drained), 60g arugula, 100g cherry tomatoes, 40g avocado, cilantro, lime juice, black pepper/cumin/chili powder - approx 424kcal/52g protein/27g carb/12g fat/11g fiber. Day total so far: 843kcal/93g protein/72g carb/20g fat/18g fiber. Dinner: ahi tuna poke bowl (no rice) - 160g ahi tuna, 80-100g arugula, 100g cucumber, 75g edamame, 30-40g seaweed salad, 40g avocado, 50g carrots, 60g mango, cilantro/scallions/jalapeno, 5g sesame seeds, lime - approx 527kcal/53g protein/38g carb/20g fat/12g fiber. Day total: 1,370kcal/146g protein/110g carb/40g fat/30g fiber - protein 9g shy of the 155g floor, fiber 5g shy of 35g. Fourth strong full day of the new tracking week.</t>
         </is>
       </c>
       <c r="J14" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6514,14 +6514,31 @@
       <c r="A17" s="32" t="n">
         <v>46261</v>
       </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
+      <c r="B17" s="18" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>67</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>98</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>123</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>86</v>
+      </c>
       <c r="H17" s="18" t="n"/>
       <c r="I17" s="18" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ring sync 10:00am. Sleep 6h26m. HR 67bpm. BP 123/86 - best reading of the whole stretch, better than the 129/89 Aug 15 baseline. SpO2 98%. HRV 25ms - lowest reading yet (prior: 40, 108, 40, 43); now 4 of 5 readings this week have been low, reinforcing the concern rather than resolving it. Pressure score 50.</t>
+        </is>
+      </c>
       <c r="K17" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C17,$A$5:$A17,"&gt;="&amp;(A17-6),$A$5:$A17,"&lt;="&amp;A17),"")</f>
         <v/>
@@ -9234,16 +9251,30 @@
       <c r="N16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n"/>
+      <c r="A17" s="29" t="n">
+        <v>46261</v>
+      </c>
       <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
+      <c r="E17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="18" t="n"/>
-      <c r="I17" s="18" t="n"/>
-      <c r="J17" s="18" t="n"/>
+      <c r="I17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" s="18" t="n"/>
       <c r="L17" s="18" t="n"/>
       <c r="M17" s="18" t="n"/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2503,13 +2503,27 @@
         <v>46261</v>
       </c>
       <c r="B15" s="30" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
+      <c r="C15" s="18" t="n">
+        <v>248</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 50g Nancys low-fat cottage cheese, 40g pico de gallo, 40g blueberries, 40g 2% milk, double espresso (2 shots) - approx 248kcal/29g protein/14g carb/7g fat/1g fiber (fat/fiber estimated, rest per Roberto). Day 5 of tracking week (Sun 8/23-Sat 8/29).</t>
+        </is>
+      </c>
       <c r="J15" s="31">
         <f>IF(C15="","",C15-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2504,24 +2504,24 @@
       </c>
       <c r="B15" s="30" t="n"/>
       <c r="C15" s="18" t="n">
-        <v>248</v>
+        <v>708</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H15" s="18" t="n"/>
       <c r="I15" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 1 whole egg, 50g Nancys low-fat cottage cheese, 40g pico de gallo, 40g blueberries, 40g 2% milk, double espresso (2 shots) - approx 248kcal/29g protein/14g carb/7g fat/1g fiber (fat/fiber estimated, rest per Roberto). Day 5 of tracking week (Sun 8/23-Sat 8/29).</t>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 50g Nancys low-fat cottage cheese, 40g pico de gallo, 40g blueberries, 40g 2% milk, double espresso (2 shots) - approx 248kcal/29g protein/14g carb/7g fat/1g fiber (fat/fiber estimated, rest per Roberto). Day 5 of tracking week (Sun 8/23-Sat 8/29). Lunch: ahi tuna poke bowl with brown rice - 125g ahi tuna, 100g brown rice, 50g edamame, 40g mango, 25g seaweed salad, 30g avocado, 60g cucumber, 30g carrots, 3g sesame seeds, light soy/ponzu - approx 460kcal/41g protein/49g carb/12g fat/9g fiber. Day total so far: 708kcal/70g protein/63g carb/19g fat/10g fiber.</t>
         </is>
       </c>
       <c r="J15" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2504,24 +2504,24 @@
       </c>
       <c r="B15" s="30" t="n"/>
       <c r="C15" s="18" t="n">
-        <v>708</v>
+        <v>1370</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H15" s="18" t="n"/>
       <c r="I15" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: 150g egg whites, 1 whole egg, 50g Nancys low-fat cottage cheese, 40g pico de gallo, 40g blueberries, 40g 2% milk, double espresso (2 shots) - approx 248kcal/29g protein/14g carb/7g fat/1g fiber (fat/fiber estimated, rest per Roberto). Day 5 of tracking week (Sun 8/23-Sat 8/29). Lunch: ahi tuna poke bowl with brown rice - 125g ahi tuna, 100g brown rice, 50g edamame, 40g mango, 25g seaweed salad, 30g avocado, 60g cucumber, 30g carrots, 3g sesame seeds, light soy/ponzu - approx 460kcal/41g protein/49g carb/12g fat/9g fiber. Day total so far: 708kcal/70g protein/63g carb/19g fat/10g fiber.</t>
+          <t>Breakfast: 150g egg whites, 1 whole egg, 50g Nancys low-fat cottage cheese, 40g pico de gallo, 40g blueberries, 40g 2% milk, double espresso (2 shots) - approx 248kcal/29g protein/14g carb/7g fat/1g fiber (fat/fiber estimated, rest per Roberto). Day 5 of tracking week (Sun 8/23-Sat 8/29). Lunch: ahi tuna poke bowl with brown rice - 125g ahi tuna, 100g brown rice, 50g edamame, 40g mango, 25g seaweed salad, 30g avocado, 60g cucumber, 30g carrots, 3g sesame seeds, light soy/ponzu - approx 460kcal/41g protein/49g carb/12g fat/9g fiber. Day total so far: 708kcal/70g protein/63g carb/19g fat/10g fiber. Dinner: skirt steak tacos, no rice/beans/avocado/cheese/crema - 2 corn tortillas, ~140g cooked skirt steak, grilled green onions, pico de gallo, lime/cilantro/jalapeno - Robertos own estimate 450-500kcal/38-43g protein, logged at midpoint approx 475kcal/41g protein/24g carb/24g fat/3g fiber (carb/fat/fiber estimated). Snack: 20g walnuts, 20g pistachios weighed in shells (~9-11g edible) - approx 187kcal/5g protein/5g carb/18g fat/2g fiber. Day total: 1,370kcal/116g protein/92g carb/61g fat/15g fiber - fat closed at 94% of the 65g budget, tightest fat margin of the week. Fifth day of the new tracking week.</t>
         </is>
       </c>
       <c r="J15" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2546,13 +2546,27 @@
         <v>46262</v>
       </c>
       <c r="B16" s="30" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
+      <c r="C16" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: carne asada egg scramble - ~0.5 whole egg, 80-90g egg whites, 45-50g carne asada, 35-40g spinach - approx 208kcal/27g protein/3g carb/11g fat/1g fiber (carb/fat/fiber estimated, rest per Roberto). Day 6 of tracking week (Sun 8/23-Sat 8/29).</t>
+        </is>
+      </c>
       <c r="J16" s="31">
         <f>IF(C16="","",C16-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2547,24 +2547,24 @@
       </c>
       <c r="B16" s="30" t="n"/>
       <c r="C16" s="18" t="n">
-        <v>208</v>
+        <v>1383</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H16" s="18" t="n"/>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: carne asada egg scramble - ~0.5 whole egg, 80-90g egg whites, 45-50g carne asada, 35-40g spinach - approx 208kcal/27g protein/3g carb/11g fat/1g fiber (carb/fat/fiber estimated, rest per Roberto). Day 6 of tracking week (Sun 8/23-Sat 8/29).</t>
+          <t>Breakfast: carne asada egg scramble - ~0.5 whole egg, 80-90g egg whites, 45-50g carne asada, 35-40g spinach - approx 208kcal/27g protein/3g carb/11g fat/1g fiber (carb/fat/fiber estimated, rest per Roberto). Day 6 of tracking week (Sun 8/23-Sat 8/29). Lunch (restaurant, 2 courses): Appetizer - 35g octopus, 30g prosciutto, 35g soft white cheese/cream, 90g watermelon, 15g avocado, 25g small vegetables/garnish, 20g sauce/dressing - approx 331kcal/24g protein/14g carb/21g fat/2g fiber. Main - 210g skin-on fish fillet, 80g zucchini, 60g broccolini/asparagus/greens, 40g green herb sauce - approx 594kcal/47g protein/7g carb/40g fat/3g fiber. Lunch total approx 925kcal/71g protein/21g carb/61g fat/5g fiber. Evening snack: 100g plain Greek yogurt, 100g mixed berries, 80g banana, 1/2 scoop protein powder (~15g), 1/2 tsp chia seeds - Robertos own estimate 250kcal/24-27g protein/32-35g carb/3-4g fat, logged at midpoint approx 250kcal/26g protein/33g carb/4g fat/6g fiber (fiber estimated). Day total: 1,383kcal/124g protein/57g carb/76g fat/12g fiber - fat closed 11g OVER the 65g budget, driven by the rich restaurant lunch (skin-on fish, cheese, prosciutto, oil-based sauces). Sixth day of the new tracking week.</t>
         </is>
       </c>
       <c r="J16" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2547,24 +2547,24 @@
       </c>
       <c r="B16" s="30" t="n"/>
       <c r="C16" s="18" t="n">
-        <v>1383</v>
+        <v>1496</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="F16" s="18" t="n">
         <v>76</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H16" s="18" t="n"/>
       <c r="I16" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: carne asada egg scramble - ~0.5 whole egg, 80-90g egg whites, 45-50g carne asada, 35-40g spinach - approx 208kcal/27g protein/3g carb/11g fat/1g fiber (carb/fat/fiber estimated, rest per Roberto). Day 6 of tracking week (Sun 8/23-Sat 8/29). Lunch (restaurant, 2 courses): Appetizer - 35g octopus, 30g prosciutto, 35g soft white cheese/cream, 90g watermelon, 15g avocado, 25g small vegetables/garnish, 20g sauce/dressing - approx 331kcal/24g protein/14g carb/21g fat/2g fiber. Main - 210g skin-on fish fillet, 80g zucchini, 60g broccolini/asparagus/greens, 40g green herb sauce - approx 594kcal/47g protein/7g carb/40g fat/3g fiber. Lunch total approx 925kcal/71g protein/21g carb/61g fat/5g fiber. Evening snack: 100g plain Greek yogurt, 100g mixed berries, 80g banana, 1/2 scoop protein powder (~15g), 1/2 tsp chia seeds - Robertos own estimate 250kcal/24-27g protein/32-35g carb/3-4g fat, logged at midpoint approx 250kcal/26g protein/33g carb/4g fat/6g fiber (fiber estimated). Day total: 1,383kcal/124g protein/57g carb/76g fat/12g fiber - fat closed 11g OVER the 65g budget, driven by the rich restaurant lunch (skin-on fish, cheese, prosciutto, oil-based sauces). Sixth day of the new tracking week.</t>
+          <t>Breakfast: carne asada egg scramble - ~0.5 whole egg, 80-90g egg whites, 45-50g carne asada, 35-40g spinach - approx 208kcal/27g protein/3g carb/11g fat/1g fiber (carb/fat/fiber estimated, rest per Roberto). Day 6 of tracking week (Sun 8/23-Sat 8/29). Lunch (restaurant, 2 courses): Appetizer - 35g octopus, 30g prosciutto, 35g soft white cheese/cream, 90g watermelon, 15g avocado, 25g small vegetables/garnish, 20g sauce/dressing - approx 331kcal/24g protein/14g carb/21g fat/2g fiber. Main - 210g skin-on fish fillet, 80g zucchini, 60g broccolini/asparagus/greens, 40g green herb sauce - approx 594kcal/47g protein/7g carb/40g fat/3g fiber. Lunch total approx 925kcal/71g protein/21g carb/61g fat/5g fiber. Evening snack: 100g plain Greek yogurt, 100g mixed berries, 80g banana, 1/2 scoop protein powder (~15g), 1/2 tsp chia seeds - Robertos own estimate 250kcal/24-27g protein/32-35g carb/3-4g fat, logged at midpoint approx 250kcal/26g protein/33g carb/4g fat/6g fiber (fiber estimated). Day total: 1,383kcal/124g protein/57g carb/76g fat/12g fiber - fat closed 11g OVER the 65g budget, driven by the rich restaurant lunch (skin-on fish, cheese, prosciutto, oil-based sauces). Sixth day of the new tracking week. Additional snack: 189g fresh mango - approx 113kcal/2g protein/29g carb/0g fat/3g fiber (per Robertos own figures). Day total: 1,496kcal/126g protein/86g carb/76g fat/15g fiber - fat still 11g over the 65g budget.</t>
         </is>
       </c>
       <c r="J16" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -6607,8 +6607,17 @@
       <c r="E19" s="18" t="n"/>
       <c r="F19" s="18" t="n"/>
       <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
-      <c r="I19" s="18" t="n"/>
+      <c r="H19" s="18" t="n">
+        <v>4308</v>
+      </c>
+      <c r="I19" s="18" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Tonal end-of-workout summary. Volume 4,308 lbs, Duration 15:02, Movement Target 100%, Calories Burned 71, Work 8.7 kJ, Time Under Tension 5:57, Coaching Cues 0. Middle-of-pack volume for the week (prior: 4,717 Sun, 4,629 Mon, 2,920 Wed; no session Tue/Thu/Fri) - still 100% movement target, 0 cues. Last day of the tracking week (Sat 8/29).</t>
+        </is>
+      </c>
       <c r="K19" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C19,$A$5:$A19,"&gt;="&amp;(A19-6),$A$5:$A19,"&lt;="&amp;A19),"")</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2589,13 +2589,27 @@
         <v>46263</v>
       </c>
       <c r="B17" s="30" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
+      <c r="C17" s="18" t="n">
+        <v>304</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>33</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>6</v>
+      </c>
       <c r="H17" s="18" t="n"/>
-      <c r="I17" s="18" t="n"/>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29).</t>
+        </is>
+      </c>
       <c r="J17" s="31">
         <f>IF(C17="","",C17-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2590,24 +2590,24 @@
       </c>
       <c r="B17" s="30" t="n"/>
       <c r="C17" s="18" t="n">
-        <v>304</v>
+        <v>1249</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H17" s="18" t="n"/>
       <c r="I17" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29).</t>
+          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29). Lunch: Wendy's Spicy Chicken Sandwich Combo — spicy chicken sandwich (breaded chicken breast, lettuce, mayo, bun), medium natural-cut fries, ketchup — approx 945kcal/33g protein/112g carb/38g fat/7g fiber (Wendy's published nutrition, fry size estimated from photo). Day total so far: 1,249kcal/65g protein/145g carb/45g fat/13g fiber.</t>
         </is>
       </c>
       <c r="J17" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2590,24 +2590,24 @@
       </c>
       <c r="B17" s="30" t="n"/>
       <c r="C17" s="18" t="n">
-        <v>1249</v>
+        <v>1629</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>45</v>
+        <v>58.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H17" s="18" t="n"/>
       <c r="I17" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29). Lunch: Wendy's Spicy Chicken Sandwich Combo — spicy chicken sandwich (breaded chicken breast, lettuce, mayo, bun), medium natural-cut fries, ketchup — approx 945kcal/33g protein/112g carb/38g fat/7g fiber (Wendy's published nutrition, fry size estimated from photo). Day total so far: 1,249kcal/65g protein/145g carb/45g fat/13g fiber.</t>
+          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29). Lunch: Wendy's Spicy Chicken Sandwich Combo — spicy chicken sandwich (breaded chicken breast, lettuce, mayo, bun), medium natural-cut fries, ketchup — approx 945kcal/33g protein/112g carb/38g fat/7g fiber (Wendy's published nutrition, fry size estimated from photo). Day total so far: 1,249kcal/65g protein/145g carb/45g fat/13g fiber. Dinner: Mediterranean baked cod with tomatoes and capers, roasted broccoli, roasted zucchini/yellow squash (Roberto's own estimate: 380kcal/43g protein/20g carb/13.5g fat/8g fiber). Day total: 1,629kcal/108g protein/165g carb/58.5g fat/21g fiber - carbs closed 5g over the 160g budget, fat landed right at the 90% watch line, protein 47g shy of the 155g floor. Final day of the tracking week (Sun 8/23-Sat 8/29) now complete - full week: 10,112kcal/962g protein across all 7 days.</t>
         </is>
       </c>
       <c r="J17" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2632,13 +2632,27 @@
         <v>46264</v>
       </c>
       <c r="B18" s="30" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
+      <c r="C18" s="18" t="n">
+        <v>210</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="H18" s="18" t="n"/>
-      <c r="I18" s="18" t="n"/>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>Breakfast: 100g plain yogurt, 50g mixed berries, 1 scoop protein powder - approx 210kcal/28g protein/15g carb/5g fat/1g fiber. First entry of a new tracking week (Sun 8/30-Sat 9/5) — prior week (Sun 8/23-Sat 8/29) closed at 10,112kcal/962g protein across all 7 days.</t>
+        </is>
+      </c>
       <c r="J18" s="31">
         <f>IF(C18="","",C18-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2590,24 +2590,24 @@
       </c>
       <c r="B17" s="30" t="n"/>
       <c r="C17" s="18" t="n">
-        <v>1629</v>
+        <v>1839</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>58.5</v>
+        <v>63.5</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="18" t="n"/>
       <c r="I17" s="18" t="inlineStr">
         <is>
-          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29). Lunch: Wendy's Spicy Chicken Sandwich Combo — spicy chicken sandwich (breaded chicken breast, lettuce, mayo, bun), medium natural-cut fries, ketchup — approx 945kcal/33g protein/112g carb/38g fat/7g fiber (Wendy's published nutrition, fry size estimated from photo). Day total so far: 1,249kcal/65g protein/145g carb/45g fat/13g fiber. Dinner: Mediterranean baked cod with tomatoes and capers, roasted broccoli, roasted zucchini/yellow squash (Roberto's own estimate: 380kcal/43g protein/20g carb/13.5g fat/8g fiber). Day total: 1,629kcal/108g protein/165g carb/58.5g fat/21g fiber - carbs closed 5g over the 160g budget, fat landed right at the 90% watch line, protein 47g shy of the 155g floor. Final day of the tracking week (Sun 8/23-Sat 8/29) now complete - full week: 10,112kcal/962g protein across all 7 days.</t>
+          <t>Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 100g egg whites, 75g mixed berries, water, hot sauce (negligible) - approx 304kcal/32g protein/33g carb/7g fat/6g fiber. Day 7 (final day) of tracking week (Sun 8/23-Sat 8/29). Lunch: Wendy's Spicy Chicken Sandwich Combo — spicy chicken sandwich (breaded chicken breast, lettuce, mayo, bun), medium natural-cut fries, ketchup — approx 945kcal/33g protein/112g carb/38g fat/7g fiber (Wendy's published nutrition, fry size estimated from photo). Day total so far: 1,249kcal/65g protein/145g carb/45g fat/13g fiber. Dinner: Mediterranean baked cod with tomatoes and capers, roasted broccoli, roasted zucchini/yellow squash (Roberto's own estimate: 380kcal/43g protein/20g carb/13.5g fat/8g fiber). Day total: 1,629kcal/108g protein/165g carb/58.5g fat/21g fiber - carbs closed 5g over the 160g budget, fat landed right at the 90% watch line, protein 47g shy of the 155g floor. Final day of the tracking week (Sun 8/23-Sat 8/29) now complete - full week: 10,112kcal/962g protein across all 7 days. Snack (corrected — this was originally mis-logged as a new day/Sunday by mistake; it's Saturday evening, ~8:39pm): 100g plain yogurt, 50g mixed berries, 1 scoop protein powder - approx 210kcal/28g protein/15g carb/5g fat/1g fiber. Day total (corrected): 1,839kcal/136g protein/180g carb/63.5g fat/22g fiber - carbs now 20g over the 160g budget, fat closed right at 98% of budget, protein closed at 88% of the 155g floor, calories closed at 99% of budget. Full week (Sun 8/23-Sat 8/29): 10,322kcal/990g protein across all 7 days.</t>
         </is>
       </c>
       <c r="J17" s="31">
@@ -2632,27 +2632,13 @@
         <v>46264</v>
       </c>
       <c r="B18" s="30" t="n"/>
-      <c r="C18" s="18" t="n">
-        <v>210</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>28</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="18" t="n">
-        <v>1</v>
-      </c>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
       <c r="H18" s="18" t="n"/>
-      <c r="I18" s="18" t="inlineStr">
-        <is>
-          <t>Breakfast: 100g plain yogurt, 50g mixed berries, 1 scoop protein powder - approx 210kcal/28g protein/15g carb/5g fat/1g fiber. First entry of a new tracking week (Sun 8/30-Sat 9/5) — prior week (Sun 8/23-Sat 8/29) closed at 10,112kcal/962g protein across all 7 days.</t>
-        </is>
-      </c>
+      <c r="I18" s="18" t="n"/>
       <c r="J18" s="31">
         <f>IF(C18="","",C18-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2632,13 +2632,27 @@
         <v>46264</v>
       </c>
       <c r="B18" s="30" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
+      <c r="C18" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" s="18" t="n"/>
-      <c r="I18" s="18" t="n"/>
+      <c r="I18" s="18" t="inlineStr">
+        <is>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days.</t>
+        </is>
+      </c>
       <c r="J18" s="31">
         <f>IF(C18="","",C18-Targets!$B$12)</f>
         <v/>
@@ -6651,8 +6665,17 @@
       <c r="E20" s="18" t="n"/>
       <c r="F20" s="18" t="n"/>
       <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="n"/>
-      <c r="I20" s="18" t="n"/>
+      <c r="H20" s="18" t="n">
+        <v>4619</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Tonal end-of-workout summary, 9:12am. Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0. Up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5).</t>
+        </is>
+      </c>
       <c r="K20" s="31">
         <f>IFERROR(AVERAGEIFS($C$5:$C20,$A$5:$A20,"&gt;="&amp;(A20-6),$A$5:$A20,"&lt;="&amp;A20),"")</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2633,24 +2633,24 @@
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n">
-        <v>5</v>
+        <v>335</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days.</t>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber.</t>
         </is>
       </c>
       <c r="J18" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2633,24 +2633,24 @@
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n">
-        <v>335</v>
+        <v>815</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber.</t>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber.</t>
         </is>
       </c>
       <c r="J18" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2633,24 +2633,24 @@
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n">
-        <v>815</v>
+        <v>950</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber.</t>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber.</t>
         </is>
       </c>
       <c r="J18" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2633,24 +2633,24 @@
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n">
-        <v>950</v>
+        <v>1085</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>22</v>
+        <v>24.5</v>
       </c>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber.</t>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber. Snack: 42 pistachio kernels (Roberto's own estimate) - approx 135kcal/5g protein/7g carb/11g fat/2.5g fiber. Day total: 1,085kcal/105g protein/97g carb/32g fat/24.5g fiber.</t>
         </is>
       </c>
       <c r="J18" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2633,24 +2633,24 @@
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n">
-        <v>1085</v>
+        <v>1425</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>24.5</v>
+        <v>30.5</v>
       </c>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber. Snack: 42 pistachio kernels (Roberto's own estimate) - approx 135kcal/5g protein/7g carb/11g fat/2.5g fiber. Day total: 1,085kcal/105g protein/97g carb/32g fat/24.5g fiber.</t>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber. Snack: 42 pistachio kernels (Roberto's own estimate) - approx 135kcal/5g protein/7g carb/11g fat/2.5g fiber. Day total: 1,085kcal/105g protein/97g carb/32g fat/24.5g fiber. Snack (smoothie): 150g frozen strawberries, 2 scoops chocolate protein powder, 1 scoop PB2, water (Roberto's own estimate) - approx 340kcal/54g protein/28g carb/5g fat/6g fiber. Day total: 1,425kcal/159g protein/125g carb/37g fat/30.5g fiber - protein floor (155g) cleared for the first time this stretch.</t>
         </is>
       </c>
       <c r="J18" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2633,24 +2633,24 @@
       </c>
       <c r="B18" s="30" t="n"/>
       <c r="C18" s="18" t="n">
-        <v>1425</v>
+        <v>1685</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>30.5</v>
+        <v>34.5</v>
       </c>
       <c r="H18" s="18" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
-          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber. Snack: 42 pistachio kernels (Roberto's own estimate) - approx 135kcal/5g protein/7g carb/11g fat/2.5g fiber. Day total: 1,085kcal/105g protein/97g carb/32g fat/24.5g fiber. Snack (smoothie): 150g frozen strawberries, 2 scoops chocolate protein powder, 1 scoop PB2, water (Roberto's own estimate) - approx 340kcal/54g protein/28g carb/5g fat/6g fiber. Day total: 1,425kcal/159g protein/125g carb/37g fat/30.5g fiber - protein floor (155g) cleared for the first time this stretch.</t>
+          <t>Double espresso (black, no sugar/cream) - negligible calories, approx 5kcal/0g protein/1g carb/0g fat/0g fiber. Tonal session this morning (9:12am): Volume 4,619 lbs, Duration 12:09, Movement Target 100%, Calories Burned 113, Work 8.8 kJ, Time Under Tension 6:12, Coaching Cues 0 - up from Sat's 4,308 lbs. First day of a new tracking week (Sun 8/30-Sat 9/5) - prior week (Sun 8/23-Sat 8/29) closed at 10,322kcal/990g protein across all 7 days. Breakfast: Kodiak Power Cakes - 40g Kodiak protein pancake mix, 1 whole egg, 150g egg whites, 75g mixed berries (blueberries/blackberries), water, hot sauce (negligible) - approx 330kcal/38g protein/33g carb/7g fat/6g fiber. Day total: 335kcal/38g protein/34g carb/7g fat/6g fiber. Lunch: 440g turkey chili (ground turkey, kidney beans, white beans, tomato broth, onion, jalapeno) + 40g plain nonfat Greek yogurt - approx 480kcal/47g protein/43g carb/11g fat/12g fiber. Day total: 815kcal/85g protein/77g carb/18g fat/18g fiber. Snack: 100g plain nonfat Greek yogurt, 40g mixed berries, 5g protein powder, 5g chia seeds (Roberto's own estimate) - approx 135kcal/15g protein/13g carb/3g fat/4g fiber. Day total: 950kcal/100g protein/90g carb/21g fat/22g fiber. Snack: 42 pistachio kernels (Roberto's own estimate) - approx 135kcal/5g protein/7g carb/11g fat/2.5g fiber. Day total: 1,085kcal/105g protein/97g carb/32g fat/24.5g fiber. Snack (smoothie): 150g frozen strawberries, 2 scoops chocolate protein powder, 1 scoop PB2, water (Roberto's own estimate) - approx 340kcal/54g protein/28g carb/5g fat/6g fiber. Day total: 1,425kcal/159g protein/125g carb/37g fat/30.5g fiber - protein floor (155g) cleared for the first time this stretch. Dinner (final meal): 100g salmon, 100g broccoli, 100g squash (Roberto's own estimate) - approx 260kcal/26g protein/13g carb/13g fat/4g fiber. Day total: 1,685kcal/185g protein/138g carb/50g fat/34.5g fiber - protein closed at 119% of the 155g floor (well cleared), fiber essentially hit the 35g floor, calories closed at 91% of budget (tightest margin of the day, still under). Strong first day of the new tracking week (Sun 8/30-Sat 9/5).</t>
         </is>
       </c>
       <c r="J18" s="31">

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2675,13 +2675,27 @@
         <v>46265</v>
       </c>
       <c r="B19" s="30" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
+      <c r="C19" s="18" t="n">
+        <v>550</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>48</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>28</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>2.5</v>
+      </c>
       <c r="H19" s="18" t="n"/>
-      <c r="I19" s="18" t="n"/>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>Day 2 of tracking week (Sun 8/30-Sat 9/5). Breakfast: 3 scrambled eggs, 4 slices smoked salmon (~85-100g), 1/2 cup cooked oatmeal, capers + red onion, latte (Roberto's own estimate, ranges given, logged at midpoint) - approx 550kcal/48g protein/28g carb/26g fat/2.5g fiber. Day total: 550kcal/48g protein/28g carb/26g fat/2.5g fiber.</t>
+        </is>
+      </c>
       <c r="J19" s="31">
         <f>IF(C19="","",C19-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2718,13 +2718,27 @@
         <v>46266</v>
       </c>
       <c r="B20" s="30" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
+      <c r="C20" s="18" t="n">
+        <v>775</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>7</v>
+      </c>
       <c r="H20" s="18" t="n"/>
-      <c r="I20" s="18" t="n"/>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>Day 3 of tracking week (Sun 8/30-Sat 9/5). Breakfast: egg scramble (approx 3 whole eggs) with diced tomatoes, spinach, jalapenos, light oil (photo) - approx 280kcal/21g protein/6g carb/20g fat/2g fiber (Claude estimate from photo). Day total so far: 280kcal/21g protein/6g carb/20g fat/2g fiber. Lunch: grilled chicken breast (~180g), green beans (~100g), maduros/fried sweet plantains (~100g) (photo) - approx 495kcal/59g protein/39g carb/10g fat/5g fiber (Claude estimate from photo). Day total: 775kcal/80g protein/45g carb/30g fat/7g fiber - light day so far, calories at 42% of budget with dinner still ahead.</t>
+        </is>
+      </c>
       <c r="J20" s="31">
         <f>IF(C20="","",C20-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2790,13 +2790,27 @@
         <v>46268</v>
       </c>
       <c r="B22" s="30" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
+      <c r="C22" s="18" t="n">
+        <v>167</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>1</v>
+      </c>
       <c r="H22" s="18" t="n"/>
-      <c r="I22" s="18" t="n"/>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>Day 5 of tracking week (Sun 8/30-Sat 9/5) - Wednesday 9/2 had no entries logged, a gap day. Breakfast: 40g spinach, 1 whole egg, 160g egg whites, black coffee (Roberto's own estimate) - approx 167kcal/25g protein/3g carb/5g fat/1g fiber. Day total: 167kcal/25g protein/3g carb/5g fat/1g fiber.</t>
+        </is>
+      </c>
       <c r="J22" s="31">
         <f>IF(C22="","",C22-Targets!$B$12)</f>
         <v/>

--- a/coach/Pulso-Macro-Tracker.xlsx
+++ b/coach/Pulso-Macro-Tracker.xlsx
@@ -2791,24 +2791,24 @@
       </c>
       <c r="B22" s="30" t="n"/>
       <c r="C22" s="18" t="n">
-        <v>167</v>
+        <v>487</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F22" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" s="18" t="n">
         <v>5</v>
-      </c>
-      <c r="G22" s="18" t="n">
-        <v>1</v>
       </c>
       <c r="H22" s="18" t="n"/>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>Day 5 of tracking week (Sun 8/30-Sat 9/5) - Wednesday 9/2 had no entries logged, a gap day. Breakfast: 40g spinach, 1 whole egg, 160g egg whites, black coffee (Roberto's own estimate) - approx 167kcal/25g protein/3g carb/5g fat/1g fiber. Day total: 167kcal/25g protein/3g carb/5g fat/1g fiber.</t>
+          <t>Day 5 of tracking week (Sun 8/30-Sat 9/5) - Wednesday 9/2 had no entries logged, a gap day. Breakfast: 40g spinach, 1 whole egg, 160g egg whites, black coffee (Roberto's own estimate) - approx 167kcal/25g protein/3g carb/5g fat/1g fiber. Day total: 167kcal/25g protein/3g carb/5g fat/1g fiber. Second breakfast: Kodiak Buttermilk pancake (40g mix, water), 1 whole egg (~50g), 150g egg whites, salt/pepper/hot sauce (Claude estimate from Kodiak product nutrition + standard egg values) - approx 320kcal/35g protein/30g carb/7g fat/4g fiber. Day total: 487kcal/60g protein/33g carb/12g fat/5g fiber.</t>
         </is>
       </c>
       <c r="J22" s="31">
